--- a/research/traditional_assets/database/data/romania/romania_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_telecom_services.xlsx
@@ -647,10 +647,10 @@
         <v>0.7252280591380939</v>
       </c>
       <c r="X2">
-        <v>0.1302152283250686</v>
+        <v>0.1301994175580972</v>
       </c>
       <c r="Y2">
-        <v>0.5950128308130253</v>
+        <v>0.5950286415799966</v>
       </c>
       <c r="Z2">
         <v>1.112141689854689</v>
@@ -659,10 +659,10 @@
         <v>0.2503390999831306</v>
       </c>
       <c r="AB2">
-        <v>0.09818882910467236</v>
+        <v>0.09818225675745859</v>
       </c>
       <c r="AC2">
-        <v>0.1521502708784582</v>
+        <v>0.152156843225672</v>
       </c>
       <c r="AD2">
         <v>1786.3</v>
@@ -781,10 +781,10 @@
         <v>0.7252280591380939</v>
       </c>
       <c r="X3">
-        <v>0.1302152283250686</v>
+        <v>0.1301994175580972</v>
       </c>
       <c r="Y3">
-        <v>0.5950128308130253</v>
+        <v>0.5950286415799966</v>
       </c>
       <c r="Z3">
         <v>1.112141689854689</v>
@@ -793,10 +793,10 @@
         <v>0.2503390999831306</v>
       </c>
       <c r="AB3">
-        <v>0.09818882910467236</v>
+        <v>0.09818225675745859</v>
       </c>
       <c r="AC3">
-        <v>0.1521502708784582</v>
+        <v>0.152156843225672</v>
       </c>
       <c r="AD3">
         <v>1786.3</v>
@@ -1151,13 +1151,13 @@
         <v>1270.8</v>
       </c>
       <c r="L2">
-        <v>4020.33521855187</v>
+        <v>4020.56340108978</v>
       </c>
       <c r="M2">
         <v>2725.7</v>
       </c>
       <c r="N2">
-        <v>3688.93521855187</v>
+        <v>3689.16340108978</v>
       </c>
       <c r="O2">
         <v>1786.3</v>
@@ -1166,16 +1166,16 @@
         <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.0981888291046724</v>
+        <v>0.09818225675745861</v>
       </c>
       <c r="R2">
-        <v>0.08450933562955371</v>
+        <v>0.08450208546512961</v>
       </c>
       <c r="S2">
         <v>0.07540477932060501</v>
       </c>
       <c r="T2">
-        <v>0.061712779320605</v>
+        <v>0.060536779320605</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="W2">
-        <v>0.130215228325069</v>
+        <v>0.130199417558097</v>
       </c>
       <c r="X2">
-        <v>0.08450933562955371</v>
+        <v>0.08450208546512961</v>
       </c>
       <c r="Y2">
         <v>1.16178975104852</v>
@@ -1230,7 +1230,7 @@
         <v>1270.8</v>
       </c>
       <c r="AK2">
-        <v>0.07265964280446037</v>
+        <v>0.07264603383006794</v>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
@@ -1418,13 +1418,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>0.08450933562955372</v>
+        <v>0.08450208546512961</v>
       </c>
       <c r="C2">
-        <v>4020.33521855187</v>
+        <v>4020.56340108978</v>
       </c>
       <c r="D2">
-        <v>3688.93521855187</v>
+        <v>3689.16340108978</v>
       </c>
       <c r="E2">
         <v>-1786.3</v>
@@ -1469,19 +1469,19 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>0.08450933562955372</v>
+        <v>0.08450208546512961</v>
       </c>
       <c r="T2">
         <v>0.532748774085323</v>
       </c>
       <c r="U2">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V2">
         <v>0.16</v>
       </c>
       <c r="W2">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
@@ -1500,13 +1500,13 @@
         <v>0.01</v>
       </c>
       <c r="B3">
-        <v>0.08460652848575248</v>
+        <v>0.08458752992159144</v>
       </c>
       <c r="C3">
-        <v>3980.52509915074</v>
+        <v>3981.865599454249</v>
       </c>
       <c r="D3">
-        <v>3679.696099150739</v>
+        <v>3681.036599454249</v>
       </c>
       <c r="E3">
         <v>-1755.729</v>
@@ -1533,37 +1533,37 @@
         <v>680.4</v>
       </c>
       <c r="M3">
-        <v>2.245977829297876</v>
+        <v>2.203178429297876</v>
       </c>
       <c r="N3">
-        <v>678.1540221707021</v>
+        <v>678.1968215707021</v>
       </c>
       <c r="O3">
-        <v>108.5046435473123</v>
+        <v>108.5114914513123</v>
       </c>
       <c r="P3">
-        <v>569.6493786233898</v>
+        <v>569.6853301193898</v>
       </c>
       <c r="Q3">
-        <v>894.3493786233898</v>
+        <v>894.3853301193899</v>
       </c>
       <c r="R3">
         <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0.08483777847731963</v>
+        <v>0.08483046679634887</v>
       </c>
       <c r="T3">
         <v>0.5372690667139257</v>
       </c>
       <c r="U3">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V3">
         <v>0.16</v>
       </c>
       <c r="W3">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>302.941547830284</v>
+        <v>308.8265530163322</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1582,13 +1582,13 @@
         <v>0.02</v>
       </c>
       <c r="B4">
-        <v>0.08470372134195124</v>
+        <v>0.0846729743780533</v>
       </c>
       <c r="C4">
-        <v>3940.761143785972</v>
+        <v>3943.203523932275</v>
       </c>
       <c r="D4">
-        <v>3670.503143785972</v>
+        <v>3672.945523932275</v>
       </c>
       <c r="E4">
         <v>-1725.158</v>
@@ -1615,37 +1615,37 @@
         <v>680.4</v>
       </c>
       <c r="M4">
-        <v>4.491955658595752</v>
+        <v>4.406356858595752</v>
       </c>
       <c r="N4">
-        <v>675.9080443414042</v>
+        <v>675.9936431414043</v>
       </c>
       <c r="O4">
-        <v>108.1452870946247</v>
+        <v>108.1589829026247</v>
       </c>
       <c r="P4">
-        <v>567.7627572467795</v>
+        <v>567.8346602387796</v>
       </c>
       <c r="Q4">
-        <v>892.4627572467796</v>
+        <v>892.5346602387797</v>
       </c>
       <c r="R4">
         <v>0.02040816326530612</v>
       </c>
       <c r="S4">
-        <v>0.08517292424034606</v>
+        <v>0.08516554978738897</v>
       </c>
       <c r="T4">
         <v>0.5418816102124999</v>
       </c>
       <c r="U4">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V4">
         <v>0.16</v>
       </c>
       <c r="W4">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>151.470773915142</v>
+        <v>154.4132765081661</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1664,13 +1664,13 @@
         <v>0.03</v>
       </c>
       <c r="B5">
-        <v>0.08480091419815002</v>
+        <v>0.08475841883451513</v>
       </c>
       <c r="C5">
-        <v>3901.043007326076</v>
+        <v>3904.576939457982</v>
       </c>
       <c r="D5">
-        <v>3661.356007326076</v>
+        <v>3664.889939457983</v>
       </c>
       <c r="E5">
         <v>-1694.587</v>
@@ -1697,37 +1697,37 @@
         <v>680.4</v>
       </c>
       <c r="M5">
-        <v>6.737933487893628</v>
+        <v>6.609535287893628</v>
       </c>
       <c r="N5">
-        <v>673.6620665121063</v>
+        <v>673.7904647121063</v>
       </c>
       <c r="O5">
-        <v>107.785930641937</v>
+        <v>107.806474353937</v>
       </c>
       <c r="P5">
-        <v>565.8761358701693</v>
+        <v>565.9839903581693</v>
       </c>
       <c r="Q5">
-        <v>890.5761358701693</v>
+        <v>890.6839903581694</v>
       </c>
       <c r="R5">
         <v>0.03092783505154639</v>
       </c>
       <c r="S5">
-        <v>0.08551498022529058</v>
+        <v>0.08550754170607935</v>
       </c>
       <c r="T5">
         <v>0.5465892577007354</v>
       </c>
       <c r="U5">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V5">
         <v>0.16</v>
       </c>
       <c r="W5">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>100.980515943428</v>
+        <v>102.9421843387774</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1746,13 +1746,13 @@
         <v>0.04</v>
       </c>
       <c r="B6">
-        <v>0.08489810705434876</v>
+        <v>0.08484386329097696</v>
       </c>
       <c r="C6">
-        <v>3861.370348071377</v>
+        <v>3865.985613023181</v>
       </c>
       <c r="D6">
-        <v>3652.254348071377</v>
+        <v>3656.869613023181</v>
       </c>
       <c r="E6">
         <v>-1664.016</v>
@@ -1779,37 +1779,37 @@
         <v>680.4</v>
       </c>
       <c r="M6">
-        <v>8.983911317191504</v>
+        <v>8.812713717191503</v>
       </c>
       <c r="N6">
-        <v>671.4160886828084</v>
+        <v>671.5872862828085</v>
       </c>
       <c r="O6">
-        <v>107.4265741892494</v>
+        <v>107.4539658052494</v>
       </c>
       <c r="P6">
-        <v>563.9895144935591</v>
+        <v>564.1333204775591</v>
       </c>
       <c r="Q6">
-        <v>888.6895144935592</v>
+        <v>888.8333204775591</v>
       </c>
       <c r="R6">
         <v>0.04166666666666667</v>
       </c>
       <c r="S6">
-        <v>0.08586416237658809</v>
+        <v>0.08585665845640914</v>
       </c>
       <c r="T6">
         <v>0.5513949811783092</v>
       </c>
       <c r="U6">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V6">
         <v>0.16</v>
       </c>
       <c r="W6">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>75.735386957571</v>
+        <v>77.20663825408306</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1828,13 +1828,13 @@
         <v>0.05</v>
       </c>
       <c r="B7">
-        <v>0.08499529991054752</v>
+        <v>0.0849293077474388</v>
       </c>
       <c r="C7">
-        <v>3821.742827711448</v>
+        <v>3827.429313654907</v>
       </c>
       <c r="D7">
-        <v>3643.197827711448</v>
+        <v>3648.884313654907</v>
       </c>
       <c r="E7">
         <v>-1633.445</v>
@@ -1861,37 +1861,37 @@
         <v>680.4</v>
       </c>
       <c r="M7">
-        <v>11.22988914648938</v>
+        <v>11.01589214648938</v>
       </c>
       <c r="N7">
-        <v>669.1701108535106</v>
+        <v>669.3841078535106</v>
       </c>
       <c r="O7">
-        <v>107.0672177365617</v>
+        <v>107.1014572565617</v>
       </c>
       <c r="P7">
-        <v>562.1028931169488</v>
+        <v>562.2826505969489</v>
       </c>
       <c r="Q7">
-        <v>886.8028931169489</v>
+        <v>886.9826505969489</v>
       </c>
       <c r="R7">
         <v>0.05263157894736843</v>
       </c>
       <c r="S7">
-        <v>0.08622069573107083</v>
+        <v>0.08621312503306164</v>
       </c>
       <c r="T7">
         <v>0.5563018777817267</v>
       </c>
       <c r="U7">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V7">
         <v>0.16</v>
       </c>
       <c r="W7">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>60.58830956605681</v>
+        <v>61.76531060326644</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1910,13 +1910,13 @@
         <v>0.06</v>
       </c>
       <c r="B8">
-        <v>0.0850924927667463</v>
+        <v>0.08501475220390065</v>
       </c>
       <c r="C8">
-        <v>3782.160111283212</v>
+        <v>3788.907812393258</v>
       </c>
       <c r="D8">
-        <v>3634.186111283212</v>
+        <v>3640.933812393258</v>
       </c>
       <c r="E8">
         <v>-1602.874</v>
@@ -1943,37 +1943,37 @@
         <v>680.4</v>
       </c>
       <c r="M8">
-        <v>13.47586697578726</v>
+        <v>13.21907057578726</v>
       </c>
       <c r="N8">
-        <v>666.9241330242128</v>
+        <v>667.1809294242128</v>
       </c>
       <c r="O8">
-        <v>106.7078612838741</v>
+        <v>106.748948707874</v>
       </c>
       <c r="P8">
-        <v>560.2162717403387</v>
+        <v>560.4319807163387</v>
       </c>
       <c r="Q8">
-        <v>884.9162717403387</v>
+        <v>885.1319807163387</v>
       </c>
       <c r="R8">
         <v>0.06382978723404255</v>
       </c>
       <c r="S8">
-        <v>0.08658481490160638</v>
+        <v>0.08657717600496208</v>
       </c>
       <c r="T8">
         <v>0.561313176440536</v>
       </c>
       <c r="U8">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V8">
         <v>0.16</v>
       </c>
       <c r="W8">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>50.49025797171401</v>
+        <v>51.4710921693887</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1992,13 +1992,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9">
-        <v>0.08518968562294506</v>
+        <v>0.08510019666036249</v>
       </c>
       <c r="C9">
-        <v>3742.621867129637</v>
+        <v>3750.420882269497</v>
       </c>
       <c r="D9">
-        <v>3625.218867129637</v>
+        <v>3633.017882269497</v>
       </c>
       <c r="E9">
         <v>-1572.303</v>
@@ -2025,37 +2025,37 @@
         <v>680.4</v>
       </c>
       <c r="M9">
-        <v>15.72184480508513</v>
+        <v>15.42224900508513</v>
       </c>
       <c r="N9">
-        <v>664.6781551949149</v>
+        <v>664.9777509949148</v>
       </c>
       <c r="O9">
-        <v>106.3485048311864</v>
+        <v>106.3964401591864</v>
       </c>
       <c r="P9">
-        <v>558.3296503637285</v>
+        <v>558.5813108357285</v>
       </c>
       <c r="Q9">
-        <v>883.0296503637286</v>
+        <v>883.2813108357285</v>
       </c>
       <c r="R9">
         <v>0.07526881720430109</v>
       </c>
       <c r="S9">
-        <v>0.08695676459193841</v>
+        <v>0.08694905603002166</v>
       </c>
       <c r="T9">
         <v>0.5664322449629756</v>
       </c>
       <c r="U9">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V9">
         <v>0.16</v>
       </c>
       <c r="W9">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>43.27736397575486</v>
+        <v>44.11807900233316</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2074,13 +2074,13 @@
         <v>0.08</v>
       </c>
       <c r="B10">
-        <v>0.08528687847914383</v>
+        <v>0.08518564111682435</v>
       </c>
       <c r="C10">
-        <v>3703.127766859046</v>
+        <v>3711.968298284461</v>
       </c>
       <c r="D10">
-        <v>3616.295766859047</v>
+        <v>3625.136298284461</v>
       </c>
       <c r="E10">
         <v>-1541.732</v>
@@ -2107,37 +2107,37 @@
         <v>680.4</v>
       </c>
       <c r="M10">
-        <v>17.96782263438301</v>
+        <v>17.62542743438301</v>
       </c>
       <c r="N10">
-        <v>662.432177365617</v>
+        <v>662.7745725656169</v>
       </c>
       <c r="O10">
-        <v>105.9891483784987</v>
+        <v>106.0439316104987</v>
       </c>
       <c r="P10">
-        <v>556.4430289871183</v>
+        <v>556.7306409551182</v>
       </c>
       <c r="Q10">
-        <v>881.1430289871183</v>
+        <v>881.4306409551183</v>
       </c>
       <c r="R10">
         <v>0.08695652173913043</v>
       </c>
       <c r="S10">
-        <v>0.08733680014510373</v>
+        <v>0.08732902040345211</v>
       </c>
       <c r="T10">
         <v>0.5716625975837292</v>
       </c>
       <c r="U10">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V10">
         <v>0.16</v>
       </c>
       <c r="W10">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>37.8676934787855</v>
+        <v>38.60331912704152</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2156,13 +2156,13 @@
         <v>0.09</v>
       </c>
       <c r="B11">
-        <v>0.08538407133534259</v>
+        <v>0.08527108557328618</v>
       </c>
       <c r="C11">
-        <v>3663.677485305037</v>
+        <v>3673.549837387246</v>
       </c>
       <c r="D11">
-        <v>3607.416485305037</v>
+        <v>3617.288837387247</v>
       </c>
       <c r="E11">
         <v>-1511.161</v>
@@ -2189,37 +2189,37 @@
         <v>680.4</v>
       </c>
       <c r="M11">
-        <v>20.21380046368089</v>
+        <v>19.82860586368088</v>
       </c>
       <c r="N11">
-        <v>660.1861995363191</v>
+        <v>660.5713941363191</v>
       </c>
       <c r="O11">
-        <v>105.6297919258111</v>
+        <v>105.6914230618111</v>
       </c>
       <c r="P11">
-        <v>554.556407610508</v>
+        <v>554.879971074508</v>
       </c>
       <c r="Q11">
-        <v>879.2564076105081</v>
+        <v>879.5799710745081</v>
       </c>
       <c r="R11">
         <v>0.0989010989010989</v>
       </c>
       <c r="S11">
-        <v>0.08772518812800895</v>
+        <v>0.08771733564223266</v>
       </c>
       <c r="T11">
         <v>0.5770079030093344</v>
       </c>
       <c r="U11">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V11">
         <v>0.16</v>
       </c>
       <c r="W11">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>33.66017198114267</v>
+        <v>34.31406144625913</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2238,13 +2238,13 @@
         <v>0.1</v>
       </c>
       <c r="B12">
-        <v>0.08548126419154137</v>
+        <v>0.08535653002974804</v>
       </c>
       <c r="C12">
-        <v>3624.270700486969</v>
+        <v>3635.165278454153</v>
       </c>
       <c r="D12">
-        <v>3598.580700486969</v>
+        <v>3609.475278454153</v>
       </c>
       <c r="E12">
         <v>-1480.59</v>
@@ -2271,37 +2271,37 @@
         <v>680.4</v>
       </c>
       <c r="M12">
-        <v>22.45977829297876</v>
+        <v>22.03178429297876</v>
       </c>
       <c r="N12">
-        <v>657.9402217070212</v>
+        <v>658.3682157070212</v>
       </c>
       <c r="O12">
-        <v>105.2704354731234</v>
+        <v>105.3389145131234</v>
       </c>
       <c r="P12">
-        <v>552.6697862338979</v>
+        <v>553.0293011938978</v>
       </c>
       <c r="Q12">
-        <v>877.3697862338979</v>
+        <v>877.7293011938979</v>
       </c>
       <c r="R12">
         <v>0.1111111111111111</v>
       </c>
       <c r="S12">
-        <v>0.08812220695497874</v>
+        <v>0.08811428010854169</v>
       </c>
       <c r="T12">
         <v>0.5824719929999531</v>
       </c>
       <c r="U12">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V12">
         <v>0.16</v>
       </c>
       <c r="W12">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.29415478302841</v>
+        <v>30.88265530163322</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2320,13 +2320,13 @@
         <v>0.11</v>
       </c>
       <c r="B13">
-        <v>0.08557845704774013</v>
+        <v>0.08544197448620988</v>
       </c>
       <c r="C13">
-        <v>3584.907093571063</v>
+        <v>3596.814402267933</v>
       </c>
       <c r="D13">
-        <v>3589.788093571063</v>
+        <v>3601.695402267933</v>
       </c>
       <c r="E13">
         <v>-1450.019</v>
@@ -2353,37 +2353,37 @@
         <v>680.4</v>
       </c>
       <c r="M13">
-        <v>24.70575612227664</v>
+        <v>24.23496272227664</v>
       </c>
       <c r="N13">
-        <v>655.6942438777234</v>
+        <v>656.1650372777233</v>
       </c>
       <c r="O13">
-        <v>104.9110790204357</v>
+        <v>104.9864059644357</v>
       </c>
       <c r="P13">
-        <v>550.7831648572876</v>
+        <v>551.1786313132875</v>
       </c>
       <c r="Q13">
-        <v>875.4831648572876</v>
+        <v>875.8786313132875</v>
       </c>
       <c r="R13">
         <v>0.1235955056179775</v>
       </c>
       <c r="S13">
-        <v>0.0885281475533411</v>
+        <v>0.08852014467521721</v>
       </c>
       <c r="T13">
         <v>0.5880588715296868</v>
       </c>
       <c r="U13">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V13">
         <v>0.16</v>
       </c>
       <c r="W13">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>27.540140711844</v>
+        <v>28.07514118330292</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2402,13 +2402,13 @@
         <v>0.12</v>
       </c>
       <c r="B14">
-        <v>0.0856756499039389</v>
+        <v>0.0855274189426717</v>
       </c>
       <c r="C14">
-        <v>3545.586348832029</v>
+        <v>3558.49699149728</v>
       </c>
       <c r="D14">
-        <v>3581.038348832029</v>
+        <v>3593.94899149728</v>
       </c>
       <c r="E14">
         <v>-1419.448</v>
@@ -2435,37 +2435,37 @@
         <v>680.4</v>
       </c>
       <c r="M14">
-        <v>26.95173395157451</v>
+        <v>26.43814115157451</v>
       </c>
       <c r="N14">
-        <v>653.4482660484255</v>
+        <v>653.9618588484254</v>
       </c>
       <c r="O14">
-        <v>104.5517225677481</v>
+        <v>104.6338974157481</v>
       </c>
       <c r="P14">
-        <v>548.8965434806773</v>
+        <v>549.3279614326774</v>
       </c>
       <c r="Q14">
-        <v>873.5965434806774</v>
+        <v>874.0279614326774</v>
       </c>
       <c r="R14">
         <v>0.1363636363636364</v>
       </c>
       <c r="S14">
-        <v>0.08894331407439351</v>
+        <v>0.08893523343658989</v>
       </c>
       <c r="T14">
         <v>0.5937727245714599</v>
       </c>
       <c r="U14">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V14">
         <v>0.16</v>
       </c>
       <c r="W14">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.245128985857</v>
+        <v>25.73554608469435</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2484,13 +2484,13 @@
         <v>0.13</v>
       </c>
       <c r="B15">
-        <v>0.08577284276013766</v>
+        <v>0.08561286339913354</v>
       </c>
       <c r="C15">
-        <v>3506.308153615297</v>
+        <v>3520.21283067658</v>
       </c>
       <c r="D15">
-        <v>3572.331153615297</v>
+        <v>3586.23583067658</v>
       </c>
       <c r="E15">
         <v>-1388.877</v>
@@ -2517,37 +2517,37 @@
         <v>680.4</v>
       </c>
       <c r="M15">
-        <v>29.19771178087239</v>
+        <v>28.64131958087239</v>
       </c>
       <c r="N15">
-        <v>651.2022882191276</v>
+        <v>651.7586804191276</v>
       </c>
       <c r="O15">
-        <v>104.1923661150604</v>
+        <v>104.2813888670604</v>
       </c>
       <c r="P15">
-        <v>547.0099221040672</v>
+        <v>547.4772915520672</v>
       </c>
       <c r="Q15">
-        <v>871.7099221040672</v>
+        <v>872.1772915520672</v>
       </c>
       <c r="R15">
         <v>0.1494252873563219</v>
       </c>
       <c r="S15">
-        <v>0.08936802465340116</v>
+        <v>0.08935986446833896</v>
       </c>
       <c r="T15">
         <v>0.5996179305567222</v>
       </c>
       <c r="U15">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V15">
         <v>0.16</v>
       </c>
       <c r="W15">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.30319598694492</v>
+        <v>23.75588869356401</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2566,13 +2566,13 @@
         <v>0.14</v>
       </c>
       <c r="B16">
-        <v>0.08587003561633644</v>
+        <v>0.0856983078555954</v>
       </c>
       <c r="C16">
-        <v>3467.072198299755</v>
+        <v>3481.961706185956</v>
       </c>
       <c r="D16">
-        <v>3563.666198299755</v>
+        <v>3578.555706185956</v>
       </c>
       <c r="E16">
         <v>-1358.306</v>
@@ -2599,37 +2599,37 @@
         <v>680.4</v>
       </c>
       <c r="M16">
-        <v>31.44368961017027</v>
+        <v>30.84449801017027</v>
       </c>
       <c r="N16">
-        <v>648.9563103898297</v>
+        <v>649.5555019898297</v>
       </c>
       <c r="O16">
-        <v>103.8330096623728</v>
+        <v>103.9288803183728</v>
       </c>
       <c r="P16">
-        <v>545.1233007274569</v>
+        <v>545.626621671457</v>
       </c>
       <c r="Q16">
-        <v>869.823300727457</v>
+        <v>870.326621671457</v>
       </c>
       <c r="R16">
         <v>0.1627906976744186</v>
       </c>
       <c r="S16">
-        <v>0.08980261222261829</v>
+        <v>0.08979437064036128</v>
       </c>
       <c r="T16">
         <v>0.6055990715648975</v>
       </c>
       <c r="U16">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V16">
         <v>0.16</v>
       </c>
       <c r="W16">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.63868198787743</v>
+        <v>22.05903950116658</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2648,13 +2648,13 @@
         <v>0.15</v>
       </c>
       <c r="B17">
-        <v>0.08596722847253518</v>
+        <v>0.08578375231205725</v>
       </c>
       <c r="C17">
-        <v>3427.878176261067</v>
+        <v>3443.743406231537</v>
       </c>
       <c r="D17">
-        <v>3555.043176261067</v>
+        <v>3570.908406231537</v>
       </c>
       <c r="E17">
         <v>-1327.735</v>
@@ -2681,37 +2681,37 @@
         <v>680.4</v>
       </c>
       <c r="M17">
-        <v>33.68966743946814</v>
+        <v>33.04767643946814</v>
       </c>
       <c r="N17">
-        <v>646.7103325605318</v>
+        <v>647.3523235605319</v>
       </c>
       <c r="O17">
-        <v>103.4736532096851</v>
+        <v>103.5763717696851</v>
       </c>
       <c r="P17">
-        <v>543.2366793508468</v>
+        <v>543.7759517908468</v>
       </c>
       <c r="Q17">
-        <v>867.9366793508468</v>
+        <v>868.4759517908468</v>
       </c>
       <c r="R17">
         <v>0.1764705882352941</v>
       </c>
       <c r="S17">
-        <v>0.09024742538169933</v>
+        <v>0.0902391004870194</v>
       </c>
       <c r="T17">
         <v>0.6117209453026767</v>
       </c>
       <c r="U17">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V17">
         <v>0.16</v>
       </c>
       <c r="W17">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.1961031886856</v>
+        <v>20.58843686775548</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2730,13 +2730,13 @@
         <v>0.16</v>
       </c>
       <c r="B18">
-        <v>0.08606442132873393</v>
+        <v>0.08586919676851908</v>
       </c>
       <c r="C18">
-        <v>3388.725783835489</v>
+        <v>3405.557720825985</v>
       </c>
       <c r="D18">
-        <v>3546.461783835489</v>
+        <v>3563.293720825985</v>
       </c>
       <c r="E18">
         <v>-1297.164</v>
@@ -2763,37 +2763,37 @@
         <v>680.4</v>
       </c>
       <c r="M18">
-        <v>35.93564526876602</v>
+        <v>35.25085486876601</v>
       </c>
       <c r="N18">
-        <v>644.4643547312339</v>
+        <v>645.1491451312339</v>
       </c>
       <c r="O18">
-        <v>103.1142967569974</v>
+        <v>103.2238632209974</v>
       </c>
       <c r="P18">
-        <v>541.3500579742365</v>
+        <v>541.9252819102364</v>
       </c>
       <c r="Q18">
-        <v>866.0500579742366</v>
+        <v>866.6252819102365</v>
       </c>
       <c r="R18">
         <v>0.1904761904761905</v>
       </c>
       <c r="S18">
-        <v>0.09070282933028231</v>
+        <v>0.09069441913955033</v>
       </c>
       <c r="T18">
         <v>0.6179885779389745</v>
       </c>
       <c r="U18">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V18">
         <v>0.16</v>
       </c>
       <c r="W18">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.93384673939275</v>
+        <v>19.30165956352076</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2812,13 +2812,13 @@
         <v>0.17</v>
       </c>
       <c r="B19">
-        <v>0.08616161418493271</v>
+        <v>0.08595464122498092</v>
       </c>
       <c r="C19">
-        <v>3349.614720284228</v>
+        <v>3367.404441769275</v>
       </c>
       <c r="D19">
-        <v>3537.921720284228</v>
+        <v>3555.711441769275</v>
       </c>
       <c r="E19">
         <v>-1266.593</v>
@@ -2845,37 +2845,37 @@
         <v>680.4</v>
       </c>
       <c r="M19">
-        <v>38.18162309806389</v>
+        <v>37.45403329806389</v>
       </c>
       <c r="N19">
-        <v>642.218376901936</v>
+        <v>642.9459667019361</v>
       </c>
       <c r="O19">
-        <v>102.7549403043098</v>
+        <v>102.8713546723098</v>
       </c>
       <c r="P19">
-        <v>539.4634365976262</v>
+        <v>540.0746120296263</v>
       </c>
       <c r="Q19">
-        <v>864.1634365976263</v>
+        <v>864.7746120296264</v>
       </c>
       <c r="R19">
         <v>0.2048192771084338</v>
       </c>
       <c r="S19">
-        <v>0.09116920686798778</v>
+        <v>0.09116070932587719</v>
       </c>
       <c r="T19">
         <v>0.6244072378677135</v>
       </c>
       <c r="U19">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V19">
         <v>0.16</v>
       </c>
       <c r="W19">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.82009104884023</v>
+        <v>18.16626782449013</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2894,13 +2894,13 @@
         <v>0.18</v>
       </c>
       <c r="B20">
-        <v>0.08625880704113147</v>
+        <v>0.08604008568144278</v>
       </c>
       <c r="C20">
-        <v>3310.544687758319</v>
+        <v>3329.283362629724</v>
       </c>
       <c r="D20">
-        <v>3529.422687758319</v>
+        <v>3548.161362629724</v>
       </c>
       <c r="E20">
         <v>-1236.022</v>
@@ -2927,37 +2927,37 @@
         <v>680.4</v>
       </c>
       <c r="M20">
-        <v>40.42760092736177</v>
+        <v>39.65721172736177</v>
       </c>
       <c r="N20">
-        <v>639.9723990726382</v>
+        <v>640.7427882726382</v>
       </c>
       <c r="O20">
-        <v>102.3955838516221</v>
+        <v>102.5188461236221</v>
       </c>
       <c r="P20">
-        <v>537.5768152210161</v>
+        <v>538.2239421490161</v>
       </c>
       <c r="Q20">
-        <v>862.2768152210161</v>
+        <v>862.9239421490162</v>
       </c>
       <c r="R20">
         <v>0.2195121951219512</v>
       </c>
       <c r="S20">
-        <v>0.0916469594675885</v>
+        <v>0.09163837244357788</v>
       </c>
       <c r="T20">
         <v>0.630982450477641</v>
       </c>
       <c r="U20">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V20">
         <v>0.16</v>
       </c>
       <c r="W20">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.83008599057133</v>
+        <v>17.15703072312957</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2976,13 +2976,13 @@
         <v>0.19</v>
       </c>
       <c r="B21">
-        <v>0.08635599989733023</v>
+        <v>0.08612553013790461</v>
       </c>
       <c r="C21">
-        <v>3271.515391263983</v>
+        <v>3291.19427872526</v>
       </c>
       <c r="D21">
-        <v>3520.964391263982</v>
+        <v>3540.64327872526</v>
       </c>
       <c r="E21">
         <v>-1205.451</v>
@@ -3009,37 +3009,37 @@
         <v>680.4</v>
       </c>
       <c r="M21">
-        <v>42.67357875665964</v>
+        <v>41.86039015665964</v>
       </c>
       <c r="N21">
-        <v>637.7264212433404</v>
+        <v>638.5396098433404</v>
       </c>
       <c r="O21">
-        <v>102.0362273989345</v>
+        <v>102.1663375749345</v>
       </c>
       <c r="P21">
-        <v>535.6901938444059</v>
+        <v>536.3732722684059</v>
       </c>
       <c r="Q21">
-        <v>860.390193844406</v>
+        <v>861.073272268406</v>
       </c>
       <c r="R21">
         <v>0.2345679012345679</v>
       </c>
       <c r="S21">
-        <v>0.09213650842767318</v>
+        <v>0.09212782971233291</v>
       </c>
       <c r="T21">
         <v>0.6377200140162087</v>
       </c>
       <c r="U21">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V21">
         <v>0.16</v>
       </c>
       <c r="W21">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.94429199106758</v>
+        <v>16.25402910612275</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3058,13 +3058,13 @@
         <v>0.2</v>
       </c>
       <c r="B22">
-        <v>0.086453192753529</v>
+        <v>0.08621097459436644</v>
       </c>
       <c r="C22">
-        <v>3232.526538628499</v>
+        <v>3253.136987104912</v>
       </c>
       <c r="D22">
-        <v>3512.546538628499</v>
+        <v>3533.156987104912</v>
       </c>
       <c r="E22">
         <v>-1174.88</v>
@@ -3091,37 +3091,37 @@
         <v>680.4</v>
       </c>
       <c r="M22">
-        <v>44.91955658595752</v>
+        <v>44.06356858595752</v>
       </c>
       <c r="N22">
-        <v>635.4804434140425</v>
+        <v>636.3364314140424</v>
       </c>
       <c r="O22">
-        <v>101.6768709462468</v>
+        <v>101.8138290262468</v>
       </c>
       <c r="P22">
-        <v>533.8035724677957</v>
+        <v>534.5226023877956</v>
       </c>
       <c r="Q22">
-        <v>858.5035724677957</v>
+        <v>859.2226023877956</v>
       </c>
       <c r="R22">
         <v>0.25</v>
       </c>
       <c r="S22">
-        <v>0.09263829611176</v>
+        <v>0.09262952341280681</v>
       </c>
       <c r="T22">
         <v>0.6446260166432407</v>
       </c>
       <c r="U22">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V22">
         <v>0.16</v>
       </c>
       <c r="W22">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.1470773915142</v>
+        <v>15.44132765081661</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3140,13 +3140,13 @@
         <v>0.21</v>
       </c>
       <c r="B23">
-        <v>0.08655038560972778</v>
+        <v>0.08629641905082829</v>
       </c>
       <c r="C23">
-        <v>3193.577840466572</v>
+        <v>3215.111286530557</v>
       </c>
       <c r="D23">
-        <v>3504.168840466572</v>
+        <v>3525.702286530557</v>
       </c>
       <c r="E23">
         <v>-1144.309</v>
@@ -3173,37 +3173,37 @@
         <v>680.4</v>
       </c>
       <c r="M23">
-        <v>47.16553441525539</v>
+        <v>46.2667470152554</v>
       </c>
       <c r="N23">
-        <v>633.2344655847446</v>
+        <v>634.1332529847446</v>
       </c>
       <c r="O23">
-        <v>101.3175144935591</v>
+        <v>101.4613204775591</v>
       </c>
       <c r="P23">
-        <v>531.9169510911854</v>
+        <v>532.6719325071854</v>
       </c>
       <c r="Q23">
-        <v>856.6169510911855</v>
+        <v>857.3719325071854</v>
       </c>
       <c r="R23">
         <v>0.2658227848101266</v>
       </c>
       <c r="S23">
-        <v>0.09315278728151989</v>
+        <v>0.09314391821962181</v>
       </c>
       <c r="T23">
         <v>0.6517068547798178</v>
       </c>
       <c r="U23">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V23">
         <v>0.16</v>
       </c>
       <c r="W23">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.42578799191829</v>
+        <v>14.70602633411105</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3222,13 +3222,13 @@
         <v>0.22</v>
       </c>
       <c r="B24">
-        <v>0.08664757846592652</v>
+        <v>0.08638186350729014</v>
       </c>
       <c r="C24">
-        <v>3154.669010147164</v>
+        <v>3177.116977458887</v>
       </c>
       <c r="D24">
-        <v>3495.831010147163</v>
+        <v>3518.278977458886</v>
       </c>
       <c r="E24">
         <v>-1113.738</v>
@@ -3255,37 +3255,37 @@
         <v>680.4</v>
       </c>
       <c r="M24">
-        <v>49.41151224455327</v>
+        <v>48.46992544455328</v>
       </c>
       <c r="N24">
-        <v>630.9884877554467</v>
+        <v>631.9300745554467</v>
       </c>
       <c r="O24">
-        <v>100.9581580408715</v>
+        <v>101.1088119288715</v>
       </c>
       <c r="P24">
-        <v>530.0303297145753</v>
+        <v>530.8212626265753</v>
       </c>
       <c r="Q24">
-        <v>854.7303297145753</v>
+        <v>855.5212626265753</v>
       </c>
       <c r="R24">
         <v>0.282051282051282</v>
       </c>
       <c r="S24">
-        <v>0.09368047053255567</v>
+        <v>0.09367150263686799</v>
       </c>
       <c r="T24">
         <v>0.6589692528686147</v>
       </c>
       <c r="U24">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V24">
         <v>0.16</v>
       </c>
       <c r="W24">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.770070355922</v>
+        <v>14.03757059165146</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3304,13 +3304,13 @@
         <v>0.23</v>
       </c>
       <c r="B25">
-        <v>0.0867447713221253</v>
+        <v>0.08646730796375199</v>
       </c>
       <c r="C25">
-        <v>3115.799763760796</v>
+        <v>3139.153862023607</v>
       </c>
       <c r="D25">
-        <v>3487.532763760796</v>
+        <v>3510.886862023607</v>
       </c>
       <c r="E25">
         <v>-1083.167</v>
@@ -3337,37 +3337,37 @@
         <v>680.4</v>
       </c>
       <c r="M25">
-        <v>51.65749007385115</v>
+        <v>50.67310387385115</v>
       </c>
       <c r="N25">
-        <v>628.7425099261488</v>
+        <v>629.7268961261489</v>
       </c>
       <c r="O25">
-        <v>100.5988015881838</v>
+        <v>100.7563033801838</v>
       </c>
       <c r="P25">
-        <v>528.143708337965</v>
+        <v>528.9705927459651</v>
       </c>
       <c r="Q25">
-        <v>852.843708337965</v>
+        <v>853.6705927459651</v>
       </c>
       <c r="R25">
         <v>0.2987012987012987</v>
       </c>
       <c r="S25">
-        <v>0.09422185984205993</v>
+        <v>0.09421279054547121</v>
       </c>
       <c r="T25">
         <v>0.666420284674004</v>
       </c>
       <c r="U25">
-        <v>0.07346759442929168</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V25">
         <v>0.16</v>
       </c>
       <c r="W25">
-        <v>0.06171277932060501</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.17137164479496</v>
+        <v>13.4272414354927</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3386,13 +3386,13 @@
         <v>0.24</v>
       </c>
       <c r="B26">
-        <v>0.08706372417832406</v>
+        <v>0.08655275242021383</v>
       </c>
       <c r="C26">
-        <v>3058.271465110749</v>
+        <v>3101.221744017849</v>
       </c>
       <c r="D26">
-        <v>3460.575465110749</v>
+        <v>3503.525744017849</v>
       </c>
       <c r="E26">
         <v>-1052.596</v>
@@ -3419,45 +3419,45 @@
         <v>680.4</v>
       </c>
       <c r="M26">
-        <v>54.71054230314901</v>
+        <v>52.87628230314903</v>
       </c>
       <c r="N26">
-        <v>625.6894576968509</v>
+        <v>627.523717696851</v>
       </c>
       <c r="O26">
-        <v>100.1103132314961</v>
+        <v>100.4037948314962</v>
       </c>
       <c r="P26">
-        <v>525.5791444653548</v>
+        <v>527.1199228653549</v>
       </c>
       <c r="Q26">
-        <v>850.2791444653549</v>
+        <v>851.8199228653549</v>
       </c>
       <c r="R26">
         <v>0.3157894736842105</v>
       </c>
       <c r="S26">
-        <v>0.09477749623865639</v>
+        <v>0.09476832287272187</v>
       </c>
       <c r="T26">
         <v>0.6740673962637455</v>
       </c>
       <c r="U26">
-        <v>0.07456759442929167</v>
+        <v>0.07206759442929168</v>
       </c>
       <c r="V26">
         <v>0.16</v>
       </c>
       <c r="W26">
-        <v>0.062636779320605</v>
+        <v>0.06053677932060501</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>Aaa/AAA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>12.43636000224472</v>
+        <v>12.86777304234717</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3468,13 +3468,13 @@
         <v>0.25</v>
       </c>
       <c r="B27">
-        <v>0.08717015703452283</v>
+        <v>0.08695319687667567</v>
       </c>
       <c r="C27">
-        <v>3018.797454891673</v>
+        <v>3036.559408016236</v>
       </c>
       <c r="D27">
-        <v>3451.672454891673</v>
+        <v>3469.434408016236</v>
       </c>
       <c r="E27">
         <v>-1022.025</v>
@@ -3501,37 +3501,37 @@
         <v>680.4</v>
       </c>
       <c r="M27">
-        <v>56.99014823244689</v>
+        <v>56.22587323244689</v>
       </c>
       <c r="N27">
-        <v>623.4098517675531</v>
+        <v>624.174126767553</v>
       </c>
       <c r="O27">
-        <v>99.74557628280849</v>
+        <v>99.86786028280849</v>
       </c>
       <c r="P27">
-        <v>523.6642754847446</v>
+        <v>524.3062664847446</v>
       </c>
       <c r="Q27">
-        <v>848.3642754847447</v>
+        <v>849.0062664847446</v>
       </c>
       <c r="R27">
         <v>0.3333333333333333</v>
       </c>
       <c r="S27">
-        <v>0.09534794960582876</v>
+        <v>0.09533866939536589</v>
       </c>
       <c r="T27">
         <v>0.6819184308292134</v>
       </c>
       <c r="U27">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V27">
         <v>0.16</v>
       </c>
       <c r="W27">
-        <v>0.062636779320605</v>
+        <v>0.061796779320605</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.93890560215493</v>
+        <v>12.1011904463825</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3550,13 +3550,13 @@
         <v>0.26</v>
       </c>
       <c r="B28">
-        <v>0.08727658989072158</v>
+        <v>0.08705124133313751</v>
       </c>
       <c r="C28">
-        <v>2979.369136606718</v>
+        <v>2997.742381962938</v>
       </c>
       <c r="D28">
-        <v>3442.815136606718</v>
+        <v>3461.188381962938</v>
       </c>
       <c r="E28">
         <v>-991.454</v>
@@ -3583,37 +3583,37 @@
         <v>680.4</v>
       </c>
       <c r="M28">
-        <v>59.26975416174477</v>
+        <v>58.47490816174477</v>
       </c>
       <c r="N28">
-        <v>621.1302458382552</v>
+        <v>621.9250918382552</v>
       </c>
       <c r="O28">
-        <v>99.38083933412084</v>
+        <v>99.50801469412083</v>
       </c>
       <c r="P28">
-        <v>521.7494065041343</v>
+        <v>522.4170771441344</v>
       </c>
       <c r="Q28">
-        <v>846.4494065041343</v>
+        <v>847.1170771441344</v>
       </c>
       <c r="R28">
         <v>0.3513513513513514</v>
       </c>
       <c r="S28">
-        <v>0.09593382063157335</v>
+        <v>0.09592443068889217</v>
       </c>
       <c r="T28">
         <v>0.6899816555180723</v>
       </c>
       <c r="U28">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V28">
         <v>0.16</v>
       </c>
       <c r="W28">
-        <v>0.062636779320605</v>
+        <v>0.061796779320605</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.47971692514897</v>
+        <v>11.63576004459856</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3632,13 +3632,13 @@
         <v>0.27</v>
       </c>
       <c r="B29">
-        <v>0.08738302274692034</v>
+        <v>0.08714928578959935</v>
       </c>
       <c r="C29">
-        <v>2939.986159406708</v>
+        <v>2958.964460679017</v>
       </c>
       <c r="D29">
-        <v>3434.003159406708</v>
+        <v>3452.981460679017</v>
       </c>
       <c r="E29">
         <v>-960.8829999999999</v>
@@ -3665,37 +3665,37 @@
         <v>680.4</v>
       </c>
       <c r="M29">
-        <v>61.54936009104264</v>
+        <v>60.72394309104265</v>
       </c>
       <c r="N29">
-        <v>618.8506399089573</v>
+        <v>619.6760569089573</v>
       </c>
       <c r="O29">
-        <v>99.01610238543317</v>
+        <v>99.14816910543317</v>
       </c>
       <c r="P29">
-        <v>519.8345375235241</v>
+        <v>520.5278878035242</v>
       </c>
       <c r="Q29">
-        <v>844.5345375235241</v>
+        <v>845.2278878035243</v>
       </c>
       <c r="R29">
         <v>0.3698630136986302</v>
       </c>
       <c r="S29">
-        <v>0.09653574291829725</v>
+        <v>0.09652624023703561</v>
       </c>
       <c r="T29">
         <v>0.6982657904723795</v>
       </c>
       <c r="U29">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V29">
         <v>0.16</v>
       </c>
       <c r="W29">
-        <v>0.062636779320605</v>
+        <v>0.061796779320605</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.05454222421753</v>
+        <v>11.20480596887269</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3714,13 +3714,13 @@
         <v>0.28</v>
       </c>
       <c r="B30">
-        <v>0.0874894556031191</v>
+        <v>0.08724733024606118</v>
       </c>
       <c r="C30">
-        <v>2900.64817602533</v>
+        <v>2920.225366655223</v>
       </c>
       <c r="D30">
-        <v>3425.23617602533</v>
+        <v>3444.813366655223</v>
       </c>
       <c r="E30">
         <v>-930.3119999999999</v>
@@ -3747,37 +3747,37 @@
         <v>680.4</v>
       </c>
       <c r="M30">
-        <v>63.82896602034052</v>
+        <v>62.97297802034053</v>
       </c>
       <c r="N30">
-        <v>616.5710339796594</v>
+        <v>617.4270219796595</v>
       </c>
       <c r="O30">
-        <v>98.65136543674551</v>
+        <v>98.78832351674552</v>
       </c>
       <c r="P30">
-        <v>517.9196685429139</v>
+        <v>518.6386984629139</v>
       </c>
       <c r="Q30">
-        <v>842.6196685429139</v>
+        <v>843.338698462914</v>
       </c>
       <c r="R30">
         <v>0.388888888888889</v>
       </c>
       <c r="S30">
-        <v>0.09715438526854125</v>
+        <v>0.09714476671707192</v>
       </c>
       <c r="T30">
         <v>0.7067800402865284</v>
       </c>
       <c r="U30">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V30">
         <v>0.16</v>
       </c>
       <c r="W30">
-        <v>0.062636779320605</v>
+        <v>0.061796779320605</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.65973714478118</v>
+        <v>10.80463432712723</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3796,13 +3796,13 @@
         <v>0.29</v>
       </c>
       <c r="B31">
-        <v>0.08759588845931786</v>
+        <v>0.08734537470252303</v>
       </c>
       <c r="C31">
-        <v>2861.354842733515</v>
+        <v>2881.52482500192</v>
       </c>
       <c r="D31">
-        <v>3416.513842733516</v>
+        <v>3436.68382500192</v>
       </c>
       <c r="E31">
         <v>-899.741</v>
@@ -3829,37 +3829,37 @@
         <v>680.4</v>
       </c>
       <c r="M31">
-        <v>66.10857194963839</v>
+        <v>65.2220129496384</v>
       </c>
       <c r="N31">
-        <v>614.2914280503616</v>
+        <v>615.1779870503616</v>
       </c>
       <c r="O31">
-        <v>98.28662848805786</v>
+        <v>98.42847792805786</v>
       </c>
       <c r="P31">
-        <v>516.0047995623037</v>
+        <v>516.7495091223037</v>
       </c>
       <c r="Q31">
-        <v>840.7047995623037</v>
+        <v>841.4495091223038</v>
       </c>
       <c r="R31">
         <v>0.4084507042253521</v>
       </c>
       <c r="S31">
-        <v>0.09779045416386256</v>
+        <v>0.09778071647823602</v>
       </c>
       <c r="T31">
         <v>0.7155341281236112</v>
       </c>
       <c r="U31">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V31">
         <v>0.16</v>
       </c>
       <c r="W31">
-        <v>0.062636779320605</v>
+        <v>0.061796779320605</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.2921600018577</v>
+        <v>10.43206072964009</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3878,13 +3878,13 @@
         <v>0.3</v>
       </c>
       <c r="B32">
-        <v>0.08770232131551664</v>
+        <v>0.08744341915898488</v>
       </c>
       <c r="C32">
-        <v>2822.10581929451</v>
+        <v>2842.862563418256</v>
       </c>
       <c r="D32">
-        <v>3407.83581929451</v>
+        <v>3428.592563418256</v>
       </c>
       <c r="E32">
         <v>-869.17</v>
@@ -3911,37 +3911,37 @@
         <v>680.4</v>
       </c>
       <c r="M32">
-        <v>68.38817787893628</v>
+        <v>67.47104787893628</v>
       </c>
       <c r="N32">
-        <v>612.0118221210637</v>
+        <v>612.9289521210637</v>
       </c>
       <c r="O32">
-        <v>97.92189153937019</v>
+        <v>98.0686323393702</v>
       </c>
       <c r="P32">
-        <v>514.0899305816935</v>
+        <v>514.8603197816935</v>
       </c>
       <c r="Q32">
-        <v>838.7899305816935</v>
+        <v>839.5603197816936</v>
       </c>
       <c r="R32">
         <v>0.4285714285714286</v>
       </c>
       <c r="S32">
-        <v>0.09844469645619305</v>
+        <v>0.09843483623257625</v>
       </c>
       <c r="T32">
         <v>0.7245383327560392</v>
       </c>
       <c r="U32">
-        <v>0.07456759442929167</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V32">
         <v>0.16</v>
       </c>
       <c r="W32">
-        <v>0.062636779320605</v>
+        <v>0.061796779320605</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.949088001795772</v>
+        <v>10.08432537198542</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3960,13 +3960,13 @@
         <v>0.31</v>
       </c>
       <c r="B33">
-        <v>0.08838163417171541</v>
+        <v>0.08754146361544671</v>
       </c>
       <c r="C33">
-        <v>2737.168970522103</v>
+        <v>2804.238312161752</v>
       </c>
       <c r="D33">
-        <v>3353.469970522103</v>
+        <v>3420.539312161752</v>
       </c>
       <c r="E33">
         <v>-838.5989999999999</v>
@@ -3993,45 +3993,45 @@
         <v>680.4</v>
       </c>
       <c r="M33">
-        <v>72.75272600823416</v>
+        <v>69.72008280823415</v>
       </c>
       <c r="N33">
-        <v>607.6472739917658</v>
+        <v>610.6799171917659</v>
       </c>
       <c r="O33">
-        <v>97.22356383868254</v>
+        <v>97.70878675068253</v>
       </c>
       <c r="P33">
-        <v>510.4237101530833</v>
+        <v>512.9711304410833</v>
       </c>
       <c r="Q33">
-        <v>835.1237101530833</v>
+        <v>837.6711304410834</v>
       </c>
       <c r="R33">
         <v>0.4492753623188406</v>
       </c>
       <c r="S33">
-        <v>0.09911790229322878</v>
+        <v>0.0991079159797959</v>
       </c>
       <c r="T33">
         <v>0.7338035288270883</v>
       </c>
       <c r="U33">
-        <v>0.07676759442929168</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V33">
         <v>0.16</v>
       </c>
       <c r="W33">
-        <v>0.06448477932060501</v>
+        <v>0.061796779320605</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y33">
-        <v>9.352226883195994</v>
+        <v>9.759024553534276</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4042,13 +4042,13 @@
         <v>0.32</v>
       </c>
       <c r="B34">
-        <v>0.08850654702791415</v>
+        <v>0.08809646807190856</v>
       </c>
       <c r="C34">
-        <v>2696.789368765543</v>
+        <v>2728.783787643222</v>
       </c>
       <c r="D34">
-        <v>3343.661368765543</v>
+        <v>3375.655787643222</v>
       </c>
       <c r="E34">
         <v>-808.028</v>
@@ -4075,37 +4075,37 @@
         <v>680.4</v>
       </c>
       <c r="M34">
-        <v>75.09958813753202</v>
+        <v>73.63218013753202</v>
       </c>
       <c r="N34">
-        <v>605.300411862468</v>
+        <v>606.7678198624679</v>
       </c>
       <c r="O34">
-        <v>96.84806589799487</v>
+        <v>97.08285117799487</v>
       </c>
       <c r="P34">
-        <v>508.4523459644731</v>
+        <v>509.6849686844731</v>
       </c>
       <c r="Q34">
-        <v>833.1523459644732</v>
+        <v>834.3849686844731</v>
       </c>
       <c r="R34">
         <v>0.4705882352941177</v>
       </c>
       <c r="S34">
-        <v>0.099810908301942</v>
+        <v>0.09980079219016906</v>
       </c>
       <c r="T34">
         <v>0.743341230664933</v>
       </c>
       <c r="U34">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V34">
         <v>0.16</v>
       </c>
       <c r="W34">
-        <v>0.06448477932060501</v>
+        <v>0.06322477932060501</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.059969793096123</v>
+        <v>9.240524981456911</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4124,13 +4124,13 @@
         <v>0.33</v>
       </c>
       <c r="B35">
-        <v>0.08863145988411293</v>
+        <v>0.0882087925283704</v>
       </c>
       <c r="C35">
-        <v>2656.466978248757</v>
+        <v>2689.271983650851</v>
       </c>
       <c r="D35">
-        <v>3333.909978248757</v>
+        <v>3366.714983650851</v>
       </c>
       <c r="E35">
         <v>-777.457</v>
@@ -4157,37 +4157,37 @@
         <v>680.4</v>
       </c>
       <c r="M35">
-        <v>77.4464502668299</v>
+        <v>75.93318576682991</v>
       </c>
       <c r="N35">
-        <v>602.9535497331701</v>
+        <v>604.4668142331701</v>
       </c>
       <c r="O35">
-        <v>96.47256795730722</v>
+        <v>96.71469027730723</v>
       </c>
       <c r="P35">
-        <v>506.4809817758629</v>
+        <v>507.7521239558629</v>
       </c>
       <c r="Q35">
-        <v>831.180981775863</v>
+        <v>832.4521239558629</v>
       </c>
       <c r="R35">
         <v>0.4925373134328359</v>
       </c>
       <c r="S35">
-        <v>0.100524601057184</v>
+        <v>0.1005143512724937</v>
       </c>
       <c r="T35">
         <v>0.7531636400203252</v>
       </c>
       <c r="U35">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V35">
         <v>0.16</v>
       </c>
       <c r="W35">
-        <v>0.06448477932060501</v>
+        <v>0.06322477932060501</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.785425253911392</v>
+        <v>8.960509072927913</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4206,13 +4206,13 @@
         <v>0.34</v>
       </c>
       <c r="B36">
-        <v>0.08875637274031169</v>
+        <v>0.08832111698483225</v>
       </c>
       <c r="C36">
-        <v>2616.201299877978</v>
+        <v>2649.807415997502</v>
       </c>
       <c r="D36">
-        <v>3324.215299877978</v>
+        <v>3357.821415997502</v>
       </c>
       <c r="E36">
         <v>-746.886</v>
@@ -4239,37 +4239,37 @@
         <v>680.4</v>
       </c>
       <c r="M36">
-        <v>79.79331239612777</v>
+        <v>78.23419139612778</v>
       </c>
       <c r="N36">
-        <v>600.6066876038722</v>
+        <v>602.1658086038722</v>
       </c>
       <c r="O36">
-        <v>96.09707001661955</v>
+        <v>96.34652937661954</v>
       </c>
       <c r="P36">
-        <v>504.5096175872526</v>
+        <v>505.8192792272527</v>
       </c>
       <c r="Q36">
-        <v>829.2096175872526</v>
+        <v>830.5192792272527</v>
       </c>
       <c r="R36">
         <v>0.5151515151515152</v>
       </c>
       <c r="S36">
-        <v>0.1012599208656151</v>
+        <v>0.1012495333573129</v>
       </c>
       <c r="T36">
         <v>0.7632836981440627</v>
       </c>
       <c r="U36">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V36">
         <v>0.16</v>
       </c>
       <c r="W36">
-        <v>0.06448477932060501</v>
+        <v>0.06322477932060501</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.527030393502232</v>
+        <v>8.696964688430032</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4288,13 +4288,13 @@
         <v>0.35</v>
       </c>
       <c r="B37">
-        <v>0.08888128559651046</v>
+        <v>0.08843344144129409</v>
       </c>
       <c r="C37">
-        <v>2575.991840347861</v>
+        <v>2610.389711328653</v>
       </c>
       <c r="D37">
-        <v>3314.576840347861</v>
+        <v>3348.974711328653</v>
       </c>
       <c r="E37">
         <v>-716.3149999999998</v>
@@ -4321,37 +4321,37 @@
         <v>680.4</v>
       </c>
       <c r="M37">
-        <v>82.14017452542566</v>
+        <v>80.53519702542566</v>
       </c>
       <c r="N37">
-        <v>598.2598254745743</v>
+        <v>599.8648029745743</v>
       </c>
       <c r="O37">
-        <v>95.72157207593189</v>
+        <v>95.9783684759319</v>
       </c>
       <c r="P37">
-        <v>502.5382533986424</v>
+        <v>503.8864344986424</v>
       </c>
       <c r="Q37">
-        <v>827.2382533986424</v>
+        <v>828.5864344986425</v>
       </c>
       <c r="R37">
         <v>0.5384615384615385</v>
       </c>
       <c r="S37">
-        <v>0.1020178658989211</v>
+        <v>0.1020073364293574</v>
       </c>
       <c r="T37">
         <v>0.7737151426716075</v>
       </c>
       <c r="U37">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V37">
         <v>0.16</v>
       </c>
       <c r="W37">
-        <v>0.06448477932060501</v>
+        <v>0.06322477932060501</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.283400953687881</v>
+        <v>8.448479983046317</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4370,13 +4370,13 @@
         <v>0.36</v>
       </c>
       <c r="B38">
-        <v>0.08900619845270923</v>
+        <v>0.08854576589775592</v>
       </c>
       <c r="C38">
-        <v>2535.838112057814</v>
+        <v>2571.018500214078</v>
       </c>
       <c r="D38">
-        <v>3304.994112057814</v>
+        <v>3340.174500214078</v>
       </c>
       <c r="E38">
         <v>-685.7439999999999</v>
@@ -4403,37 +4403,37 @@
         <v>680.4</v>
       </c>
       <c r="M38">
-        <v>84.48703665472354</v>
+        <v>82.83620265472354</v>
       </c>
       <c r="N38">
-        <v>595.9129633452765</v>
+        <v>597.5637973452765</v>
       </c>
       <c r="O38">
-        <v>95.34607413524424</v>
+        <v>95.61020757524425</v>
       </c>
       <c r="P38">
-        <v>500.5668892100322</v>
+        <v>501.9535897700322</v>
       </c>
       <c r="Q38">
-        <v>825.2668892100323</v>
+        <v>826.6535897700323</v>
       </c>
       <c r="R38">
         <v>0.5625</v>
       </c>
       <c r="S38">
-        <v>0.1027994967145179</v>
+        <v>0.1027888208474033</v>
       </c>
       <c r="T38">
         <v>0.784472569840638</v>
       </c>
       <c r="U38">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V38">
         <v>0.16</v>
       </c>
       <c r="W38">
-        <v>0.06448477932060501</v>
+        <v>0.06322477932060501</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.053306482752108</v>
+        <v>8.213799983517253</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4452,13 +4452,13 @@
         <v>0.37</v>
       </c>
       <c r="B39">
-        <v>0.089131111308908</v>
+        <v>0.08865809035421779</v>
       </c>
       <c r="C39">
-        <v>2495.739633029775</v>
+        <v>2531.693417096434</v>
       </c>
       <c r="D39">
-        <v>3295.466633029775</v>
+        <v>3331.420417096434</v>
       </c>
       <c r="E39">
         <v>-655.173</v>
@@ -4485,37 +4485,37 @@
         <v>680.4</v>
       </c>
       <c r="M39">
-        <v>86.8338987840214</v>
+        <v>85.13720828402141</v>
       </c>
       <c r="N39">
-        <v>593.5661012159786</v>
+        <v>595.2627917159786</v>
       </c>
       <c r="O39">
-        <v>94.97057619455659</v>
+        <v>95.24204667455658</v>
       </c>
       <c r="P39">
-        <v>498.595525021422</v>
+        <v>500.0207450414219</v>
       </c>
       <c r="Q39">
-        <v>823.295525021422</v>
+        <v>824.720745041422</v>
       </c>
       <c r="R39">
         <v>0.5873015873015873</v>
       </c>
       <c r="S39">
-        <v>0.1036059412068002</v>
+        <v>0.1035951142945935</v>
       </c>
       <c r="T39">
         <v>0.7955715026340823</v>
       </c>
       <c r="U39">
-        <v>0.07676759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V39">
         <v>0.16</v>
       </c>
       <c r="W39">
-        <v>0.06448477932060501</v>
+        <v>0.06322477932060501</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.835649550785836</v>
+        <v>7.991805389368137</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4534,13 +4534,13 @@
         <v>0.38</v>
       </c>
       <c r="B40">
-        <v>0.08973482416510675</v>
+        <v>0.08877041481067961</v>
       </c>
       <c r="C40">
-        <v>2419.885293188525</v>
+        <v>2492.414100240643</v>
       </c>
       <c r="D40">
-        <v>3250.183293188525</v>
+        <v>3322.712100240643</v>
       </c>
       <c r="E40">
         <v>-624.6020000000001</v>
@@ -4567,45 +4567,45 @@
         <v>680.4</v>
       </c>
       <c r="M40">
-        <v>90.92330791331928</v>
+        <v>87.43821391331927</v>
       </c>
       <c r="N40">
-        <v>589.4766920866807</v>
+        <v>592.9617860866807</v>
       </c>
       <c r="O40">
-        <v>94.31627073386892</v>
+        <v>94.87388577386892</v>
       </c>
       <c r="P40">
-        <v>495.1604213528118</v>
+        <v>498.0879003128118</v>
       </c>
       <c r="Q40">
-        <v>819.8604213528118</v>
+        <v>822.7879003128119</v>
       </c>
       <c r="R40">
         <v>0.6129032258064516</v>
       </c>
       <c r="S40">
-        <v>0.1044384000375433</v>
+        <v>0.1044274172078221</v>
       </c>
       <c r="T40">
         <v>0.8070284655176375</v>
       </c>
       <c r="U40">
-        <v>0.07826759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V40">
         <v>0.16</v>
       </c>
       <c r="W40">
-        <v>0.065744779320605</v>
+        <v>0.06322477932060501</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>7.483229719805748</v>
+        <v>7.781494721226872</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4616,13 +4616,13 @@
         <v>0.39</v>
       </c>
       <c r="B41">
-        <v>0.08987233702130551</v>
+        <v>0.08888273926714146</v>
       </c>
       <c r="C41">
-        <v>2379.173192942359</v>
+        <v>2453.18019168405</v>
       </c>
       <c r="D41">
-        <v>3240.04219294236</v>
+        <v>3314.049191684051</v>
       </c>
       <c r="E41">
         <v>-594.0309999999999</v>
@@ -4649,45 +4649,45 @@
         <v>680.4</v>
       </c>
       <c r="M41">
-        <v>93.31602654261717</v>
+        <v>89.73921954261716</v>
       </c>
       <c r="N41">
-        <v>587.0839734573829</v>
+        <v>590.6607804573828</v>
       </c>
       <c r="O41">
-        <v>93.93343575318126</v>
+        <v>94.50572487318125</v>
       </c>
       <c r="P41">
-        <v>493.1505377042016</v>
+        <v>496.1550555842015</v>
       </c>
       <c r="Q41">
-        <v>817.8505377042017</v>
+        <v>820.8550555842016</v>
       </c>
       <c r="R41">
         <v>0.639344262295082</v>
       </c>
       <c r="S41">
-        <v>0.1052981526004419</v>
+        <v>0.1052870087411566</v>
       </c>
       <c r="T41">
         <v>0.8188610665285225</v>
       </c>
       <c r="U41">
-        <v>0.07826759442929168</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V41">
         <v>0.16</v>
       </c>
       <c r="W41">
-        <v>0.065744779320605</v>
+        <v>0.06322477932060501</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.291352034682523</v>
+        <v>7.581969215554387</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4698,13 +4698,13 @@
         <v>0.4</v>
       </c>
       <c r="B42">
-        <v>0.09000984987750428</v>
+        <v>0.0892638637236033</v>
       </c>
       <c r="C42">
-        <v>2338.524179617489</v>
+        <v>2393.549069351151</v>
       </c>
       <c r="D42">
-        <v>3229.964179617489</v>
+        <v>3284.989069351151</v>
       </c>
       <c r="E42">
         <v>-563.46</v>
@@ -4731,37 +4731,37 @@
         <v>680.4</v>
       </c>
       <c r="M42">
-        <v>95.70874517191503</v>
+        <v>93.01849717191503</v>
       </c>
       <c r="N42">
-        <v>584.691254828085</v>
+        <v>587.381502828085</v>
       </c>
       <c r="O42">
-        <v>93.5506007724936</v>
+        <v>93.9810404524936</v>
       </c>
       <c r="P42">
-        <v>491.1406540555914</v>
+        <v>493.4004623755914</v>
       </c>
       <c r="Q42">
-        <v>815.8406540555915</v>
+        <v>818.1004623755914</v>
       </c>
       <c r="R42">
         <v>0.6666666666666667</v>
       </c>
       <c r="S42">
-        <v>0.1061865635821038</v>
+        <v>0.1061752533256022</v>
       </c>
       <c r="T42">
         <v>0.8310880875731038</v>
       </c>
       <c r="U42">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V42">
         <v>0.16</v>
       </c>
       <c r="W42">
-        <v>0.065744779320605</v>
+        <v>0.063896779320605</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.109068233815461</v>
+        <v>7.314674185097805</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4780,13 +4780,13 @@
         <v>0.41</v>
       </c>
       <c r="B43">
-        <v>0.09014736273370304</v>
+        <v>0.08938290818006514</v>
       </c>
       <c r="C43">
-        <v>2297.937666351773</v>
+        <v>2354.005291843319</v>
       </c>
       <c r="D43">
-        <v>3219.948666351773</v>
+        <v>3276.016291843319</v>
       </c>
       <c r="E43">
         <v>-532.8889999999999</v>
@@ -4813,37 +4813,37 @@
         <v>680.4</v>
       </c>
       <c r="M43">
-        <v>98.10146380121292</v>
+        <v>95.34395960121292</v>
       </c>
       <c r="N43">
-        <v>582.298536198787</v>
+        <v>585.0560403987871</v>
       </c>
       <c r="O43">
-        <v>93.16776579180592</v>
+        <v>93.60896646380594</v>
       </c>
       <c r="P43">
-        <v>489.1307704069811</v>
+        <v>491.4470739349812</v>
       </c>
       <c r="Q43">
-        <v>813.8307704069812</v>
+        <v>816.1470739349812</v>
       </c>
       <c r="R43">
         <v>0.6949152542372882</v>
       </c>
       <c r="S43">
-        <v>0.1071050901902627</v>
+        <v>0.1070936078959612</v>
       </c>
       <c r="T43">
         <v>0.8437295839073318</v>
       </c>
       <c r="U43">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V43">
         <v>0.16</v>
       </c>
       <c r="W43">
-        <v>0.065744779320605</v>
+        <v>0.063896779320605</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.935676325673619</v>
+        <v>7.136267497656394</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4862,13 +4862,13 @@
         <v>0.42</v>
       </c>
       <c r="B44">
-        <v>0.09028487558990181</v>
+        <v>0.08950195263652699</v>
       </c>
       <c r="C44">
-        <v>2257.413073539569</v>
+        <v>2314.51039816593</v>
       </c>
       <c r="D44">
-        <v>3209.995073539569</v>
+        <v>3267.09239816593</v>
       </c>
       <c r="E44">
         <v>-502.318</v>
@@ -4895,37 +4895,37 @@
         <v>680.4</v>
       </c>
       <c r="M44">
-        <v>100.4941824305108</v>
+        <v>97.66942203051077</v>
       </c>
       <c r="N44">
-        <v>579.9058175694892</v>
+        <v>582.7305779694892</v>
       </c>
       <c r="O44">
-        <v>92.78493081111827</v>
+        <v>93.23689247511828</v>
       </c>
       <c r="P44">
-        <v>487.1208867583709</v>
+        <v>489.4936854943709</v>
       </c>
       <c r="Q44">
-        <v>811.820886758371</v>
+        <v>814.193685494371</v>
       </c>
       <c r="R44">
         <v>0.7241379310344827</v>
       </c>
       <c r="S44">
-        <v>0.1080552901297374</v>
+        <v>0.1080436298652981</v>
       </c>
       <c r="T44">
         <v>0.8568069939082573</v>
       </c>
       <c r="U44">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V44">
         <v>0.16</v>
       </c>
       <c r="W44">
-        <v>0.065744779320605</v>
+        <v>0.063896779320605</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.770541175062343</v>
+        <v>6.966356366759814</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4944,13 +4944,13 @@
         <v>0.43</v>
       </c>
       <c r="B45">
-        <v>0.09042238844610057</v>
+        <v>0.08962099709298883</v>
       </c>
       <c r="C45">
-        <v>2216.949828719919</v>
+        <v>2275.063989924421</v>
       </c>
       <c r="D45">
-        <v>3200.102828719919</v>
+        <v>3258.216989924421</v>
       </c>
       <c r="E45">
         <v>-471.7470000000001</v>
@@ -4977,37 +4977,37 @@
         <v>680.4</v>
       </c>
       <c r="M45">
-        <v>102.8869010598087</v>
+        <v>99.99488445980865</v>
       </c>
       <c r="N45">
-        <v>577.5130989401913</v>
+        <v>580.4051155401913</v>
       </c>
       <c r="O45">
-        <v>92.40209583043061</v>
+        <v>92.86481848643062</v>
       </c>
       <c r="P45">
-        <v>485.1110031097607</v>
+        <v>487.5402970537607</v>
       </c>
       <c r="Q45">
-        <v>809.8110031097608</v>
+        <v>812.2402970537607</v>
       </c>
       <c r="R45">
         <v>0.7543859649122806</v>
       </c>
       <c r="S45">
-        <v>0.1090388304179656</v>
+        <v>0.1090269859388222</v>
       </c>
       <c r="T45">
         <v>0.8703432604004433</v>
       </c>
       <c r="U45">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V45">
         <v>0.16</v>
       </c>
       <c r="W45">
-        <v>0.065744779320605</v>
+        <v>0.063896779320605</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.613086729130661</v>
+        <v>6.804348079160749</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5026,13 +5026,13 @@
         <v>0.44</v>
       </c>
       <c r="B46">
-        <v>0.09055990130229934</v>
+        <v>0.08974004154945067</v>
       </c>
       <c r="C46">
-        <v>2176.547366466796</v>
+        <v>2235.665673041623</v>
       </c>
       <c r="D46">
-        <v>3190.271366466796</v>
+        <v>3249.389673041623</v>
       </c>
       <c r="E46">
         <v>-441.1759999999999</v>
@@ -5059,37 +5059,37 @@
         <v>680.4</v>
       </c>
       <c r="M46">
-        <v>105.2796196891065</v>
+        <v>102.3203468891065</v>
       </c>
       <c r="N46">
-        <v>575.1203803108934</v>
+        <v>578.0796531108934</v>
       </c>
       <c r="O46">
-        <v>92.01926084974295</v>
+        <v>92.49274449774295</v>
       </c>
       <c r="P46">
-        <v>483.1011194611505</v>
+        <v>485.5869086131505</v>
       </c>
       <c r="Q46">
-        <v>807.8011194611505</v>
+        <v>810.2869086131506</v>
       </c>
       <c r="R46">
         <v>0.7857142857142857</v>
       </c>
       <c r="S46">
-        <v>0.1100574971450592</v>
+        <v>0.1100454618721151</v>
       </c>
       <c r="T46">
         <v>0.884362964981636</v>
       </c>
       <c r="U46">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V46">
         <v>0.16</v>
       </c>
       <c r="W46">
-        <v>0.065744779320605</v>
+        <v>0.063896779320605</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.4627893034686</v>
+        <v>6.649703804634368</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5108,13 +5108,13 @@
         <v>0.45</v>
       </c>
       <c r="B47">
-        <v>0.09069741415849811</v>
+        <v>0.08985908600591251</v>
       </c>
       <c r="C47">
-        <v>2136.205128281379</v>
+        <v>2196.315057699443</v>
       </c>
       <c r="D47">
-        <v>3180.500128281379</v>
+        <v>3240.610057699443</v>
       </c>
       <c r="E47">
         <v>-410.605</v>
@@ -5141,37 +5141,37 @@
         <v>680.4</v>
       </c>
       <c r="M47">
-        <v>107.6723383184044</v>
+        <v>104.6458093184044</v>
       </c>
       <c r="N47">
-        <v>572.7276616815956</v>
+        <v>575.7541906815956</v>
       </c>
       <c r="O47">
-        <v>91.63642586905529</v>
+        <v>92.12067050905529</v>
       </c>
       <c r="P47">
-        <v>481.0912358125403</v>
+        <v>483.6335201725403</v>
       </c>
       <c r="Q47">
-        <v>805.7912358125403</v>
+        <v>808.3335201725404</v>
       </c>
       <c r="R47">
         <v>0.8181818181818181</v>
       </c>
       <c r="S47">
-        <v>0.1111132062985924</v>
+        <v>0.1111009732938914</v>
       </c>
       <c r="T47">
         <v>0.8988924770021448</v>
       </c>
       <c r="U47">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V47">
         <v>0.16</v>
       </c>
       <c r="W47">
-        <v>0.065744779320605</v>
+        <v>0.063896779320605</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.319171763391521</v>
+        <v>6.501932608975826</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5190,13 +5190,13 @@
         <v>0.46</v>
       </c>
       <c r="B48">
-        <v>0.09083492701469686</v>
+        <v>0.08997813046237436</v>
       </c>
       <c r="C48">
-        <v>2095.922562486285</v>
+        <v>2157.011758281472</v>
       </c>
       <c r="D48">
-        <v>3170.788562486285</v>
+        <v>3231.877758281472</v>
       </c>
       <c r="E48">
         <v>-380.0339999999999</v>
@@ -5223,37 +5223,37 @@
         <v>680.4</v>
       </c>
       <c r="M48">
-        <v>110.0650569477023</v>
+        <v>106.9712717477023</v>
       </c>
       <c r="N48">
-        <v>570.3349430522977</v>
+        <v>573.4287282522977</v>
       </c>
       <c r="O48">
-        <v>91.25359088836764</v>
+        <v>91.74859652036763</v>
       </c>
       <c r="P48">
-        <v>479.0813521639301</v>
+        <v>481.68013173193</v>
       </c>
       <c r="Q48">
-        <v>803.7813521639301</v>
+        <v>806.3801317319301</v>
       </c>
       <c r="R48">
         <v>0.8518518518518519</v>
       </c>
       <c r="S48">
-        <v>0.1122080157911455</v>
+        <v>0.112195577731289</v>
       </c>
       <c r="T48">
         <v>0.9139601190974873</v>
       </c>
       <c r="U48">
-        <v>0.07826759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V48">
         <v>0.16</v>
       </c>
       <c r="W48">
-        <v>0.065744779320605</v>
+        <v>0.063896779320605</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.181798464187357</v>
+        <v>6.360586247911134</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5272,13 +5272,13 @@
         <v>0.47</v>
       </c>
       <c r="B49">
-        <v>0.09152515987089563</v>
+        <v>0.0900971749188362</v>
       </c>
       <c r="C49">
-        <v>2017.487706961959</v>
+        <v>2117.755393316535</v>
       </c>
       <c r="D49">
-        <v>3122.924706961959</v>
+        <v>3223.192393316535</v>
       </c>
       <c r="E49">
         <v>-349.463</v>
@@ -5305,45 +5305,45 @@
         <v>680.4</v>
       </c>
       <c r="M49">
-        <v>114.4693473770002</v>
+        <v>109.2967341770002</v>
       </c>
       <c r="N49">
-        <v>565.9306526229998</v>
+        <v>571.1032658229998</v>
       </c>
       <c r="O49">
-        <v>90.54890441967997</v>
+        <v>91.37652253167997</v>
       </c>
       <c r="P49">
-        <v>475.3817482033198</v>
+        <v>479.7267432913198</v>
       </c>
       <c r="Q49">
-        <v>800.0817482033199</v>
+        <v>804.4267432913199</v>
       </c>
       <c r="R49">
         <v>0.8867924528301887</v>
       </c>
       <c r="S49">
-        <v>0.1133441388494552</v>
+        <v>0.1133314879965129</v>
       </c>
       <c r="T49">
         <v>0.9295963514605786</v>
       </c>
       <c r="U49">
-        <v>0.07966759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V49">
         <v>0.16</v>
       </c>
       <c r="W49">
-        <v>0.06692077932060501</v>
+        <v>0.063896779320605</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y49">
-        <v>5.94394932434733</v>
+        <v>6.225254625615152</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5354,13 +5354,13 @@
         <v>0.48</v>
       </c>
       <c r="B50">
-        <v>0.09167443272709441</v>
+        <v>0.09021621937529806</v>
       </c>
       <c r="C50">
-        <v>1976.75488341473</v>
+        <v>2078.545585423135</v>
       </c>
       <c r="D50">
-        <v>3112.762883414729</v>
+        <v>3214.553585423135</v>
       </c>
       <c r="E50">
         <v>-318.8920000000001</v>
@@ -5387,45 +5387,45 @@
         <v>680.4</v>
       </c>
       <c r="M50">
-        <v>116.904865406298</v>
+        <v>111.622196606298</v>
       </c>
       <c r="N50">
-        <v>563.4951345937019</v>
+        <v>568.7778033937019</v>
       </c>
       <c r="O50">
-        <v>90.1592215349923</v>
+        <v>91.00444854299231</v>
       </c>
       <c r="P50">
-        <v>473.3359130587096</v>
+        <v>477.7733548507096</v>
       </c>
       <c r="Q50">
-        <v>798.0359130587096</v>
+        <v>802.4733548507097</v>
       </c>
       <c r="R50">
         <v>0.923076923076923</v>
       </c>
       <c r="S50">
-        <v>0.1145239589484692</v>
+        <v>0.1145110871180916</v>
       </c>
       <c r="T50">
         <v>0.9458339773760964</v>
       </c>
       <c r="U50">
-        <v>0.07966759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V50">
         <v>0.16</v>
       </c>
       <c r="W50">
-        <v>0.06692077932060501</v>
+        <v>0.063896779320605</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y50">
-        <v>5.82011704675676</v>
+        <v>6.095561820914837</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5436,13 +5436,13 @@
         <v>0.49</v>
       </c>
       <c r="B51">
-        <v>0.09182370558329317</v>
+        <v>0.09074686383175989</v>
       </c>
       <c r="C51">
-        <v>1936.087977394388</v>
+        <v>2010.023438342235</v>
       </c>
       <c r="D51">
-        <v>3102.666977394388</v>
+        <v>3176.602438342235</v>
       </c>
       <c r="E51">
         <v>-288.3209999999999</v>
@@ -5469,37 +5469,37 @@
         <v>680.4</v>
       </c>
       <c r="M51">
-        <v>119.3403834355959</v>
+        <v>115.4456380355959</v>
       </c>
       <c r="N51">
-        <v>561.059616564404</v>
+        <v>564.954361964404</v>
       </c>
       <c r="O51">
-        <v>89.76953865030464</v>
+        <v>90.39269791430465</v>
       </c>
       <c r="P51">
-        <v>471.2900779140994</v>
+        <v>474.5616640500994</v>
       </c>
       <c r="Q51">
-        <v>795.9900779140994</v>
+        <v>799.2616640500994</v>
       </c>
       <c r="R51">
         <v>0.9607843137254901</v>
       </c>
       <c r="S51">
-        <v>0.1157500465023465</v>
+        <v>0.1157369450287518</v>
       </c>
       <c r="T51">
         <v>0.96270837293536</v>
       </c>
       <c r="U51">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V51">
         <v>0.16</v>
       </c>
       <c r="W51">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.701339147843357</v>
+        <v>5.893683049247897</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5518,13 +5518,13 @@
         <v>0.5</v>
       </c>
       <c r="B52">
-        <v>0.09197297843949193</v>
+        <v>0.09087430828822173</v>
       </c>
       <c r="C52">
-        <v>1895.486349585611</v>
+        <v>1970.470816959137</v>
       </c>
       <c r="D52">
-        <v>3092.636349585611</v>
+        <v>3167.620816959136</v>
       </c>
       <c r="E52">
         <v>-257.75</v>
@@ -5551,37 +5551,37 @@
         <v>680.4</v>
       </c>
       <c r="M52">
-        <v>121.7759014648938</v>
+        <v>117.8016714648938</v>
       </c>
       <c r="N52">
-        <v>558.6240985351062</v>
+        <v>562.5983285351062</v>
       </c>
       <c r="O52">
-        <v>89.37985576561699</v>
+        <v>90.015732565617</v>
       </c>
       <c r="P52">
-        <v>469.2442427694892</v>
+        <v>472.5825959694893</v>
       </c>
       <c r="Q52">
-        <v>793.9442427694893</v>
+        <v>797.2825959694893</v>
       </c>
       <c r="R52">
         <v>1</v>
       </c>
       <c r="S52">
-        <v>0.1170251775583789</v>
+        <v>0.1170118372558384</v>
       </c>
       <c r="T52">
         <v>0.9802577443169942</v>
       </c>
       <c r="U52">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V52">
         <v>0.16</v>
       </c>
       <c r="W52">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.587312364886491</v>
+        <v>5.77580938826294</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5600,13 +5600,13 @@
         <v>0.51</v>
       </c>
       <c r="B53">
-        <v>0.09212225129569068</v>
+        <v>0.09100175274468358</v>
       </c>
       <c r="C53">
-        <v>1854.94936891382</v>
+        <v>1930.968842189754</v>
       </c>
       <c r="D53">
-        <v>3082.670368913819</v>
+        <v>3158.689842189754</v>
       </c>
       <c r="E53">
         <v>-227.1790000000001</v>
@@ -5633,37 +5633,37 @@
         <v>680.4</v>
       </c>
       <c r="M53">
-        <v>124.2114194941917</v>
+        <v>120.1577048941917</v>
       </c>
       <c r="N53">
-        <v>556.1885805058083</v>
+        <v>560.2422951058084</v>
       </c>
       <c r="O53">
-        <v>88.99017288092934</v>
+        <v>89.63876721692934</v>
       </c>
       <c r="P53">
-        <v>467.198407624879</v>
+        <v>470.603527888879</v>
       </c>
       <c r="Q53">
-        <v>791.898407624879</v>
+        <v>795.303527888879</v>
       </c>
       <c r="R53">
         <v>1.040816326530612</v>
       </c>
       <c r="S53">
-        <v>0.1183523547799635</v>
+        <v>0.1183387659003572</v>
       </c>
       <c r="T53">
         <v>0.9985234165713481</v>
       </c>
       <c r="U53">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V53">
         <v>0.16</v>
       </c>
       <c r="W53">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.477757220476952</v>
+        <v>5.662558223787197</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5682,13 +5682,13 @@
         <v>0.52</v>
       </c>
       <c r="B54">
-        <v>0.09227152415188947</v>
+        <v>0.09112919720114543</v>
       </c>
       <c r="C54">
-        <v>1814.476412412821</v>
+        <v>1891.517086850472</v>
       </c>
       <c r="D54">
-        <v>3072.76841241282</v>
+        <v>3149.809086850472</v>
       </c>
       <c r="E54">
         <v>-196.6079999999999</v>
@@ -5715,37 +5715,37 @@
         <v>680.4</v>
       </c>
       <c r="M54">
-        <v>126.6469375234896</v>
+        <v>122.5137383234895</v>
       </c>
       <c r="N54">
-        <v>553.7530624765104</v>
+        <v>557.8862616765105</v>
       </c>
       <c r="O54">
-        <v>88.60048999624166</v>
+        <v>89.26180186824168</v>
       </c>
       <c r="P54">
-        <v>465.1525724802688</v>
+        <v>468.6244598082688</v>
       </c>
       <c r="Q54">
-        <v>789.8525724802688</v>
+        <v>793.3244598082688</v>
       </c>
       <c r="R54">
         <v>1.083333333333333</v>
       </c>
       <c r="S54">
-        <v>0.1197348310524476</v>
+        <v>0.1197209832383975</v>
       </c>
       <c r="T54">
         <v>1.017550158502967</v>
       </c>
       <c r="U54">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V54">
         <v>0.16</v>
       </c>
       <c r="W54">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.372415735467779</v>
+        <v>5.553662873329749</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5764,13 +5764,13 @@
         <v>0.53</v>
       </c>
       <c r="B55">
-        <v>0.09242079700808822</v>
+        <v>0.09125664165760725</v>
       </c>
       <c r="C55">
-        <v>1774.066865095009</v>
+        <v>1852.115128548366</v>
       </c>
       <c r="D55">
-        <v>3062.929865095009</v>
+        <v>3140.978128548365</v>
       </c>
       <c r="E55">
         <v>-166.037</v>
@@ -5797,37 +5797,37 @@
         <v>680.4</v>
       </c>
       <c r="M55">
-        <v>129.0824555527874</v>
+        <v>124.8697717527874</v>
       </c>
       <c r="N55">
-        <v>551.3175444472125</v>
+        <v>555.5302282472126</v>
       </c>
       <c r="O55">
-        <v>88.210807111554</v>
+        <v>88.88483651955401</v>
       </c>
       <c r="P55">
-        <v>463.1067373356585</v>
+        <v>466.6453917276585</v>
       </c>
       <c r="Q55">
-        <v>787.8067373356586</v>
+        <v>791.3453917276586</v>
       </c>
       <c r="R55">
         <v>1.127659574468085</v>
       </c>
       <c r="S55">
-        <v>0.1211761361024842</v>
+        <v>0.1211620183355034</v>
       </c>
       <c r="T55">
         <v>1.03738654902742</v>
       </c>
       <c r="U55">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V55">
         <v>0.16</v>
       </c>
       <c r="W55">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.271049400836311</v>
+        <v>5.448876781380132</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5846,13 +5846,13 @@
         <v>0.54</v>
       </c>
       <c r="B56">
-        <v>0.09257006986428698</v>
+        <v>0.0913840861140691</v>
       </c>
       <c r="C56">
-        <v>1733.720119824029</v>
+        <v>1812.762549614223</v>
       </c>
       <c r="D56">
-        <v>3053.154119824029</v>
+        <v>3132.196549614223</v>
       </c>
       <c r="E56">
         <v>-135.4659999999999</v>
@@ -5879,37 +5879,37 @@
         <v>680.4</v>
       </c>
       <c r="M56">
-        <v>131.5179735820853</v>
+        <v>127.2258051820853</v>
       </c>
       <c r="N56">
-        <v>548.8820264179146</v>
+        <v>553.1741948179147</v>
       </c>
       <c r="O56">
-        <v>87.82112422686635</v>
+        <v>88.50787117086635</v>
       </c>
       <c r="P56">
-        <v>461.0609021910483</v>
+        <v>464.6663236470483</v>
       </c>
       <c r="Q56">
-        <v>785.7609021910483</v>
+        <v>789.3663236470484</v>
       </c>
       <c r="R56">
         <v>1.173913043478261</v>
       </c>
       <c r="S56">
-        <v>0.1226801065894789</v>
+        <v>0.1226657071324835</v>
       </c>
       <c r="T56">
         <v>1.058085391313807</v>
       </c>
       <c r="U56">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V56">
         <v>0.16</v>
       </c>
       <c r="W56">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.173437374894897</v>
+        <v>5.347971655799018</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5928,13 +5928,13 @@
         <v>0.55</v>
       </c>
       <c r="B57">
-        <v>0.09271934272048574</v>
+        <v>0.09151153057053094</v>
       </c>
       <c r="C57">
-        <v>1693.435577189892</v>
+        <v>1773.458937036719</v>
       </c>
       <c r="D57">
-        <v>3043.440577189891</v>
+        <v>3123.463937036719</v>
       </c>
       <c r="E57">
         <v>-104.895</v>
@@ -5961,37 +5961,37 @@
         <v>680.4</v>
       </c>
       <c r="M57">
-        <v>133.9534916113832</v>
+        <v>129.5818386113832</v>
       </c>
       <c r="N57">
-        <v>546.4465083886168</v>
+        <v>550.8181613886168</v>
       </c>
       <c r="O57">
-        <v>87.4314413421787</v>
+        <v>88.13090582217869</v>
       </c>
       <c r="P57">
-        <v>459.0150670464382</v>
+        <v>462.6872555664381</v>
       </c>
       <c r="Q57">
-        <v>783.7150670464382</v>
+        <v>787.3872555664382</v>
       </c>
       <c r="R57">
         <v>1.222222222222223</v>
       </c>
       <c r="S57">
-        <v>0.1242509202092289</v>
+        <v>0.1242362265426626</v>
       </c>
       <c r="T57">
         <v>1.079704182146255</v>
       </c>
       <c r="U57">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V57">
         <v>0.16</v>
       </c>
       <c r="W57">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.079374877169537</v>
+        <v>5.250735807511763</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6010,13 +6010,13 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09286861557668452</v>
+        <v>0.09163897502699279</v>
       </c>
       <c r="C58">
-        <v>1653.212645386453</v>
+        <v>1734.203882397638</v>
       </c>
       <c r="D58">
-        <v>3033.788645386453</v>
+        <v>3114.779882397638</v>
       </c>
       <c r="E58">
         <v>-74.32399999999984</v>
@@ -6043,37 +6043,37 @@
         <v>680.4</v>
       </c>
       <c r="M58">
-        <v>136.3890096406811</v>
+        <v>131.937872040681</v>
       </c>
       <c r="N58">
-        <v>544.010990359319</v>
+        <v>548.4621279593189</v>
       </c>
       <c r="O58">
-        <v>87.04175845749103</v>
+        <v>87.75394047349103</v>
       </c>
       <c r="P58">
-        <v>456.9692319018279</v>
+        <v>460.7081874858279</v>
       </c>
       <c r="Q58">
-        <v>781.669231901828</v>
+        <v>785.408187485828</v>
       </c>
       <c r="R58">
         <v>1.272727272727273</v>
       </c>
       <c r="S58">
-        <v>0.1258931344480584</v>
+        <v>0.1258781331987591</v>
       </c>
       <c r="T58">
         <v>1.102305645289268</v>
       </c>
       <c r="U58">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V58">
         <v>0.16</v>
       </c>
       <c r="W58">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.988671754362938</v>
+        <v>5.15697266809191</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6092,13 +6092,13 @@
         <v>0.5700000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09301788843288328</v>
+        <v>0.09176641948345463</v>
       </c>
       <c r="C59">
-        <v>1613.05074009123</v>
+        <v>1694.996981808224</v>
       </c>
       <c r="D59">
-        <v>3024.19774009123</v>
+        <v>3106.143981808224</v>
       </c>
       <c r="E59">
         <v>-43.75299999999993</v>
@@ -6125,37 +6125,37 @@
         <v>680.4</v>
       </c>
       <c r="M59">
-        <v>138.8245276699789</v>
+        <v>134.2939054699789</v>
       </c>
       <c r="N59">
-        <v>541.5754723300211</v>
+        <v>546.1060945300211</v>
       </c>
       <c r="O59">
-        <v>86.65207557280337</v>
+        <v>87.37697512480338</v>
       </c>
       <c r="P59">
-        <v>454.9233967572177</v>
+        <v>458.7291194052177</v>
       </c>
       <c r="Q59">
-        <v>779.6233967572177</v>
+        <v>783.4291194052178</v>
       </c>
       <c r="R59">
         <v>1.325581395348838</v>
       </c>
       <c r="S59">
-        <v>0.127611730744508</v>
+        <v>0.1275964076063018</v>
       </c>
       <c r="T59">
         <v>1.125958339276143</v>
       </c>
       <c r="U59">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V59">
         <v>0.16</v>
       </c>
       <c r="W59">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.901151197268852</v>
+        <v>5.066499463388544</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6174,13 +6174,13 @@
         <v>0.58</v>
       </c>
       <c r="B60">
-        <v>0.09316716128908203</v>
+        <v>0.09189386393991647</v>
       </c>
       <c r="C60">
-        <v>1572.949284347468</v>
+        <v>1655.837835846545</v>
       </c>
       <c r="D60">
-        <v>3014.667284347468</v>
+        <v>3097.555835846545</v>
       </c>
       <c r="E60">
         <v>-13.18200000000002</v>
@@ -6207,37 +6207,37 @@
         <v>680.4</v>
       </c>
       <c r="M60">
-        <v>141.2600456992768</v>
+        <v>136.6499388992768</v>
       </c>
       <c r="N60">
-        <v>539.1399543007232</v>
+        <v>543.7500611007232</v>
       </c>
       <c r="O60">
-        <v>86.26239268811571</v>
+        <v>87.00000977611572</v>
       </c>
       <c r="P60">
-        <v>452.8775616126075</v>
+        <v>456.7500513246075</v>
       </c>
       <c r="Q60">
-        <v>777.5775616126075</v>
+        <v>781.4500513246076</v>
       </c>
       <c r="R60">
         <v>1.380952380952381</v>
       </c>
       <c r="S60">
-        <v>0.129412164959836</v>
+        <v>0.1293965046046799</v>
       </c>
       <c r="T60">
         <v>1.150737352024297</v>
       </c>
       <c r="U60">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V60">
         <v>0.16</v>
       </c>
       <c r="W60">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.816648590419389</v>
+        <v>4.979146024364603</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6256,13 +6256,13 @@
         <v>0.59</v>
       </c>
       <c r="B61">
-        <v>0.0933164341452808</v>
+        <v>0.09202130839637832</v>
       </c>
       <c r="C61">
-        <v>1532.907708448451</v>
+        <v>1616.726049495923</v>
       </c>
       <c r="D61">
-        <v>3005.19670844845</v>
+        <v>3089.015049495923</v>
       </c>
       <c r="E61">
         <v>17.3889999999999</v>
@@ -6289,37 +6289,37 @@
         <v>680.4</v>
       </c>
       <c r="M61">
-        <v>143.6955637285747</v>
+        <v>139.0059723285747</v>
       </c>
       <c r="N61">
-        <v>536.7044362714253</v>
+        <v>541.3940276714253</v>
       </c>
       <c r="O61">
-        <v>85.87270980342804</v>
+        <v>86.62304442742806</v>
       </c>
       <c r="P61">
-        <v>450.8317264679972</v>
+        <v>454.7709832439973</v>
       </c>
       <c r="Q61">
-        <v>775.5317264679973</v>
+        <v>779.4709832439974</v>
       </c>
       <c r="R61">
         <v>1.439024390243902</v>
       </c>
       <c r="S61">
-        <v>0.1313004252344484</v>
+        <v>0.131284411212735</v>
       </c>
       <c r="T61">
         <v>1.17672509710163</v>
       </c>
       <c r="U61">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V61">
         <v>0.16</v>
       </c>
       <c r="W61">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.735010478717365</v>
+        <v>4.894753718866898</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6338,13 +6338,13 @@
         <v>0.6</v>
       </c>
       <c r="B62">
-        <v>0.09346570700147958</v>
+        <v>0.09214875285284016</v>
       </c>
       <c r="C62">
-        <v>1492.925449823978</v>
+        <v>1577.661232084365</v>
       </c>
       <c r="D62">
-        <v>2995.785449823978</v>
+        <v>3080.521232084365</v>
       </c>
       <c r="E62">
         <v>47.96000000000004</v>
@@ -6371,37 +6371,37 @@
         <v>680.4</v>
       </c>
       <c r="M62">
-        <v>146.1310817578726</v>
+        <v>141.3620057578725</v>
       </c>
       <c r="N62">
-        <v>534.2689182421275</v>
+        <v>539.0379942421274</v>
       </c>
       <c r="O62">
-        <v>85.48302691874039</v>
+        <v>86.24607907874039</v>
       </c>
       <c r="P62">
-        <v>448.7858913233871</v>
+        <v>452.791915163387</v>
       </c>
       <c r="Q62">
-        <v>773.4858913233871</v>
+        <v>777.491915163387</v>
       </c>
       <c r="R62">
         <v>1.5</v>
       </c>
       <c r="S62">
-        <v>0.1332830985227914</v>
+        <v>0.1332667131511929</v>
       </c>
       <c r="T62">
         <v>1.20401222943283</v>
       </c>
       <c r="U62">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V62">
         <v>0.16</v>
       </c>
       <c r="W62">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.656093637405409</v>
+        <v>4.813174490219117</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6420,13 +6420,13 @@
         <v>0.61</v>
       </c>
       <c r="B63">
-        <v>0.09361497985767833</v>
+        <v>0.092276197309302</v>
       </c>
       <c r="C63">
-        <v>1453.001952928969</v>
+        <v>1538.642997224993</v>
       </c>
       <c r="D63">
-        <v>2986.432952928968</v>
+        <v>3072.073997224993</v>
       </c>
       <c r="E63">
         <v>78.53099999999995</v>
@@ -6453,37 +6453,37 @@
         <v>680.4</v>
       </c>
       <c r="M63">
-        <v>148.5665997871704</v>
+        <v>143.7180391871704</v>
       </c>
       <c r="N63">
-        <v>531.8334002128296</v>
+        <v>536.6819608128296</v>
       </c>
       <c r="O63">
-        <v>85.09334403405273</v>
+        <v>85.86911373005275</v>
       </c>
       <c r="P63">
-        <v>446.7400561787769</v>
+        <v>450.8128470827769</v>
       </c>
       <c r="Q63">
-        <v>771.4400561787769</v>
+        <v>775.5128470827769</v>
       </c>
       <c r="R63">
         <v>1.564102564102564</v>
       </c>
       <c r="S63">
-        <v>0.1353674473643827</v>
+        <v>0.1353506715993152</v>
       </c>
       <c r="T63">
         <v>1.232698701883578</v>
       </c>
       <c r="U63">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V63">
         <v>0.16</v>
       </c>
       <c r="W63">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.579764233513517</v>
+        <v>4.73426999037946</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6502,13 +6502,13 @@
         <v>0.62</v>
       </c>
       <c r="B64">
-        <v>0.0937642527138771</v>
+        <v>0.09240364176576385</v>
       </c>
       <c r="C64">
-        <v>1413.136669134136</v>
+        <v>1499.670962757456</v>
       </c>
       <c r="D64">
-        <v>2977.138669134136</v>
+        <v>3063.672962757456</v>
       </c>
       <c r="E64">
         <v>109.1020000000001</v>
@@ -6535,37 +6535,37 @@
         <v>680.4</v>
       </c>
       <c r="M64">
-        <v>151.0021178164683</v>
+        <v>146.0740726164683</v>
       </c>
       <c r="N64">
-        <v>529.3978821835317</v>
+        <v>534.3259273835317</v>
       </c>
       <c r="O64">
-        <v>84.70366114936508</v>
+        <v>85.49214838136508</v>
       </c>
       <c r="P64">
-        <v>444.6942210341666</v>
+        <v>448.8337790021666</v>
       </c>
       <c r="Q64">
-        <v>769.3942210341667</v>
+        <v>773.5337790021667</v>
       </c>
       <c r="R64">
         <v>1.631578947368421</v>
       </c>
       <c r="S64">
-        <v>0.1375614987765842</v>
+        <v>0.137544312071023</v>
       </c>
       <c r="T64">
         <v>1.262894988673839</v>
       </c>
       <c r="U64">
-        <v>0.07966759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V64">
         <v>0.16</v>
       </c>
       <c r="W64">
-        <v>0.06692077932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.505897068456846</v>
+        <v>4.657910796986242</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6584,13 +6584,13 @@
         <v>0.63</v>
       </c>
       <c r="B65">
-        <v>0.09528944557007585</v>
+        <v>0.09253108622222569</v>
       </c>
       <c r="C65">
-        <v>1290.814578012153</v>
+        <v>1460.744750690295</v>
       </c>
       <c r="D65">
-        <v>2885.387578012153</v>
+        <v>3055.317750690295</v>
       </c>
       <c r="E65">
         <v>139.673</v>
@@ -6617,45 +6617,45 @@
         <v>680.4</v>
       </c>
       <c r="M65">
-        <v>158.4451656457662</v>
+        <v>148.4301060457662</v>
       </c>
       <c r="N65">
-        <v>521.9548343542338</v>
+        <v>531.9698939542338</v>
       </c>
       <c r="O65">
-        <v>83.5127734966774</v>
+        <v>85.11518303267742</v>
       </c>
       <c r="P65">
-        <v>438.4420608575564</v>
+        <v>446.8547109215564</v>
       </c>
       <c r="Q65">
-        <v>763.1420608575564</v>
+        <v>771.5547109215565</v>
       </c>
       <c r="R65">
         <v>1.702702702702703</v>
       </c>
       <c r="S65">
-        <v>0.1398741475624181</v>
+        <v>0.1398565277033636</v>
       </c>
       <c r="T65">
         <v>1.294723507182493</v>
       </c>
       <c r="U65">
-        <v>0.08226759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V65">
         <v>0.16</v>
       </c>
       <c r="W65">
-        <v>0.06910477932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y65">
-        <v>4.294230103057618</v>
+        <v>4.583975704970587</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6666,13 +6666,13 @@
         <v>0.64</v>
       </c>
       <c r="B66">
-        <v>0.09546055842627461</v>
+        <v>0.09265853067868753</v>
       </c>
       <c r="C66">
-        <v>1250.301545031451</v>
+        <v>1421.863987144252</v>
       </c>
       <c r="D66">
-        <v>2875.445545031451</v>
+        <v>3047.007987144252</v>
       </c>
       <c r="E66">
         <v>170.2439999999999</v>
@@ -6699,45 +6699,45 @@
         <v>680.4</v>
       </c>
       <c r="M66">
-        <v>160.9601682750641</v>
+        <v>150.786139475064</v>
       </c>
       <c r="N66">
-        <v>519.4398317249359</v>
+        <v>529.6138605249359</v>
       </c>
       <c r="O66">
-        <v>83.11037307598974</v>
+        <v>84.73821768398976</v>
       </c>
       <c r="P66">
-        <v>436.3294586489461</v>
+        <v>444.8756428409462</v>
       </c>
       <c r="Q66">
-        <v>761.0294586489462</v>
+        <v>769.5756428409462</v>
       </c>
       <c r="R66">
         <v>1.777777777777778</v>
       </c>
       <c r="S66">
-        <v>0.1423152768363539</v>
+        <v>0.1422971997597231</v>
       </c>
       <c r="T66">
         <v>1.328320276719405</v>
       </c>
       <c r="U66">
-        <v>0.08226759442929168</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V66">
         <v>0.16</v>
       </c>
       <c r="W66">
-        <v>0.06910477932060501</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.227132757697342</v>
+        <v>4.512351084580422</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>0.65</v>
       </c>
       <c r="B67">
-        <v>0.09563167128247339</v>
+        <v>0.09415097513514938</v>
       </c>
       <c r="C67">
-        <v>1209.856790300945</v>
+        <v>1297.241312560702</v>
       </c>
       <c r="D67">
-        <v>2865.571790300944</v>
+        <v>2952.956312560702</v>
       </c>
       <c r="E67">
         <v>200.8150000000001</v>
@@ -6781,37 +6781,37 @@
         <v>680.4</v>
       </c>
       <c r="M67">
-        <v>163.475170904362</v>
+        <v>158.1099604043619</v>
       </c>
       <c r="N67">
-        <v>516.924829095638</v>
+        <v>522.2900395956381</v>
       </c>
       <c r="O67">
-        <v>82.70797265530207</v>
+        <v>83.56640633530209</v>
       </c>
       <c r="P67">
-        <v>434.2168564403359</v>
+        <v>438.723633260336</v>
       </c>
       <c r="Q67">
-        <v>758.916856440336</v>
+        <v>763.423633260336</v>
       </c>
       <c r="R67">
         <v>1.857142857142857</v>
       </c>
       <c r="S67">
-        <v>0.1448958992116575</v>
+        <v>0.1448773387907318</v>
       </c>
       <c r="T67">
         <v>1.363836861658427</v>
       </c>
       <c r="U67">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V67">
         <v>0.16</v>
       </c>
       <c r="W67">
-        <v>0.06910477932060501</v>
+        <v>0.066836779320605</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.16209994604046</v>
+        <v>4.303334200197732</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6830,13 +6830,13 @@
         <v>0.66</v>
       </c>
       <c r="B68">
-        <v>0.09580278413867216</v>
+        <v>0.09429941959161123</v>
       </c>
       <c r="C68">
-        <v>1169.479612862481</v>
+        <v>1257.632060176142</v>
       </c>
       <c r="D68">
-        <v>2855.765612862481</v>
+        <v>2943.918060176141</v>
       </c>
       <c r="E68">
         <v>231.386</v>
@@ -6863,37 +6863,37 @@
         <v>680.4</v>
       </c>
       <c r="M68">
-        <v>165.9901735336598</v>
+        <v>160.5424213336598</v>
       </c>
       <c r="N68">
-        <v>514.4098264663402</v>
+        <v>519.8575786663401</v>
       </c>
       <c r="O68">
-        <v>82.30557223461443</v>
+        <v>83.17721258661443</v>
       </c>
       <c r="P68">
-        <v>432.1042542317257</v>
+        <v>436.6803660797257</v>
       </c>
       <c r="Q68">
-        <v>756.8042542317257</v>
+        <v>761.3803660797257</v>
       </c>
       <c r="R68">
         <v>1.941176470588236</v>
       </c>
       <c r="S68">
-        <v>0.1476283229031554</v>
+        <v>0.1476092507059174</v>
       </c>
       <c r="T68">
         <v>1.401442657476214</v>
       </c>
       <c r="U68">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V68">
         <v>0.16</v>
       </c>
       <c r="W68">
-        <v>0.06910477932060501</v>
+        <v>0.066836779320605</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.099037825645908</v>
+        <v>4.238132166861403</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6912,13 +6912,13 @@
         <v>0.67</v>
       </c>
       <c r="B69">
-        <v>0.09597389699487091</v>
+        <v>0.09444786404807305</v>
       </c>
       <c r="C69">
-        <v>1129.169321320087</v>
+        <v>1218.077966573529</v>
       </c>
       <c r="D69">
-        <v>2846.026321320087</v>
+        <v>2934.934966573529</v>
       </c>
       <c r="E69">
         <v>261.9570000000001</v>
@@ -6945,37 +6945,37 @@
         <v>680.4</v>
       </c>
       <c r="M69">
-        <v>168.5051761629577</v>
+        <v>162.9748822629577</v>
       </c>
       <c r="N69">
-        <v>511.8948238370423</v>
+        <v>517.4251177370422</v>
       </c>
       <c r="O69">
-        <v>81.90317181392676</v>
+        <v>82.78801883792676</v>
       </c>
       <c r="P69">
-        <v>429.9916520231155</v>
+        <v>434.6370988991155</v>
       </c>
       <c r="Q69">
-        <v>754.6916520231156</v>
+        <v>759.3370988991155</v>
       </c>
       <c r="R69">
         <v>2.030303030303031</v>
       </c>
       <c r="S69">
-        <v>0.1505263480305017</v>
+        <v>0.1505067330402052</v>
       </c>
       <c r="T69">
         <v>1.441327592434474</v>
       </c>
       <c r="U69">
-        <v>0.08226759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V69">
         <v>0.16</v>
       </c>
       <c r="W69">
-        <v>0.06910477932060501</v>
+        <v>0.066836779320605</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.037858156606417</v>
+        <v>4.174876462878396</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6994,13 +6994,13 @@
         <v>0.68</v>
       </c>
       <c r="B70">
-        <v>0.09768724985106968</v>
+        <v>0.09459630850453489</v>
       </c>
       <c r="C70">
-        <v>1004.620564926238</v>
+        <v>1178.57852835318</v>
       </c>
       <c r="D70">
-        <v>2752.048564926238</v>
+        <v>2926.006528353179</v>
       </c>
       <c r="E70">
         <v>292.528</v>
@@ -7027,45 +7027,45 @@
         <v>680.4</v>
       </c>
       <c r="M70">
-        <v>176.6330143922555</v>
+        <v>165.4073431922556</v>
       </c>
       <c r="N70">
-        <v>503.7669856077445</v>
+        <v>514.9926568077444</v>
       </c>
       <c r="O70">
-        <v>80.60271769723911</v>
+        <v>82.39882508923911</v>
       </c>
       <c r="P70">
-        <v>423.1642679105054</v>
+        <v>432.5938317185053</v>
       </c>
       <c r="Q70">
-        <v>747.8642679105054</v>
+        <v>757.2938317185053</v>
       </c>
       <c r="R70">
         <v>2.125</v>
       </c>
       <c r="S70">
-        <v>0.1536054997283071</v>
+        <v>0.1535853080203859</v>
       </c>
       <c r="T70">
         <v>1.483705335827624</v>
       </c>
       <c r="U70">
-        <v>0.08496759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V70">
         <v>0.16</v>
       </c>
       <c r="W70">
-        <v>0.07137277932060501</v>
+        <v>0.066836779320605</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>3.852054511672491</v>
+        <v>4.113481220777244</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7076,13 +7076,13 @@
         <v>0.6900000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09788104270726844</v>
+        <v>0.09474475296099674</v>
       </c>
       <c r="C71">
-        <v>963.8092294016128</v>
+        <v>1139.133248222451</v>
       </c>
       <c r="D71">
-        <v>2741.808229401613</v>
+        <v>2917.13224822245</v>
       </c>
       <c r="E71">
         <v>323.0989999999999</v>
@@ -7109,45 +7109,45 @@
         <v>680.4</v>
       </c>
       <c r="M71">
-        <v>179.2305587215534</v>
+        <v>167.8398041215534</v>
       </c>
       <c r="N71">
-        <v>501.1694412784466</v>
+        <v>512.5601958784466</v>
       </c>
       <c r="O71">
-        <v>80.18711060455145</v>
+        <v>82.00963134055146</v>
       </c>
       <c r="P71">
-        <v>420.9823306738951</v>
+        <v>430.5505645378952</v>
       </c>
       <c r="Q71">
-        <v>745.6823306738952</v>
+        <v>755.2505645378952</v>
       </c>
       <c r="R71">
         <v>2.225806451612904</v>
       </c>
       <c r="S71">
-        <v>0.156883306374358</v>
+        <v>0.1568625007412235</v>
       </c>
       <c r="T71">
         <v>1.528817127181624</v>
       </c>
       <c r="U71">
-        <v>0.08496759442929168</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V71">
         <v>0.16</v>
       </c>
       <c r="W71">
-        <v>0.07137277932060501</v>
+        <v>0.066836779320605</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.79622763469173</v>
+        <v>4.053865550910908</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7158,13 +7158,13 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09807483556346722</v>
+        <v>0.09695119741745858</v>
       </c>
       <c r="C72">
-        <v>923.0738196584207</v>
+        <v>982.7296068997734</v>
       </c>
       <c r="D72">
-        <v>2731.643819658421</v>
+        <v>2791.299606899774</v>
       </c>
       <c r="E72">
         <v>353.6700000000003</v>
@@ -7191,37 +7191,37 @@
         <v>680.4</v>
       </c>
       <c r="M72">
-        <v>181.8281030508513</v>
+        <v>177.7621600508513</v>
       </c>
       <c r="N72">
-        <v>498.5718969491487</v>
+        <v>502.6378399491487</v>
       </c>
       <c r="O72">
-        <v>79.77150351186378</v>
+        <v>80.42205439186378</v>
       </c>
       <c r="P72">
-        <v>418.8003934372849</v>
+        <v>422.2157855572849</v>
       </c>
       <c r="Q72">
-        <v>743.5003934372849</v>
+        <v>746.9157855572849</v>
       </c>
       <c r="R72">
         <v>2.333333333333334</v>
       </c>
       <c r="S72">
-        <v>0.160379633463479</v>
+        <v>0.1603581729767836</v>
       </c>
       <c r="T72">
         <v>1.576936371292556</v>
       </c>
       <c r="U72">
-        <v>0.08496759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V72">
         <v>0.16</v>
       </c>
       <c r="W72">
-        <v>0.07137277932060501</v>
+        <v>0.06977677932060501</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.74199581133899</v>
+        <v>3.827586252357431</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0.71</v>
       </c>
       <c r="B73">
-        <v>0.09826862841966598</v>
+        <v>0.09712904187392044</v>
       </c>
       <c r="C73">
-        <v>882.4134944011425</v>
+        <v>942.4873341994066</v>
       </c>
       <c r="D73">
-        <v>2721.554494401142</v>
+        <v>2781.628334199406</v>
       </c>
       <c r="E73">
         <v>384.2409999999998</v>
@@ -7273,37 +7273,37 @@
         <v>680.4</v>
       </c>
       <c r="M73">
-        <v>184.4256473801492</v>
+        <v>180.3016194801492</v>
       </c>
       <c r="N73">
-        <v>495.9743526198508</v>
+        <v>500.0983805198508</v>
       </c>
       <c r="O73">
-        <v>79.35589641917613</v>
+        <v>80.01574088317614</v>
       </c>
       <c r="P73">
-        <v>416.6184562006747</v>
+        <v>420.0826396366747</v>
       </c>
       <c r="Q73">
-        <v>741.3184562006747</v>
+        <v>744.7826396366747</v>
       </c>
       <c r="R73">
         <v>2.448275862068965</v>
       </c>
       <c r="S73">
-        <v>0.1641170865587463</v>
+        <v>0.1640949260561754</v>
       </c>
       <c r="T73">
         <v>1.628374183962863</v>
       </c>
       <c r="U73">
-        <v>0.08496759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V73">
         <v>0.16</v>
       </c>
       <c r="W73">
-        <v>0.07137277932060501</v>
+        <v>0.06977677932060501</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.689291644982104</v>
+        <v>3.773676586831272</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7322,13 +7322,13 @@
         <v>0.72</v>
       </c>
       <c r="B74">
-        <v>0.09846242127586474</v>
+        <v>0.09730688633038229</v>
       </c>
       <c r="C74">
-        <v>841.8274247178138</v>
+        <v>902.31184799534</v>
       </c>
       <c r="D74">
-        <v>2711.539424717814</v>
+        <v>2772.02384799534</v>
       </c>
       <c r="E74">
         <v>414.8120000000001</v>
@@ -7355,37 +7355,37 @@
         <v>680.4</v>
       </c>
       <c r="M74">
-        <v>187.0231917094471</v>
+        <v>182.8410789094471</v>
       </c>
       <c r="N74">
-        <v>493.3768082905529</v>
+        <v>497.5589210905529</v>
       </c>
       <c r="O74">
-        <v>78.94028932648847</v>
+        <v>79.60942737448846</v>
       </c>
       <c r="P74">
-        <v>414.4365189640644</v>
+        <v>417.9494937160644</v>
       </c>
       <c r="Q74">
-        <v>739.1365189640644</v>
+        <v>742.6494937160644</v>
       </c>
       <c r="R74">
         <v>2.571428571428571</v>
       </c>
       <c r="S74">
-        <v>0.1681215005893897</v>
+        <v>0.1680985900698095</v>
       </c>
       <c r="T74">
         <v>1.68348612610962</v>
       </c>
       <c r="U74">
-        <v>0.08496759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V74">
         <v>0.16</v>
       </c>
       <c r="W74">
-        <v>0.07137277932060501</v>
+        <v>0.06977677932060501</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.638051483246241</v>
+        <v>3.72126441201417</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7404,13 +7404,13 @@
         <v>0.73</v>
       </c>
       <c r="B75">
-        <v>0.0986562141320635</v>
+        <v>0.09748473078684411</v>
       </c>
       <c r="C75">
-        <v>801.3147938530174</v>
+        <v>862.2024588610498</v>
       </c>
       <c r="D75">
-        <v>2701.597793853017</v>
+        <v>2762.48545886105</v>
       </c>
       <c r="E75">
         <v>445.383</v>
@@ -7437,37 +7437,37 @@
         <v>680.4</v>
       </c>
       <c r="M75">
-        <v>189.620736038745</v>
+        <v>185.3805383387449</v>
       </c>
       <c r="N75">
-        <v>490.779263961255</v>
+        <v>495.019461661255</v>
       </c>
       <c r="O75">
-        <v>78.5246822338008</v>
+        <v>79.2031138658008</v>
       </c>
       <c r="P75">
-        <v>412.2545817274543</v>
+        <v>415.8163477954542</v>
       </c>
       <c r="Q75">
-        <v>736.9545817274543</v>
+        <v>740.5163477954543</v>
       </c>
       <c r="R75">
         <v>2.703703703703703</v>
       </c>
       <c r="S75">
-        <v>0.1724225378815624</v>
+        <v>0.1723988217881572</v>
       </c>
       <c r="T75">
         <v>1.742680434341323</v>
       </c>
       <c r="U75">
-        <v>0.08496759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V75">
         <v>0.16</v>
       </c>
       <c r="W75">
-        <v>0.07137277932060501</v>
+        <v>0.06977677932060501</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.588215161557936</v>
+        <v>3.670288187192058</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7486,13 +7486,13 @@
         <v>0.74</v>
       </c>
       <c r="B76">
-        <v>0.09885000698826227</v>
+        <v>0.09766257524330596</v>
       </c>
       <c r="C76">
-        <v>760.8747969858373</v>
+        <v>822.1584868265904</v>
       </c>
       <c r="D76">
-        <v>2691.728796985837</v>
+        <v>2753.01248682659</v>
       </c>
       <c r="E76">
         <v>475.954</v>
@@ -7519,37 +7519,37 @@
         <v>680.4</v>
       </c>
       <c r="M76">
-        <v>192.2182803680428</v>
+        <v>187.9199977680428</v>
       </c>
       <c r="N76">
-        <v>488.1817196319572</v>
+        <v>492.4800022319572</v>
       </c>
       <c r="O76">
-        <v>78.10907514111315</v>
+        <v>78.79680035711316</v>
       </c>
       <c r="P76">
-        <v>410.072644490844</v>
+        <v>413.683201874844</v>
       </c>
       <c r="Q76">
-        <v>734.7726444908441</v>
+        <v>738.3832018748441</v>
       </c>
       <c r="R76">
         <v>2.846153846153846</v>
       </c>
       <c r="S76">
-        <v>0.1770544241962098</v>
+        <v>0.1770298405617625</v>
       </c>
       <c r="T76">
         <v>1.806428150898541</v>
       </c>
       <c r="U76">
-        <v>0.08496759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V76">
         <v>0.16</v>
       </c>
       <c r="W76">
-        <v>0.07137277932060501</v>
+        <v>0.06977677932060501</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.53972576748283</v>
+        <v>3.62068969817595</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>0.75</v>
       </c>
       <c r="B77">
-        <v>0.102004799844461</v>
+        <v>0.09784041969976781</v>
       </c>
       <c r="C77">
-        <v>579.2162243398102</v>
+        <v>782.1792612170157</v>
       </c>
       <c r="D77">
-        <v>2540.64122433981</v>
+        <v>2743.604261217015</v>
       </c>
       <c r="E77">
         <v>506.5249999999999</v>
@@ -7601,45 +7601,45 @@
         <v>680.4</v>
       </c>
       <c r="M77">
-        <v>205.5921021973407</v>
+        <v>190.4594571973407</v>
       </c>
       <c r="N77">
-        <v>474.8078978026593</v>
+        <v>489.9405428026593</v>
       </c>
       <c r="O77">
-        <v>75.9692636484255</v>
+        <v>78.3904868484255</v>
       </c>
       <c r="P77">
-        <v>398.8386341542338</v>
+        <v>411.5500559542338</v>
       </c>
       <c r="Q77">
-        <v>723.5386341542339</v>
+        <v>736.2500559542339</v>
       </c>
       <c r="R77">
         <v>3</v>
       </c>
       <c r="S77">
-        <v>0.1820568614160291</v>
+        <v>0.1820313408372562</v>
       </c>
       <c r="T77">
         <v>1.875275684780337</v>
       </c>
       <c r="U77">
-        <v>0.08966759442929167</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V77">
         <v>0.16</v>
       </c>
       <c r="W77">
-        <v>0.07532077932060501</v>
+        <v>0.06977677932060501</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.309465649351198</v>
+        <v>3.572413835533604</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7650,13 +7650,13 @@
         <v>0.76</v>
       </c>
       <c r="B78">
-        <v>0.1022380727006598</v>
+        <v>0.09801826415622965</v>
       </c>
       <c r="C78">
-        <v>538.1441103467532</v>
+        <v>742.2641204940937</v>
       </c>
       <c r="D78">
-        <v>2530.140110346753</v>
+        <v>2734.260120494093</v>
       </c>
       <c r="E78">
         <v>537.0959999999998</v>
@@ -7683,45 +7683,45 @@
         <v>680.4</v>
       </c>
       <c r="M78">
-        <v>208.3333302266385</v>
+        <v>192.9989166266386</v>
       </c>
       <c r="N78">
-        <v>472.0666697733615</v>
+        <v>487.4010833733614</v>
       </c>
       <c r="O78">
-        <v>75.53066716373783</v>
+        <v>77.98417333973782</v>
       </c>
       <c r="P78">
-        <v>396.5360026096237</v>
+        <v>409.4169100336236</v>
       </c>
       <c r="Q78">
-        <v>721.2360026096237</v>
+        <v>734.1169100336236</v>
       </c>
       <c r="R78">
         <v>3.166666666666667</v>
       </c>
       <c r="S78">
-        <v>0.1874761684041666</v>
+        <v>0.1874496328023743</v>
       </c>
       <c r="T78">
         <v>1.949860513152282</v>
       </c>
       <c r="U78">
-        <v>0.08966759442929167</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V78">
         <v>0.16</v>
       </c>
       <c r="W78">
-        <v>0.07532077932060501</v>
+        <v>0.06977677932060501</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y78">
-        <v>3.265920048701841</v>
+        <v>3.525408390329214</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7732,13 +7732,13 @@
         <v>0.77</v>
       </c>
       <c r="B79">
-        <v>0.1024713455568586</v>
+        <v>0.1000071486126915</v>
       </c>
       <c r="C79">
-        <v>497.1584465634223</v>
+        <v>611.37189732057</v>
       </c>
       <c r="D79">
-        <v>2519.725446563422</v>
+        <v>2633.93889732057</v>
       </c>
       <c r="E79">
         <v>567.6670000000001</v>
@@ -7765,37 +7765,37 @@
         <v>680.4</v>
       </c>
       <c r="M79">
-        <v>211.0745582559364</v>
+        <v>202.1294836559364</v>
       </c>
       <c r="N79">
-        <v>469.3254417440635</v>
+        <v>478.2705163440635</v>
       </c>
       <c r="O79">
-        <v>75.09207067905017</v>
+        <v>76.52328261505016</v>
       </c>
       <c r="P79">
-        <v>394.2333710650134</v>
+        <v>401.7472337290134</v>
       </c>
       <c r="Q79">
-        <v>718.9333710650135</v>
+        <v>726.4472337290134</v>
       </c>
       <c r="R79">
         <v>3.347826086956522</v>
       </c>
       <c r="S79">
-        <v>0.1933667194782291</v>
+        <v>0.1933390805905462</v>
       </c>
       <c r="T79">
         <v>2.030930978773962</v>
       </c>
       <c r="U79">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V79">
         <v>0.16</v>
       </c>
       <c r="W79">
-        <v>0.07532077932060501</v>
+        <v>0.072128779320605</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.223505502614803</v>
+        <v>3.366159096107783</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7814,13 +7814,13 @@
         <v>0.78</v>
       </c>
       <c r="B80">
-        <v>0.1027046184130573</v>
+        <v>0.1002085130691533</v>
       </c>
       <c r="C80">
-        <v>456.2581698166746</v>
+        <v>571.0527596764018</v>
       </c>
       <c r="D80">
-        <v>2509.396169816675</v>
+        <v>2624.190759676402</v>
       </c>
       <c r="E80">
         <v>598.2380000000001</v>
@@ -7847,37 +7847,37 @@
         <v>680.4</v>
       </c>
       <c r="M80">
-        <v>213.8157862852343</v>
+        <v>204.7545418852343</v>
       </c>
       <c r="N80">
-        <v>466.5842137147657</v>
+        <v>475.6454581147657</v>
       </c>
       <c r="O80">
-        <v>74.6534741943625</v>
+        <v>76.10327329836251</v>
       </c>
       <c r="P80">
-        <v>391.9307395204032</v>
+        <v>399.5421848164032</v>
       </c>
       <c r="Q80">
-        <v>716.6307395204033</v>
+        <v>724.2421848164032</v>
       </c>
       <c r="R80">
         <v>3.545454545454546</v>
       </c>
       <c r="S80">
-        <v>0.1997927751953883</v>
+        <v>0.1997639327230974</v>
       </c>
       <c r="T80">
         <v>2.119371486724885</v>
       </c>
       <c r="U80">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V80">
         <v>0.16</v>
       </c>
       <c r="W80">
-        <v>0.07532077932060501</v>
+        <v>0.072128779320605</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.182178508991537</v>
+        <v>3.323003210260248</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7896,13 +7896,13 @@
         <v>0.79</v>
       </c>
       <c r="B81">
-        <v>0.1029378912692561</v>
+        <v>0.1004098775256152</v>
       </c>
       <c r="C81">
-        <v>415.4422342955349</v>
+        <v>530.8055111675749</v>
       </c>
       <c r="D81">
-        <v>2499.151234295535</v>
+        <v>2614.514511167575</v>
       </c>
       <c r="E81">
         <v>628.809</v>
@@ -7929,37 +7929,37 @@
         <v>680.4</v>
       </c>
       <c r="M81">
-        <v>216.5570143145322</v>
+        <v>207.3796001145322</v>
       </c>
       <c r="N81">
-        <v>463.8429856854678</v>
+        <v>473.0203998854678</v>
       </c>
       <c r="O81">
-        <v>74.21487770967485</v>
+        <v>75.68326398167484</v>
       </c>
       <c r="P81">
-        <v>389.6281079757929</v>
+        <v>397.337135903793</v>
       </c>
       <c r="Q81">
-        <v>714.328107975793</v>
+        <v>722.037135903793</v>
       </c>
       <c r="R81">
         <v>3.761904761904763</v>
       </c>
       <c r="S81">
-        <v>0.2068308362189435</v>
+        <v>0.2068006755349391</v>
       </c>
       <c r="T81">
         <v>2.216234900194944</v>
       </c>
       <c r="U81">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V81">
         <v>0.16</v>
       </c>
       <c r="W81">
-        <v>0.07532077932060501</v>
+        <v>0.072128779320605</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.141897768371391</v>
+        <v>3.280939878484801</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7978,13 +7978,13 @@
         <v>0.8</v>
       </c>
       <c r="B82">
-        <v>0.1031711641254549</v>
+        <v>0.100611241982077</v>
       </c>
       <c r="C82">
-        <v>374.7096111982255</v>
+        <v>490.6293594794411</v>
       </c>
       <c r="D82">
-        <v>2488.989611198225</v>
+        <v>2604.909359479441</v>
       </c>
       <c r="E82">
         <v>659.3799999999999</v>
@@ -8011,37 +8011,37 @@
         <v>680.4</v>
       </c>
       <c r="M82">
-        <v>219.2982423438301</v>
+        <v>210.00465834383</v>
       </c>
       <c r="N82">
-        <v>461.1017576561699</v>
+        <v>470.3953416561699</v>
       </c>
       <c r="O82">
-        <v>73.77628122498719</v>
+        <v>75.26325466498719</v>
       </c>
       <c r="P82">
-        <v>387.3254764311827</v>
+        <v>395.1320869911827</v>
       </c>
       <c r="Q82">
-        <v>712.0254764311828</v>
+        <v>719.8320869911828</v>
       </c>
       <c r="R82">
         <v>4.000000000000001</v>
       </c>
       <c r="S82">
-        <v>0.2145727033448543</v>
+        <v>0.2145410926279651</v>
       </c>
       <c r="T82">
         <v>2.322784655012009</v>
       </c>
       <c r="U82">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V82">
         <v>0.16</v>
       </c>
       <c r="W82">
-        <v>0.07532077932060501</v>
+        <v>0.072128779320605</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.102624046266748</v>
+        <v>3.239928130003742</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8060,13 +8060,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1034044369816536</v>
+        <v>0.1008126064385389</v>
       </c>
       <c r="C83">
-        <v>334.0592883877584</v>
+        <v>450.5235238978908</v>
       </c>
       <c r="D83">
-        <v>2478.910288387759</v>
+        <v>2595.374523897891</v>
       </c>
       <c r="E83">
         <v>689.9510000000002</v>
@@ -8093,37 +8093,37 @@
         <v>680.4</v>
       </c>
       <c r="M83">
-        <v>222.039470373128</v>
+        <v>212.629716573128</v>
       </c>
       <c r="N83">
-        <v>458.360529626872</v>
+        <v>467.770283426872</v>
       </c>
       <c r="O83">
-        <v>73.33768474029952</v>
+        <v>74.84324534829953</v>
       </c>
       <c r="P83">
-        <v>385.0228448865724</v>
+        <v>392.9270380785725</v>
       </c>
       <c r="Q83">
-        <v>709.7228448865725</v>
+        <v>717.6270380785725</v>
       </c>
       <c r="R83">
         <v>4.263157894736843</v>
       </c>
       <c r="S83">
-        <v>0.2231295038524398</v>
+        <v>0.2230962904676253</v>
       </c>
       <c r="T83">
         <v>2.440550173494028</v>
       </c>
       <c r="U83">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V83">
         <v>0.16</v>
       </c>
       <c r="W83">
-        <v>0.07532077932060501</v>
+        <v>0.072128779320605</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.064320045695553</v>
+        <v>3.199929017287646</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8142,13 +8142,13 @@
         <v>0.8200000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1036377098378524</v>
+        <v>0.1010139708950007</v>
       </c>
       <c r="C84">
-        <v>293.490270055881</v>
+        <v>410.4872350978262</v>
       </c>
       <c r="D84">
-        <v>2468.912270055881</v>
+        <v>2585.909235097826</v>
       </c>
       <c r="E84">
         <v>720.5220000000002</v>
@@ -8175,37 +8175,37 @@
         <v>680.4</v>
       </c>
       <c r="M84">
-        <v>224.7806984024258</v>
+        <v>215.2547748024258</v>
       </c>
       <c r="N84">
-        <v>455.6193015975741</v>
+        <v>465.1452251975742</v>
       </c>
       <c r="O84">
-        <v>72.89908825561186</v>
+        <v>74.42323603161186</v>
       </c>
       <c r="P84">
-        <v>382.7202133419623</v>
+        <v>390.7219891659623</v>
       </c>
       <c r="Q84">
-        <v>707.4202133419624</v>
+        <v>715.4219891659624</v>
       </c>
       <c r="R84">
         <v>4.555555555555557</v>
       </c>
       <c r="S84">
-        <v>0.2326370599719793</v>
+        <v>0.2326020658450256</v>
       </c>
       <c r="T84">
         <v>2.571400749585159</v>
       </c>
       <c r="U84">
-        <v>0.08966759442929167</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V84">
         <v>0.16</v>
       </c>
       <c r="W84">
-        <v>0.07532077932060501</v>
+        <v>0.072128779320605</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.02695028904073</v>
+        <v>3.160905492686577</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8224,13 +8224,13 @@
         <v>0.8300000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1103549426940511</v>
+        <v>0.1012153353514625</v>
       </c>
       <c r="C85">
-        <v>6.017816388880419</v>
+        <v>370.5197349362256</v>
       </c>
       <c r="D85">
-        <v>2212.01081638888</v>
+        <v>2576.512734936226</v>
       </c>
       <c r="E85">
         <v>751.0930000000001</v>
@@ -8257,45 +8257,45 @@
         <v>680.4</v>
       </c>
       <c r="M85">
-        <v>251.1196813317237</v>
+        <v>217.8798330317237</v>
       </c>
       <c r="N85">
-        <v>429.2803186682763</v>
+        <v>462.5201669682763</v>
       </c>
       <c r="O85">
-        <v>68.6848509869242</v>
+        <v>74.00322671492421</v>
       </c>
       <c r="P85">
-        <v>360.595467681352</v>
+        <v>388.5169402533521</v>
       </c>
       <c r="Q85">
-        <v>685.2954676813521</v>
+        <v>713.216940253352</v>
       </c>
       <c r="R85">
         <v>4.882352941176473</v>
       </c>
       <c r="S85">
-        <v>0.2432631521055824</v>
+        <v>0.2432261677374141</v>
       </c>
       <c r="T85">
         <v>2.717645511098778</v>
       </c>
       <c r="U85">
-        <v>0.09896759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V85">
         <v>0.16</v>
       </c>
       <c r="W85">
-        <v>0.083132779320605</v>
+        <v>0.072128779320605</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y85">
-        <v>2.709465050257077</v>
+        <v>3.12282229397951</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8306,13 +8306,13 @@
         <v>0.84</v>
       </c>
       <c r="B86">
-        <v>0.1106663355502499</v>
+        <v>0.1014166998079244</v>
       </c>
       <c r="C86">
-        <v>-35.17201015981982</v>
+        <v>330.6202762497301</v>
       </c>
       <c r="D86">
-        <v>2201.39198984018</v>
+        <v>2567.18427624973</v>
       </c>
       <c r="E86">
         <v>781.664</v>
@@ -8339,45 +8339,45 @@
         <v>680.4</v>
       </c>
       <c r="M86">
-        <v>254.1452196610216</v>
+        <v>220.5048912610216</v>
       </c>
       <c r="N86">
-        <v>426.2547803389784</v>
+        <v>459.8951087389784</v>
       </c>
       <c r="O86">
-        <v>68.20076485423655</v>
+        <v>73.58321739823656</v>
       </c>
       <c r="P86">
-        <v>358.0540154847419</v>
+        <v>386.3118913407419</v>
       </c>
       <c r="Q86">
-        <v>682.7540154847419</v>
+        <v>711.0118913407418</v>
       </c>
       <c r="R86">
         <v>5.249999999999999</v>
       </c>
       <c r="S86">
-        <v>0.2552175057558856</v>
+        <v>0.2551782823663511</v>
       </c>
       <c r="T86">
         <v>2.882170867801597</v>
       </c>
       <c r="U86">
-        <v>0.09896759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V86">
         <v>0.16</v>
       </c>
       <c r="W86">
-        <v>0.083132779320605</v>
+        <v>0.072128779320605</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.677209513944493</v>
+        <v>3.085645838098801</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8388,13 +8388,13 @@
         <v>0.85</v>
       </c>
       <c r="B87">
-        <v>0.1109777284064487</v>
+        <v>0.1016180642643862</v>
       </c>
       <c r="C87">
-        <v>-76.26037178148681</v>
+        <v>290.7881226565873</v>
       </c>
       <c r="D87">
-        <v>2190.874628218513</v>
+        <v>2557.923122656587</v>
       </c>
       <c r="E87">
         <v>812.2349999999999</v>
@@ -8421,45 +8421,45 @@
         <v>680.4</v>
       </c>
       <c r="M87">
-        <v>257.1707579903194</v>
+        <v>223.1299494903194</v>
       </c>
       <c r="N87">
-        <v>423.2292420096805</v>
+        <v>457.2700505096806</v>
       </c>
       <c r="O87">
-        <v>67.71667872154889</v>
+        <v>73.16320808154889</v>
       </c>
       <c r="P87">
-        <v>355.5125632881317</v>
+        <v>384.1068424281317</v>
       </c>
       <c r="Q87">
-        <v>680.2125632881317</v>
+        <v>708.8068424281317</v>
       </c>
       <c r="R87">
         <v>5.666666666666666</v>
       </c>
       <c r="S87">
-        <v>0.2687657732262294</v>
+        <v>0.2687240122791464</v>
       </c>
       <c r="T87">
         <v>3.06863293873146</v>
       </c>
       <c r="U87">
-        <v>0.09896759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V87">
         <v>0.16</v>
       </c>
       <c r="W87">
-        <v>0.083132779320605</v>
+        <v>0.072128779320605</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y87">
-        <v>2.645712931427499</v>
+        <v>3.049344122356463</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8470,13 +8470,13 @@
         <v>0.86</v>
       </c>
       <c r="B88">
-        <v>0.1112891212626474</v>
+        <v>0.1018194287208481</v>
       </c>
       <c r="C88">
-        <v>-117.2487158365129</v>
+        <v>251.0225483628797</v>
       </c>
       <c r="D88">
-        <v>2180.457284163487</v>
+        <v>2548.728548362879</v>
       </c>
       <c r="E88">
         <v>842.8059999999998</v>
@@ -8503,45 +8503,45 @@
         <v>680.4</v>
       </c>
       <c r="M88">
-        <v>260.1962963196173</v>
+        <v>225.7550077196173</v>
       </c>
       <c r="N88">
-        <v>420.2037036803827</v>
+        <v>454.6449922803827</v>
       </c>
       <c r="O88">
-        <v>67.23259258886122</v>
+        <v>72.74319876486123</v>
       </c>
       <c r="P88">
-        <v>352.9711110915214</v>
+        <v>381.9017935155214</v>
       </c>
       <c r="Q88">
-        <v>677.6711110915214</v>
+        <v>706.6017935155214</v>
       </c>
       <c r="R88">
         <v>6.142857142857142</v>
       </c>
       <c r="S88">
-        <v>0.2842495074780509</v>
+        <v>0.2842048464651983</v>
       </c>
       <c r="T88">
         <v>3.281732448365589</v>
       </c>
       <c r="U88">
-        <v>0.09896759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V88">
         <v>0.16</v>
       </c>
       <c r="W88">
-        <v>0.083132779320605</v>
+        <v>0.072128779320605</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y88">
-        <v>2.614948827573691</v>
+        <v>3.01388663256162</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8552,13 +8552,13 @@
         <v>0.87</v>
       </c>
       <c r="B89">
-        <v>0.1116005141188462</v>
+        <v>0.1077210331773099</v>
       </c>
       <c r="C89">
-        <v>-158.1384622874721</v>
+        <v>-22.46409737995828</v>
       </c>
       <c r="D89">
-        <v>2170.138537712528</v>
+        <v>2305.812902620042</v>
       </c>
       <c r="E89">
         <v>873.3770000000002</v>
@@ -8585,37 +8585,37 @@
         <v>680.4</v>
       </c>
       <c r="M89">
-        <v>263.2218346489152</v>
+        <v>249.1255465489152</v>
       </c>
       <c r="N89">
-        <v>417.1781653510848</v>
+        <v>431.2744534510848</v>
       </c>
       <c r="O89">
-        <v>66.74850645617356</v>
+        <v>69.00391255217356</v>
       </c>
       <c r="P89">
-        <v>350.4296588949112</v>
+        <v>362.2705408989112</v>
       </c>
       <c r="Q89">
-        <v>675.1296588949112</v>
+        <v>686.9705408989112</v>
       </c>
       <c r="R89">
         <v>6.692307692307692</v>
       </c>
       <c r="S89">
-        <v>0.3021153546916911</v>
+        <v>0.3020673474491043</v>
       </c>
       <c r="T89">
         <v>3.527616497943431</v>
       </c>
       <c r="U89">
-        <v>0.09896759442929168</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V89">
         <v>0.16</v>
       </c>
       <c r="W89">
-        <v>0.083132779320605</v>
+        <v>0.07868077932060501</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.584891944498131</v>
+        <v>2.731153064892143</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8634,13 +8634,13 @@
         <v>0.88</v>
       </c>
       <c r="B90">
-        <v>0.111911906975045</v>
+        <v>0.1079879176337718</v>
       </c>
       <c r="C90">
-        <v>-198.931004344342</v>
+        <v>-62.93067913657069</v>
       </c>
       <c r="D90">
-        <v>2159.916995655658</v>
+        <v>2295.917320863429</v>
       </c>
       <c r="E90">
         <v>903.9480000000001</v>
@@ -8667,37 +8667,37 @@
         <v>680.4</v>
       </c>
       <c r="M90">
-        <v>266.2473729782131</v>
+        <v>251.9890585782131</v>
       </c>
       <c r="N90">
-        <v>414.1526270217869</v>
+        <v>428.4109414217869</v>
       </c>
       <c r="O90">
-        <v>66.26442032348591</v>
+        <v>68.5457506274859</v>
       </c>
       <c r="P90">
-        <v>347.888206698301</v>
+        <v>359.865190794301</v>
       </c>
       <c r="Q90">
-        <v>672.5882066983011</v>
+        <v>684.5651907943011</v>
       </c>
       <c r="R90">
         <v>7.333333333333334</v>
       </c>
       <c r="S90">
-        <v>0.3229588431076046</v>
+        <v>0.3229069319303279</v>
       </c>
       <c r="T90">
         <v>3.814481222450913</v>
       </c>
       <c r="U90">
-        <v>0.09896759442929168</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V90">
         <v>0.16</v>
       </c>
       <c r="W90">
-        <v>0.083132779320605</v>
+        <v>0.07868077932060501</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.555518172401562</v>
+        <v>2.700117234609277</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8716,13 +8716,13 @@
         <v>0.89</v>
       </c>
       <c r="B91">
-        <v>0.1122232998312437</v>
+        <v>0.1082548020902336</v>
       </c>
       <c r="C91">
-        <v>-239.6277090915955</v>
+        <v>-103.312688470563</v>
       </c>
       <c r="D91">
-        <v>2149.791290908404</v>
+        <v>2286.106311529437</v>
       </c>
       <c r="E91">
         <v>934.519</v>
@@ -8749,37 +8749,37 @@
         <v>680.4</v>
       </c>
       <c r="M91">
-        <v>269.2729113075109</v>
+        <v>254.852570607511</v>
       </c>
       <c r="N91">
-        <v>411.1270886924891</v>
+        <v>425.547429392489</v>
       </c>
       <c r="O91">
-        <v>65.78033419079824</v>
+        <v>68.08758870279824</v>
       </c>
       <c r="P91">
-        <v>345.3467545016908</v>
+        <v>357.4598406896907</v>
       </c>
       <c r="Q91">
-        <v>670.0467545016909</v>
+        <v>682.1598406896908</v>
       </c>
       <c r="R91">
         <v>8.090909090909092</v>
       </c>
       <c r="S91">
-        <v>0.3475920566900479</v>
+        <v>0.347535531771774</v>
       </c>
       <c r="T91">
         <v>4.153503169596118</v>
       </c>
       <c r="U91">
-        <v>0.09896759442929168</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V91">
         <v>0.16</v>
       </c>
       <c r="W91">
-        <v>0.083132779320605</v>
+        <v>0.07868077932060501</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.526804485071207</v>
+        <v>2.669778838714791</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>0.9</v>
       </c>
       <c r="B92">
-        <v>0.1160878926874425</v>
+        <v>0.1085216865466954</v>
       </c>
       <c r="C92">
-        <v>-388.399266079517</v>
+        <v>-143.6112049637986</v>
       </c>
       <c r="D92">
-        <v>2031.590733920483</v>
+        <v>2276.378795036201</v>
       </c>
       <c r="E92">
         <v>965.0899999999999</v>
@@ -8831,45 +8831,45 @@
         <v>680.4</v>
       </c>
       <c r="M92">
-        <v>285.2299826368089</v>
+        <v>257.7160826368088</v>
       </c>
       <c r="N92">
-        <v>395.1700173631911</v>
+        <v>422.6839173631911</v>
       </c>
       <c r="O92">
-        <v>63.22720277811058</v>
+        <v>67.62942677811058</v>
       </c>
       <c r="P92">
-        <v>331.9428145850806</v>
+        <v>355.0544905850805</v>
       </c>
       <c r="Q92">
-        <v>656.6428145850806</v>
+        <v>679.7544905850806</v>
       </c>
       <c r="R92">
         <v>9.000000000000002</v>
       </c>
       <c r="S92">
-        <v>0.3771519129889799</v>
+        <v>0.3770898515815094</v>
       </c>
       <c r="T92">
         <v>4.560329506170365</v>
       </c>
       <c r="U92">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V92">
         <v>0.16</v>
       </c>
       <c r="W92">
-        <v>0.08708077932060501</v>
+        <v>0.07868077932060501</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y92">
-        <v>2.385443471650636</v>
+        <v>2.640114629395738</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8880,13 +8880,13 @@
         <v>0.91</v>
       </c>
       <c r="B93">
-        <v>0.1164387655436413</v>
+        <v>0.1087885710031573</v>
       </c>
       <c r="C93">
-        <v>-429.0614679564414</v>
+        <v>-183.8272899012559</v>
       </c>
       <c r="D93">
-        <v>2021.499532043558</v>
+        <v>2266.733710098744</v>
       </c>
       <c r="E93">
         <v>995.6609999999998</v>
@@ -8913,45 +8913,45 @@
         <v>680.4</v>
       </c>
       <c r="M93">
-        <v>288.3992046661067</v>
+        <v>260.5795946661067</v>
       </c>
       <c r="N93">
-        <v>392.0007953338933</v>
+        <v>419.8204053338933</v>
       </c>
       <c r="O93">
-        <v>62.72012725342292</v>
+        <v>67.17126485342293</v>
       </c>
       <c r="P93">
-        <v>329.2806680804704</v>
+        <v>352.6491404804704</v>
       </c>
       <c r="Q93">
-        <v>653.9806680804704</v>
+        <v>677.3491404804704</v>
       </c>
       <c r="R93">
         <v>10.11111111111111</v>
       </c>
       <c r="S93">
-        <v>0.4132806262432301</v>
+        <v>0.4132117980156304</v>
       </c>
       <c r="T93">
         <v>5.057561695316667</v>
       </c>
       <c r="U93">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V93">
         <v>0.16</v>
       </c>
       <c r="W93">
-        <v>0.08708077932060501</v>
+        <v>0.07868077932060501</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.359229807127003</v>
+        <v>2.61110238072106</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8962,13 +8962,13 @@
         <v>0.92</v>
       </c>
       <c r="B94">
-        <v>0.11678963839984</v>
+        <v>0.1090554554596191</v>
       </c>
       <c r="C94">
-        <v>-469.6239164354101</v>
+        <v>-223.9619866570183</v>
       </c>
       <c r="D94">
-        <v>2011.50808356459</v>
+        <v>2257.170013342982</v>
       </c>
       <c r="E94">
         <v>1026.232</v>
@@ -8995,45 +8995,45 @@
         <v>680.4</v>
       </c>
       <c r="M94">
-        <v>291.5684266954046</v>
+        <v>263.4431066954046</v>
       </c>
       <c r="N94">
-        <v>388.8315733045953</v>
+        <v>416.9568933045954</v>
       </c>
       <c r="O94">
-        <v>62.21305172873526</v>
+        <v>66.71310292873527</v>
       </c>
       <c r="P94">
-        <v>326.6185215758601</v>
+        <v>350.2437903758601</v>
       </c>
       <c r="Q94">
-        <v>651.3185215758601</v>
+        <v>674.9437903758601</v>
       </c>
       <c r="R94">
         <v>11.50000000000001</v>
       </c>
       <c r="S94">
-        <v>0.4584415178110429</v>
+        <v>0.4583642310582817</v>
       </c>
       <c r="T94">
         <v>5.679101931749545</v>
       </c>
       <c r="U94">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V94">
         <v>0.16</v>
       </c>
       <c r="W94">
-        <v>0.08708077932060501</v>
+        <v>0.07868077932060501</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y94">
-        <v>2.333586004875622</v>
+        <v>2.582720833104526</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9044,13 +9044,13 @@
         <v>0.93</v>
       </c>
       <c r="B95">
-        <v>0.1171405112560388</v>
+        <v>0.109322339916081</v>
       </c>
       <c r="C95">
-        <v>-510.0880833628821</v>
+        <v>-264.0163210705309</v>
       </c>
       <c r="D95">
-        <v>2001.614916637118</v>
+        <v>2247.686678929469</v>
       </c>
       <c r="E95">
         <v>1056.803</v>
@@ -9077,45 +9077,45 @@
         <v>680.4</v>
       </c>
       <c r="M95">
-        <v>294.7376487247025</v>
+        <v>266.3066187247024</v>
       </c>
       <c r="N95">
-        <v>385.6623512752975</v>
+        <v>414.0933812752975</v>
       </c>
       <c r="O95">
-        <v>61.7059762040476</v>
+        <v>66.25494100404761</v>
       </c>
       <c r="P95">
-        <v>323.9563750712499</v>
+        <v>347.8384402712499</v>
       </c>
       <c r="Q95">
-        <v>648.65637507125</v>
+        <v>672.53844027125</v>
       </c>
       <c r="R95">
         <v>13.2857142857143</v>
       </c>
       <c r="S95">
-        <v>0.5165055212553734</v>
+        <v>0.5164173592559761</v>
       </c>
       <c r="T95">
         <v>6.478225092877531</v>
       </c>
       <c r="U95">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V95">
         <v>0.16</v>
       </c>
       <c r="W95">
-        <v>0.08708077932060501</v>
+        <v>0.07868077932060501</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y95">
-        <v>2.308493682242551</v>
+        <v>2.554949641350714</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9126,13 +9126,13 @@
         <v>0.9400000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1174913841122376</v>
+        <v>0.1095892243725428</v>
       </c>
       <c r="C96">
-        <v>-550.4554117712028</v>
+        <v>-303.9913018134102</v>
       </c>
       <c r="D96">
-        <v>1991.818588228797</v>
+        <v>2238.28269818659</v>
       </c>
       <c r="E96">
         <v>1087.374</v>
@@ -9159,45 +9159,45 @@
         <v>680.4</v>
       </c>
       <c r="M96">
-        <v>297.9068707540004</v>
+        <v>269.1701307540004</v>
       </c>
       <c r="N96">
-        <v>382.4931292459996</v>
+        <v>411.2298692459996</v>
       </c>
       <c r="O96">
-        <v>61.19890067935994</v>
+        <v>65.79677907935994</v>
       </c>
       <c r="P96">
-        <v>321.2942285666397</v>
+        <v>345.4330901666397</v>
       </c>
       <c r="Q96">
-        <v>645.9942285666398</v>
+        <v>670.1330901666397</v>
       </c>
       <c r="R96">
         <v>15.66666666666668</v>
       </c>
       <c r="S96">
-        <v>0.5939241925144811</v>
+        <v>0.5938215301862355</v>
       </c>
       <c r="T96">
         <v>7.54372264104818</v>
       </c>
       <c r="U96">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V96">
         <v>0.16</v>
       </c>
       <c r="W96">
-        <v>0.08708077932060501</v>
+        <v>0.07868077932060501</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y96">
-        <v>2.283935238814439</v>
+        <v>2.527769326017196</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9208,13 +9208,13 @@
         <v>0.9500000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1178422569684363</v>
+        <v>0.1098561088290047</v>
       </c>
       <c r="C97">
-        <v>-590.7273165802762</v>
+        <v>-343.8879207470882</v>
       </c>
       <c r="D97">
-        <v>1982.117683419724</v>
+        <v>2228.957079252912</v>
       </c>
       <c r="E97">
         <v>1117.945</v>
@@ -9241,45 +9241,45 @@
         <v>680.4</v>
       </c>
       <c r="M97">
-        <v>301.0760927832982</v>
+        <v>272.0336427832982</v>
       </c>
       <c r="N97">
-        <v>379.3239072167017</v>
+        <v>408.3663572167018</v>
       </c>
       <c r="O97">
-        <v>60.69182515467228</v>
+        <v>65.33861715467228</v>
       </c>
       <c r="P97">
-        <v>318.6320820620294</v>
+        <v>343.0277400620295</v>
       </c>
       <c r="Q97">
-        <v>643.3320820620295</v>
+        <v>667.7277400620295</v>
       </c>
       <c r="R97">
         <v>19.00000000000003</v>
       </c>
       <c r="S97">
-        <v>0.7023103322772319</v>
+        <v>0.7021873694885988</v>
       </c>
       <c r="T97">
         <v>9.03541920848709</v>
       </c>
       <c r="U97">
-        <v>0.1036675944292917</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V97">
         <v>0.16</v>
       </c>
       <c r="W97">
-        <v>0.08708077932060501</v>
+        <v>0.07868077932060501</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.259893815247971</v>
+        <v>2.501161227848594</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9290,13 +9290,13 @@
         <v>0.96</v>
       </c>
       <c r="B98">
-        <v>0.1181931298246351</v>
+        <v>0.1132679532854665</v>
       </c>
       <c r="C98">
-        <v>-630.905185278843</v>
+        <v>-487.1769518153078</v>
       </c>
       <c r="D98">
-        <v>1972.510814721157</v>
+        <v>2116.239048184692</v>
       </c>
       <c r="E98">
         <v>1148.516</v>
@@ -9323,37 +9323,37 @@
         <v>680.4</v>
       </c>
       <c r="M98">
-        <v>304.2453148125961</v>
+        <v>286.342937212596</v>
       </c>
       <c r="N98">
-        <v>376.1546851874039</v>
+        <v>394.0570627874039</v>
       </c>
       <c r="O98">
-        <v>60.18474962998462</v>
+        <v>63.04913004598463</v>
       </c>
       <c r="P98">
-        <v>315.9699355574193</v>
+        <v>331.0079327414193</v>
       </c>
       <c r="Q98">
-        <v>640.6699355574193</v>
+        <v>655.7079327414194</v>
       </c>
       <c r="R98">
         <v>23.99999999999998</v>
       </c>
       <c r="S98">
-        <v>0.864889541921356</v>
+        <v>0.8647361284421415</v>
       </c>
       <c r="T98">
         <v>11.27296405964542</v>
       </c>
       <c r="U98">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V98">
         <v>0.16</v>
       </c>
       <c r="W98">
-        <v>0.08708077932060501</v>
+        <v>0.08195677932060501</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.236353254672471</v>
+        <v>2.376171756228215</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9372,13 +9372,13 @@
         <v>0.97</v>
       </c>
       <c r="B99">
-        <v>0.1185440026808338</v>
+        <v>0.1135675977419283</v>
       </c>
       <c r="C99">
-        <v>-670.990378586032</v>
+        <v>-527.1052157654258</v>
       </c>
       <c r="D99">
-        <v>1962.996621413968</v>
+        <v>2106.881784234574</v>
       </c>
       <c r="E99">
         <v>1179.087</v>
@@ -9405,37 +9405,37 @@
         <v>680.4</v>
       </c>
       <c r="M99">
-        <v>307.4145368418939</v>
+        <v>289.325676141894</v>
       </c>
       <c r="N99">
-        <v>372.985463158106</v>
+        <v>391.074323858106</v>
       </c>
       <c r="O99">
-        <v>59.67767410529697</v>
+        <v>62.57189181729697</v>
       </c>
       <c r="P99">
-        <v>313.3077890528091</v>
+        <v>328.5024320408091</v>
       </c>
       <c r="Q99">
-        <v>638.0077890528091</v>
+        <v>653.2024320408091</v>
       </c>
       <c r="R99">
         <v>32.33333333333331</v>
       </c>
       <c r="S99">
-        <v>1.135854891328232</v>
+        <v>1.135650726698049</v>
       </c>
       <c r="T99">
         <v>15.00220547824268</v>
       </c>
       <c r="U99">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V99">
         <v>0.16</v>
       </c>
       <c r="W99">
-        <v>0.08708077932060501</v>
+        <v>0.08195677932060501</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.213298066479972</v>
+        <v>2.351675140184625</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9454,13 +9454,13 @@
         <v>0.98</v>
       </c>
       <c r="B100">
-        <v>0.1188948755370326</v>
+        <v>0.1138672421983902</v>
       </c>
       <c r="C100">
-        <v>-710.9842310938679</v>
+        <v>-566.9510949389683</v>
       </c>
       <c r="D100">
-        <v>1953.573768906132</v>
+        <v>2097.606905061032</v>
       </c>
       <c r="E100">
         <v>1209.658</v>
@@ -9487,37 +9487,37 @@
         <v>680.4</v>
       </c>
       <c r="M100">
-        <v>310.5837588711919</v>
+        <v>292.3084150711919</v>
       </c>
       <c r="N100">
-        <v>369.8162411288081</v>
+        <v>388.0915849288081</v>
       </c>
       <c r="O100">
-        <v>59.17059858060929</v>
+        <v>62.0946535886093</v>
       </c>
       <c r="P100">
-        <v>310.6456425481988</v>
+        <v>325.9969313401988</v>
       </c>
       <c r="Q100">
-        <v>635.3456425481988</v>
+        <v>650.6969313401989</v>
       </c>
       <c r="R100">
         <v>48.99999999999996</v>
       </c>
       <c r="S100">
-        <v>1.677785590141983</v>
+        <v>1.677479923209862</v>
       </c>
       <c r="T100">
         <v>22.4606883154372</v>
       </c>
       <c r="U100">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V100">
         <v>0.16</v>
       </c>
       <c r="W100">
-        <v>0.08708077932060501</v>
+        <v>0.08195677932060501</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,7 +9525,7 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.190713392332217</v>
+        <v>2.3276784550807</v>
       </c>
       <c r="Z100">
         <v>0</v>
@@ -9536,13 +9536,13 @@
         <v>0.99</v>
       </c>
       <c r="B101">
-        <v>0.1192457483932314</v>
+        <v>0.114166886654852</v>
       </c>
       <c r="C101">
-        <v>-750.8880518913511</v>
+        <v>-606.7156725858604</v>
       </c>
       <c r="D101">
-        <v>1944.240948108649</v>
+        <v>2088.41332741414</v>
       </c>
       <c r="E101">
         <v>1240.229</v>
@@ -9569,37 +9569,37 @@
         <v>680.4</v>
       </c>
       <c r="M101">
-        <v>313.7529809004897</v>
+        <v>295.2911540004897</v>
       </c>
       <c r="N101">
-        <v>366.6470190995103</v>
+        <v>385.1088459995103</v>
       </c>
       <c r="O101">
-        <v>58.66352305592164</v>
+        <v>61.61741535992164</v>
       </c>
       <c r="P101">
-        <v>307.9834960435886</v>
+        <v>323.4914306395886</v>
       </c>
       <c r="Q101">
-        <v>632.6834960435887</v>
+        <v>648.1914306395886</v>
       </c>
       <c r="R101">
         <v>98.99999999999991</v>
       </c>
       <c r="S101">
-        <v>3.303577686583238</v>
+        <v>3.302967512745304</v>
       </c>
       <c r="T101">
         <v>44.83613682702074</v>
       </c>
       <c r="U101">
-        <v>0.1036675944292917</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V101">
         <v>0.16</v>
       </c>
       <c r="W101">
-        <v>0.08708077932060501</v>
+        <v>0.08195677932060501</v>
       </c>
       <c r="X101" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         </is>
       </c>
       <c r="Y101">
-        <v>2.168584974227851</v>
+        <v>2.304166551494027</v>
       </c>
       <c r="Z101">
         <v>0</v>

--- a/research/traditional_assets/database/data/romania/romania_telecom_services.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_telecom_services.xlsx
@@ -1133,43 +1133,43 @@
         <v>9.307797537619701</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>308.826553016332</v>
       </c>
       <c r="G2">
         <v>1.77723609591085</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.0304158790170132</v>
       </c>
       <c r="I2">
         <v>0.58431192960649</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>1270.8</v>
       </c>
       <c r="L2">
-        <v>4020.56340108978</v>
+        <v>3981.86559945425</v>
       </c>
       <c r="M2">
         <v>2725.7</v>
       </c>
       <c r="N2">
-        <v>3689.16340108978</v>
+        <v>3681.03659945425</v>
       </c>
       <c r="O2">
         <v>1786.3</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>30.571</v>
       </c>
       <c r="Q2">
         <v>0.09818225675745861</v>
       </c>
       <c r="R2">
-        <v>0.08450208546512961</v>
+        <v>0.0845875299215914</v>
       </c>
       <c r="S2">
         <v>0.07540477932060501</v>
@@ -1191,13 +1191,13 @@
         <v>0.130199417558097</v>
       </c>
       <c r="X2">
-        <v>0.08450208546512961</v>
+        <v>0.0848304667963489</v>
       </c>
       <c r="Y2">
         <v>1.16178975104852</v>
       </c>
       <c r="Z2">
-        <v>0.532748774085323</v>
+        <v>0.537269066713926</v>
       </c>
       <c r="AA2">
         <v>1786.3</v>
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08450208546512961</v>
+        <v>0.08458752992159144</v>
       </c>
       <c r="C2">
-        <v>4020.56340108978</v>
+        <v>3981.865599454249</v>
       </c>
       <c r="D2">
-        <v>3689.16340108978</v>
+        <v>3681.036599454249</v>
       </c>
       <c r="E2">
-        <v>-1786.3</v>
+        <v>-1755.729</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>30.571</v>
       </c>
       <c r="G2">
         <v>331.4</v>
@@ -1451,28 +1451,28 @@
         <v>680.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.203178429297876</v>
       </c>
       <c r="N2">
-        <v>680.4</v>
+        <v>678.1968215707021</v>
       </c>
       <c r="O2">
-        <v>108.864</v>
+        <v>108.5114914513123</v>
       </c>
       <c r="P2">
-        <v>571.5359999999999</v>
+        <v>569.6853301193898</v>
       </c>
       <c r="Q2">
-        <v>896.236</v>
+        <v>894.3853301193899</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08450208546512961</v>
+        <v>0.08483046679634887</v>
       </c>
       <c r="T2">
-        <v>0.532748774085323</v>
+        <v>0.5372690667139257</v>
       </c>
       <c r="U2">
         <v>0.07206759442929168</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>308.8265530163322</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08458752992159144</v>
+        <v>0.0846729743780533</v>
       </c>
       <c r="C3">
-        <v>3981.865599454249</v>
+        <v>3943.203523932275</v>
       </c>
       <c r="D3">
-        <v>3681.036599454249</v>
+        <v>3672.945523932275</v>
       </c>
       <c r="E3">
-        <v>-1755.729</v>
+        <v>-1725.158</v>
       </c>
       <c r="F3">
-        <v>30.571</v>
+        <v>61.142</v>
       </c>
       <c r="G3">
         <v>331.4</v>
@@ -1533,28 +1533,28 @@
         <v>680.4</v>
       </c>
       <c r="M3">
-        <v>2.203178429297876</v>
+        <v>4.406356858595752</v>
       </c>
       <c r="N3">
-        <v>678.1968215707021</v>
+        <v>675.9936431414043</v>
       </c>
       <c r="O3">
-        <v>108.5114914513123</v>
+        <v>108.1589829026247</v>
       </c>
       <c r="P3">
-        <v>569.6853301193898</v>
+        <v>567.8346602387796</v>
       </c>
       <c r="Q3">
-        <v>894.3853301193899</v>
+        <v>892.5346602387797</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08483046679634887</v>
+        <v>0.08516554978738897</v>
       </c>
       <c r="T3">
-        <v>0.5372690667139257</v>
+        <v>0.5418816102124999</v>
       </c>
       <c r="U3">
         <v>0.07206759442929168</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>308.8265530163322</v>
+        <v>154.4132765081661</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.0846729743780533</v>
+        <v>0.08475841883451513</v>
       </c>
       <c r="C4">
-        <v>3943.203523932275</v>
+        <v>3904.576939457982</v>
       </c>
       <c r="D4">
-        <v>3672.945523932275</v>
+        <v>3664.889939457983</v>
       </c>
       <c r="E4">
-        <v>-1725.158</v>
+        <v>-1694.587</v>
       </c>
       <c r="F4">
-        <v>61.142</v>
+        <v>91.71299999999999</v>
       </c>
       <c r="G4">
         <v>331.4</v>
@@ -1615,28 +1615,28 @@
         <v>680.4</v>
       </c>
       <c r="M4">
-        <v>4.406356858595752</v>
+        <v>6.609535287893628</v>
       </c>
       <c r="N4">
-        <v>675.9936431414043</v>
+        <v>673.7904647121063</v>
       </c>
       <c r="O4">
-        <v>108.1589829026247</v>
+        <v>107.806474353937</v>
       </c>
       <c r="P4">
-        <v>567.8346602387796</v>
+        <v>565.9839903581693</v>
       </c>
       <c r="Q4">
-        <v>892.5346602387797</v>
+        <v>890.6839903581694</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08516554978738897</v>
+        <v>0.08550754170607935</v>
       </c>
       <c r="T4">
-        <v>0.5418816102124999</v>
+        <v>0.5465892577007354</v>
       </c>
       <c r="U4">
         <v>0.07206759442929168</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>154.4132765081661</v>
+        <v>102.9421843387774</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08475841883451513</v>
+        <v>0.08484386329097696</v>
       </c>
       <c r="C5">
-        <v>3904.576939457982</v>
+        <v>3865.985613023181</v>
       </c>
       <c r="D5">
-        <v>3664.889939457983</v>
+        <v>3656.869613023181</v>
       </c>
       <c r="E5">
-        <v>-1694.587</v>
+        <v>-1664.016</v>
       </c>
       <c r="F5">
-        <v>91.71299999999999</v>
+        <v>122.284</v>
       </c>
       <c r="G5">
         <v>331.4</v>
@@ -1697,28 +1697,28 @@
         <v>680.4</v>
       </c>
       <c r="M5">
-        <v>6.609535287893628</v>
+        <v>8.812713717191503</v>
       </c>
       <c r="N5">
-        <v>673.7904647121063</v>
+        <v>671.5872862828085</v>
       </c>
       <c r="O5">
-        <v>107.806474353937</v>
+        <v>107.4539658052494</v>
       </c>
       <c r="P5">
-        <v>565.9839903581693</v>
+        <v>564.1333204775591</v>
       </c>
       <c r="Q5">
-        <v>890.6839903581694</v>
+        <v>888.8333204775591</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08550754170607935</v>
+        <v>0.08585665845640914</v>
       </c>
       <c r="T5">
-        <v>0.5465892577007354</v>
+        <v>0.5513949811783092</v>
       </c>
       <c r="U5">
         <v>0.07206759442929168</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>102.9421843387774</v>
+        <v>77.20663825408306</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08484386329097696</v>
+        <v>0.0849293077474388</v>
       </c>
       <c r="C6">
-        <v>3865.985613023181</v>
+        <v>3827.429313654907</v>
       </c>
       <c r="D6">
-        <v>3656.869613023181</v>
+        <v>3648.884313654907</v>
       </c>
       <c r="E6">
-        <v>-1664.016</v>
+        <v>-1633.445</v>
       </c>
       <c r="F6">
-        <v>122.284</v>
+        <v>152.855</v>
       </c>
       <c r="G6">
         <v>331.4</v>
@@ -1779,28 +1779,28 @@
         <v>680.4</v>
       </c>
       <c r="M6">
-        <v>8.812713717191503</v>
+        <v>11.01589214648938</v>
       </c>
       <c r="N6">
-        <v>671.5872862828085</v>
+        <v>669.3841078535106</v>
       </c>
       <c r="O6">
-        <v>107.4539658052494</v>
+        <v>107.1014572565617</v>
       </c>
       <c r="P6">
-        <v>564.1333204775591</v>
+        <v>562.2826505969489</v>
       </c>
       <c r="Q6">
-        <v>888.8333204775591</v>
+        <v>886.9826505969489</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08585665845640914</v>
+        <v>0.08621312503306164</v>
       </c>
       <c r="T6">
-        <v>0.5513949811783092</v>
+        <v>0.5563018777817267</v>
       </c>
       <c r="U6">
         <v>0.07206759442929168</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>77.20663825408306</v>
+        <v>61.76531060326644</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0849293077474388</v>
+        <v>0.08501475220390065</v>
       </c>
       <c r="C7">
-        <v>3827.429313654907</v>
+        <v>3788.907812393258</v>
       </c>
       <c r="D7">
-        <v>3648.884313654907</v>
+        <v>3640.933812393258</v>
       </c>
       <c r="E7">
-        <v>-1633.445</v>
+        <v>-1602.874</v>
       </c>
       <c r="F7">
-        <v>152.855</v>
+        <v>183.426</v>
       </c>
       <c r="G7">
         <v>331.4</v>
@@ -1861,28 +1861,28 @@
         <v>680.4</v>
       </c>
       <c r="M7">
-        <v>11.01589214648938</v>
+        <v>13.21907057578726</v>
       </c>
       <c r="N7">
-        <v>669.3841078535106</v>
+        <v>667.1809294242128</v>
       </c>
       <c r="O7">
-        <v>107.1014572565617</v>
+        <v>106.748948707874</v>
       </c>
       <c r="P7">
-        <v>562.2826505969489</v>
+        <v>560.4319807163387</v>
       </c>
       <c r="Q7">
-        <v>886.9826505969489</v>
+        <v>885.1319807163387</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08621312503306164</v>
+        <v>0.08657717600496208</v>
       </c>
       <c r="T7">
-        <v>0.5563018777817267</v>
+        <v>0.561313176440536</v>
       </c>
       <c r="U7">
         <v>0.07206759442929168</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>61.76531060326644</v>
+        <v>51.47109216938869</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08501475220390065</v>
+        <v>0.0851001966603625</v>
       </c>
       <c r="C8">
-        <v>3788.907812393258</v>
+        <v>3750.420882269495</v>
       </c>
       <c r="D8">
-        <v>3640.933812393258</v>
+        <v>3633.017882269495</v>
       </c>
       <c r="E8">
-        <v>-1602.874</v>
+        <v>-1572.303</v>
       </c>
       <c r="F8">
-        <v>183.426</v>
+        <v>213.997</v>
       </c>
       <c r="G8">
         <v>331.4</v>
@@ -1943,28 +1943,28 @@
         <v>680.4</v>
       </c>
       <c r="M8">
-        <v>13.21907057578726</v>
+        <v>15.42224900508513</v>
       </c>
       <c r="N8">
-        <v>667.1809294242128</v>
+        <v>664.9777509949148</v>
       </c>
       <c r="O8">
-        <v>106.748948707874</v>
+        <v>106.3964401591864</v>
       </c>
       <c r="P8">
-        <v>560.4319807163387</v>
+        <v>558.5813108357285</v>
       </c>
       <c r="Q8">
-        <v>885.1319807163387</v>
+        <v>883.2813108357285</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08657717600496208</v>
+        <v>0.08694905603002166</v>
       </c>
       <c r="T8">
-        <v>0.561313176440536</v>
+        <v>0.5664322449629756</v>
       </c>
       <c r="U8">
         <v>0.07206759442929168</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>51.4710921693887</v>
+        <v>44.11807900233317</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08510019666036249</v>
+        <v>0.08518564111682435</v>
       </c>
       <c r="C9">
-        <v>3750.420882269497</v>
+        <v>3711.968298284461</v>
       </c>
       <c r="D9">
-        <v>3633.017882269497</v>
+        <v>3625.136298284461</v>
       </c>
       <c r="E9">
-        <v>-1572.303</v>
+        <v>-1541.732</v>
       </c>
       <c r="F9">
-        <v>213.997</v>
+        <v>244.568</v>
       </c>
       <c r="G9">
         <v>331.4</v>
@@ -2025,28 +2025,28 @@
         <v>680.4</v>
       </c>
       <c r="M9">
-        <v>15.42224900508513</v>
+        <v>17.62542743438301</v>
       </c>
       <c r="N9">
-        <v>664.9777509949148</v>
+        <v>662.7745725656169</v>
       </c>
       <c r="O9">
-        <v>106.3964401591864</v>
+        <v>106.0439316104987</v>
       </c>
       <c r="P9">
-        <v>558.5813108357285</v>
+        <v>556.7306409551182</v>
       </c>
       <c r="Q9">
-        <v>883.2813108357285</v>
+        <v>881.4306409551183</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08694905603002166</v>
+        <v>0.08732902040345211</v>
       </c>
       <c r="T9">
-        <v>0.5664322449629756</v>
+        <v>0.5716625975837292</v>
       </c>
       <c r="U9">
         <v>0.07206759442929168</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>44.11807900233316</v>
+        <v>38.60331912704152</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08518564111682435</v>
+        <v>0.08527108557328618</v>
       </c>
       <c r="C10">
-        <v>3711.968298284461</v>
+        <v>3673.549837387246</v>
       </c>
       <c r="D10">
-        <v>3625.136298284461</v>
+        <v>3617.288837387247</v>
       </c>
       <c r="E10">
-        <v>-1541.732</v>
+        <v>-1511.161</v>
       </c>
       <c r="F10">
-        <v>244.568</v>
+        <v>275.139</v>
       </c>
       <c r="G10">
         <v>331.4</v>
@@ -2107,28 +2107,28 @@
         <v>680.4</v>
       </c>
       <c r="M10">
-        <v>17.62542743438301</v>
+        <v>19.82860586368088</v>
       </c>
       <c r="N10">
-        <v>662.7745725656169</v>
+        <v>660.5713941363191</v>
       </c>
       <c r="O10">
-        <v>106.0439316104987</v>
+        <v>105.6914230618111</v>
       </c>
       <c r="P10">
-        <v>556.7306409551182</v>
+        <v>554.879971074508</v>
       </c>
       <c r="Q10">
-        <v>881.4306409551183</v>
+        <v>879.5799710745081</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08732902040345211</v>
+        <v>0.08771733564223266</v>
       </c>
       <c r="T10">
-        <v>0.5716625975837292</v>
+        <v>0.5770079030093344</v>
       </c>
       <c r="U10">
         <v>0.07206759442929168</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>38.60331912704152</v>
+        <v>34.31406144625913</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08527108557328618</v>
+        <v>0.08535653002974804</v>
       </c>
       <c r="C11">
-        <v>3673.549837387246</v>
+        <v>3635.165278454153</v>
       </c>
       <c r="D11">
-        <v>3617.288837387247</v>
+        <v>3609.475278454153</v>
       </c>
       <c r="E11">
-        <v>-1511.161</v>
+        <v>-1480.59</v>
       </c>
       <c r="F11">
-        <v>275.139</v>
+        <v>305.71</v>
       </c>
       <c r="G11">
         <v>331.4</v>
@@ -2189,28 +2189,28 @@
         <v>680.4</v>
       </c>
       <c r="M11">
-        <v>19.82860586368088</v>
+        <v>22.03178429297876</v>
       </c>
       <c r="N11">
-        <v>660.5713941363191</v>
+        <v>658.3682157070212</v>
       </c>
       <c r="O11">
-        <v>105.6914230618111</v>
+        <v>105.3389145131234</v>
       </c>
       <c r="P11">
-        <v>554.879971074508</v>
+        <v>553.0293011938978</v>
       </c>
       <c r="Q11">
-        <v>879.5799710745081</v>
+        <v>877.7293011938979</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08771733564223266</v>
+        <v>0.08811428010854169</v>
       </c>
       <c r="T11">
-        <v>0.5770079030093344</v>
+        <v>0.5824719929999531</v>
       </c>
       <c r="U11">
         <v>0.07206759442929168</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>34.31406144625913</v>
+        <v>30.88265530163322</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08535653002974804</v>
+        <v>0.08544197448620988</v>
       </c>
       <c r="C12">
-        <v>3635.165278454153</v>
+        <v>3596.814402267933</v>
       </c>
       <c r="D12">
-        <v>3609.475278454153</v>
+        <v>3601.695402267933</v>
       </c>
       <c r="E12">
-        <v>-1480.59</v>
+        <v>-1450.019</v>
       </c>
       <c r="F12">
-        <v>305.71</v>
+        <v>336.281</v>
       </c>
       <c r="G12">
         <v>331.4</v>
@@ -2271,28 +2271,28 @@
         <v>680.4</v>
       </c>
       <c r="M12">
-        <v>22.03178429297876</v>
+        <v>24.23496272227664</v>
       </c>
       <c r="N12">
-        <v>658.3682157070212</v>
+        <v>656.1650372777233</v>
       </c>
       <c r="O12">
-        <v>105.3389145131234</v>
+        <v>104.9864059644357</v>
       </c>
       <c r="P12">
-        <v>553.0293011938978</v>
+        <v>551.1786313132875</v>
       </c>
       <c r="Q12">
-        <v>877.7293011938979</v>
+        <v>875.8786313132875</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.08811428010854169</v>
+        <v>0.08852014467521721</v>
       </c>
       <c r="T12">
-        <v>0.5824719929999531</v>
+        <v>0.5880588715296868</v>
       </c>
       <c r="U12">
         <v>0.07206759442929168</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.88265530163322</v>
+        <v>28.07514118330292</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08544197448620988</v>
+        <v>0.0855274189426717</v>
       </c>
       <c r="C13">
-        <v>3596.814402267933</v>
+        <v>3558.49699149728</v>
       </c>
       <c r="D13">
-        <v>3601.695402267933</v>
+        <v>3593.94899149728</v>
       </c>
       <c r="E13">
-        <v>-1450.019</v>
+        <v>-1419.448</v>
       </c>
       <c r="F13">
-        <v>336.281</v>
+        <v>366.852</v>
       </c>
       <c r="G13">
         <v>331.4</v>
@@ -2353,28 +2353,28 @@
         <v>680.4</v>
       </c>
       <c r="M13">
-        <v>24.23496272227664</v>
+        <v>26.43814115157451</v>
       </c>
       <c r="N13">
-        <v>656.1650372777233</v>
+        <v>653.9618588484254</v>
       </c>
       <c r="O13">
-        <v>104.9864059644357</v>
+        <v>104.6338974157481</v>
       </c>
       <c r="P13">
-        <v>551.1786313132875</v>
+        <v>549.3279614326774</v>
       </c>
       <c r="Q13">
-        <v>875.8786313132875</v>
+        <v>874.0279614326774</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08852014467521721</v>
+        <v>0.08893523343658989</v>
       </c>
       <c r="T13">
-        <v>0.5880588715296868</v>
+        <v>0.5937727245714599</v>
       </c>
       <c r="U13">
         <v>0.07206759442929168</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>28.07514118330292</v>
+        <v>25.73554608469435</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0855274189426717</v>
+        <v>0.08561286339913354</v>
       </c>
       <c r="C14">
-        <v>3558.49699149728</v>
+        <v>3520.21283067658</v>
       </c>
       <c r="D14">
-        <v>3593.94899149728</v>
+        <v>3586.23583067658</v>
       </c>
       <c r="E14">
-        <v>-1419.448</v>
+        <v>-1388.877</v>
       </c>
       <c r="F14">
-        <v>366.852</v>
+        <v>397.423</v>
       </c>
       <c r="G14">
         <v>331.4</v>
@@ -2435,28 +2435,28 @@
         <v>680.4</v>
       </c>
       <c r="M14">
-        <v>26.43814115157451</v>
+        <v>28.64131958087239</v>
       </c>
       <c r="N14">
-        <v>653.9618588484254</v>
+        <v>651.7586804191276</v>
       </c>
       <c r="O14">
-        <v>104.6338974157481</v>
+        <v>104.2813888670604</v>
       </c>
       <c r="P14">
-        <v>549.3279614326774</v>
+        <v>547.4772915520672</v>
       </c>
       <c r="Q14">
-        <v>874.0279614326774</v>
+        <v>872.1772915520672</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08893523343658989</v>
+        <v>0.08935986446833896</v>
       </c>
       <c r="T14">
-        <v>0.5937727245714599</v>
+        <v>0.5996179305567222</v>
       </c>
       <c r="U14">
         <v>0.07206759442929168</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.73554608469435</v>
+        <v>23.75588869356401</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08561286339913354</v>
+        <v>0.0856983078555954</v>
       </c>
       <c r="C15">
-        <v>3520.21283067658</v>
+        <v>3481.961706185956</v>
       </c>
       <c r="D15">
-        <v>3586.23583067658</v>
+        <v>3578.555706185956</v>
       </c>
       <c r="E15">
-        <v>-1388.877</v>
+        <v>-1358.306</v>
       </c>
       <c r="F15">
-        <v>397.423</v>
+        <v>427.994</v>
       </c>
       <c r="G15">
         <v>331.4</v>
@@ -2517,28 +2517,28 @@
         <v>680.4</v>
       </c>
       <c r="M15">
-        <v>28.64131958087239</v>
+        <v>30.84449801017027</v>
       </c>
       <c r="N15">
-        <v>651.7586804191276</v>
+        <v>649.5555019898297</v>
       </c>
       <c r="O15">
-        <v>104.2813888670604</v>
+        <v>103.9288803183728</v>
       </c>
       <c r="P15">
-        <v>547.4772915520672</v>
+        <v>545.626621671457</v>
       </c>
       <c r="Q15">
-        <v>872.1772915520672</v>
+        <v>870.326621671457</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08935986446833896</v>
+        <v>0.08979437064036128</v>
       </c>
       <c r="T15">
-        <v>0.5996179305567222</v>
+        <v>0.6055990715648975</v>
       </c>
       <c r="U15">
         <v>0.07206759442929168</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.75588869356401</v>
+        <v>22.05903950116658</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0856983078555954</v>
+        <v>0.08578375231205725</v>
       </c>
       <c r="C16">
-        <v>3481.961706185956</v>
+        <v>3443.743406231537</v>
       </c>
       <c r="D16">
-        <v>3578.555706185956</v>
+        <v>3570.908406231537</v>
       </c>
       <c r="E16">
-        <v>-1358.306</v>
+        <v>-1327.735</v>
       </c>
       <c r="F16">
-        <v>427.994</v>
+        <v>458.5650000000001</v>
       </c>
       <c r="G16">
         <v>331.4</v>
@@ -2599,28 +2599,28 @@
         <v>680.4</v>
       </c>
       <c r="M16">
-        <v>30.84449801017027</v>
+        <v>33.04767643946815</v>
       </c>
       <c r="N16">
-        <v>649.5555019898297</v>
+        <v>647.3523235605319</v>
       </c>
       <c r="O16">
-        <v>103.9288803183728</v>
+        <v>103.5763717696851</v>
       </c>
       <c r="P16">
-        <v>545.626621671457</v>
+        <v>543.7759517908468</v>
       </c>
       <c r="Q16">
-        <v>870.326621671457</v>
+        <v>868.4759517908468</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08979437064036128</v>
+        <v>0.0902391004870194</v>
       </c>
       <c r="T16">
-        <v>0.6055990715648975</v>
+        <v>0.6117209453026767</v>
       </c>
       <c r="U16">
         <v>0.07206759442929168</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.05903950116658</v>
+        <v>20.58843686775548</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08578375231205725</v>
+        <v>0.08586919676851908</v>
       </c>
       <c r="C17">
-        <v>3443.743406231537</v>
+        <v>3405.557720825985</v>
       </c>
       <c r="D17">
-        <v>3570.908406231537</v>
+        <v>3563.293720825985</v>
       </c>
       <c r="E17">
-        <v>-1327.735</v>
+        <v>-1297.164</v>
       </c>
       <c r="F17">
-        <v>458.565</v>
+        <v>489.136</v>
       </c>
       <c r="G17">
         <v>331.4</v>
@@ -2681,28 +2681,28 @@
         <v>680.4</v>
       </c>
       <c r="M17">
-        <v>33.04767643946814</v>
+        <v>35.25085486876601</v>
       </c>
       <c r="N17">
-        <v>647.3523235605319</v>
+        <v>645.1491451312339</v>
       </c>
       <c r="O17">
-        <v>103.5763717696851</v>
+        <v>103.2238632209974</v>
       </c>
       <c r="P17">
-        <v>543.7759517908468</v>
+        <v>541.9252819102364</v>
       </c>
       <c r="Q17">
-        <v>868.4759517908468</v>
+        <v>866.6252819102365</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.0902391004870194</v>
+        <v>0.09069441913955033</v>
       </c>
       <c r="T17">
-        <v>0.6117209453026767</v>
+        <v>0.6179885779389745</v>
       </c>
       <c r="U17">
         <v>0.07206759442929168</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.58843686775548</v>
+        <v>19.30165956352076</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08586919676851908</v>
+        <v>0.08595464122498092</v>
       </c>
       <c r="C18">
-        <v>3405.557720825985</v>
+        <v>3367.404441769275</v>
       </c>
       <c r="D18">
-        <v>3563.293720825985</v>
+        <v>3555.711441769275</v>
       </c>
       <c r="E18">
-        <v>-1297.164</v>
+        <v>-1266.593</v>
       </c>
       <c r="F18">
-        <v>489.136</v>
+        <v>519.707</v>
       </c>
       <c r="G18">
         <v>331.4</v>
@@ -2763,28 +2763,28 @@
         <v>680.4</v>
       </c>
       <c r="M18">
-        <v>35.25085486876601</v>
+        <v>37.45403329806389</v>
       </c>
       <c r="N18">
-        <v>645.1491451312339</v>
+        <v>642.9459667019361</v>
       </c>
       <c r="O18">
-        <v>103.2238632209974</v>
+        <v>102.8713546723098</v>
       </c>
       <c r="P18">
-        <v>541.9252819102364</v>
+        <v>540.0746120296263</v>
       </c>
       <c r="Q18">
-        <v>866.6252819102365</v>
+        <v>864.7746120296264</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09069441913955033</v>
+        <v>0.09116070932587719</v>
       </c>
       <c r="T18">
-        <v>0.6179885779389745</v>
+        <v>0.6244072378677135</v>
       </c>
       <c r="U18">
         <v>0.07206759442929168</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>19.30165956352076</v>
+        <v>18.16626782449013</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08595464122498092</v>
+        <v>0.08604008568144277</v>
       </c>
       <c r="C19">
-        <v>3367.404441769275</v>
+        <v>3329.283362629726</v>
       </c>
       <c r="D19">
-        <v>3555.711441769275</v>
+        <v>3548.161362629726</v>
       </c>
       <c r="E19">
-        <v>-1266.593</v>
+        <v>-1236.022</v>
       </c>
       <c r="F19">
-        <v>519.707</v>
+        <v>550.278</v>
       </c>
       <c r="G19">
         <v>331.4</v>
@@ -2845,28 +2845,28 @@
         <v>680.4</v>
       </c>
       <c r="M19">
-        <v>37.45403329806389</v>
+        <v>39.65721172736177</v>
       </c>
       <c r="N19">
-        <v>642.9459667019361</v>
+        <v>640.7427882726382</v>
       </c>
       <c r="O19">
-        <v>102.8713546723098</v>
+        <v>102.5188461236221</v>
       </c>
       <c r="P19">
-        <v>540.0746120296263</v>
+        <v>538.2239421490161</v>
       </c>
       <c r="Q19">
-        <v>864.7746120296264</v>
+        <v>862.9239421490162</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09116070932587719</v>
+        <v>0.09163837244357788</v>
       </c>
       <c r="T19">
-        <v>0.6244072378677135</v>
+        <v>0.630982450477641</v>
       </c>
       <c r="U19">
         <v>0.07206759442929168</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.16626782449013</v>
+        <v>17.15703072312957</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08604008568144278</v>
+        <v>0.08612553013790461</v>
       </c>
       <c r="C20">
-        <v>3329.283362629724</v>
+        <v>3291.19427872526</v>
       </c>
       <c r="D20">
-        <v>3548.161362629724</v>
+        <v>3540.64327872526</v>
       </c>
       <c r="E20">
-        <v>-1236.022</v>
+        <v>-1205.451</v>
       </c>
       <c r="F20">
-        <v>550.278</v>
+        <v>580.8489999999999</v>
       </c>
       <c r="G20">
         <v>331.4</v>
@@ -2927,28 +2927,28 @@
         <v>680.4</v>
       </c>
       <c r="M20">
-        <v>39.65721172736177</v>
+        <v>41.86039015665964</v>
       </c>
       <c r="N20">
-        <v>640.7427882726382</v>
+        <v>638.5396098433404</v>
       </c>
       <c r="O20">
-        <v>102.5188461236221</v>
+        <v>102.1663375749345</v>
       </c>
       <c r="P20">
-        <v>538.2239421490161</v>
+        <v>536.3732722684059</v>
       </c>
       <c r="Q20">
-        <v>862.9239421490162</v>
+        <v>861.073272268406</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09163837244357788</v>
+        <v>0.09212782971233291</v>
       </c>
       <c r="T20">
-        <v>0.630982450477641</v>
+        <v>0.6377200140162087</v>
       </c>
       <c r="U20">
         <v>0.07206759442929168</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.15703072312957</v>
+        <v>16.25402910612275</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08612553013790461</v>
+        <v>0.08621097459436644</v>
       </c>
       <c r="C21">
-        <v>3291.19427872526</v>
+        <v>3253.136987104912</v>
       </c>
       <c r="D21">
-        <v>3540.64327872526</v>
+        <v>3533.156987104912</v>
       </c>
       <c r="E21">
-        <v>-1205.451</v>
+        <v>-1174.88</v>
       </c>
       <c r="F21">
-        <v>580.8489999999999</v>
+        <v>611.42</v>
       </c>
       <c r="G21">
         <v>331.4</v>
@@ -3009,28 +3009,28 @@
         <v>680.4</v>
       </c>
       <c r="M21">
-        <v>41.86039015665964</v>
+        <v>44.06356858595752</v>
       </c>
       <c r="N21">
-        <v>638.5396098433404</v>
+        <v>636.3364314140424</v>
       </c>
       <c r="O21">
-        <v>102.1663375749345</v>
+        <v>101.8138290262468</v>
       </c>
       <c r="P21">
-        <v>536.3732722684059</v>
+        <v>534.5226023877956</v>
       </c>
       <c r="Q21">
-        <v>861.073272268406</v>
+        <v>859.2226023877956</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09212782971233291</v>
+        <v>0.09262952341280681</v>
       </c>
       <c r="T21">
-        <v>0.6377200140162087</v>
+        <v>0.6446260166432407</v>
       </c>
       <c r="U21">
         <v>0.07206759442929168</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.25402910612275</v>
+        <v>15.44132765081661</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08621097459436644</v>
+        <v>0.08629641905082829</v>
       </c>
       <c r="C22">
-        <v>3253.136987104912</v>
+        <v>3215.111286530557</v>
       </c>
       <c r="D22">
-        <v>3533.156987104912</v>
+        <v>3525.702286530557</v>
       </c>
       <c r="E22">
-        <v>-1174.88</v>
+        <v>-1144.309</v>
       </c>
       <c r="F22">
-        <v>611.42</v>
+        <v>641.991</v>
       </c>
       <c r="G22">
         <v>331.4</v>
@@ -3091,28 +3091,28 @@
         <v>680.4</v>
       </c>
       <c r="M22">
-        <v>44.06356858595752</v>
+        <v>46.2667470152554</v>
       </c>
       <c r="N22">
-        <v>636.3364314140424</v>
+        <v>634.1332529847446</v>
       </c>
       <c r="O22">
-        <v>101.8138290262468</v>
+        <v>101.4613204775591</v>
       </c>
       <c r="P22">
-        <v>534.5226023877956</v>
+        <v>532.6719325071854</v>
       </c>
       <c r="Q22">
-        <v>859.2226023877956</v>
+        <v>857.3719325071854</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09262952341280681</v>
+        <v>0.09314391821962181</v>
       </c>
       <c r="T22">
-        <v>0.6446260166432407</v>
+        <v>0.6517068547798178</v>
       </c>
       <c r="U22">
         <v>0.07206759442929168</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.44132765081661</v>
+        <v>14.70602633411105</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08629641905082829</v>
+        <v>0.08638186350729014</v>
       </c>
       <c r="C23">
-        <v>3215.111286530557</v>
+        <v>3177.116977458887</v>
       </c>
       <c r="D23">
-        <v>3525.702286530557</v>
+        <v>3518.278977458886</v>
       </c>
       <c r="E23">
-        <v>-1144.309</v>
+        <v>-1113.738</v>
       </c>
       <c r="F23">
-        <v>641.991</v>
+        <v>672.562</v>
       </c>
       <c r="G23">
         <v>331.4</v>
@@ -3173,28 +3173,28 @@
         <v>680.4</v>
       </c>
       <c r="M23">
-        <v>46.2667470152554</v>
+        <v>48.46992544455328</v>
       </c>
       <c r="N23">
-        <v>634.1332529847446</v>
+        <v>631.9300745554467</v>
       </c>
       <c r="O23">
-        <v>101.4613204775591</v>
+        <v>101.1088119288715</v>
       </c>
       <c r="P23">
-        <v>532.6719325071854</v>
+        <v>530.8212626265753</v>
       </c>
       <c r="Q23">
-        <v>857.3719325071854</v>
+        <v>855.5212626265753</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09314391821962181</v>
+        <v>0.09367150263686799</v>
       </c>
       <c r="T23">
-        <v>0.6517068547798178</v>
+        <v>0.6589692528686147</v>
       </c>
       <c r="U23">
         <v>0.07206759442929168</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.70602633411105</v>
+        <v>14.03757059165146</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08638186350729014</v>
+        <v>0.08646730796375199</v>
       </c>
       <c r="C24">
-        <v>3177.116977458887</v>
+        <v>3139.153862023607</v>
       </c>
       <c r="D24">
-        <v>3518.278977458886</v>
+        <v>3510.886862023607</v>
       </c>
       <c r="E24">
-        <v>-1113.738</v>
+        <v>-1083.167</v>
       </c>
       <c r="F24">
-        <v>672.562</v>
+        <v>703.133</v>
       </c>
       <c r="G24">
         <v>331.4</v>
@@ -3255,28 +3255,28 @@
         <v>680.4</v>
       </c>
       <c r="M24">
-        <v>48.46992544455328</v>
+        <v>50.67310387385115</v>
       </c>
       <c r="N24">
-        <v>631.9300745554467</v>
+        <v>629.7268961261489</v>
       </c>
       <c r="O24">
-        <v>101.1088119288715</v>
+        <v>100.7563033801838</v>
       </c>
       <c r="P24">
-        <v>530.8212626265753</v>
+        <v>528.9705927459651</v>
       </c>
       <c r="Q24">
-        <v>855.5212626265753</v>
+        <v>853.6705927459651</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09367150263686799</v>
+        <v>0.09421279054547121</v>
       </c>
       <c r="T24">
-        <v>0.6589692528686147</v>
+        <v>0.666420284674004</v>
       </c>
       <c r="U24">
         <v>0.07206759442929168</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.03757059165146</v>
+        <v>13.4272414354927</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08646730796375199</v>
+        <v>0.08655275242021383</v>
       </c>
       <c r="C25">
-        <v>3139.153862023607</v>
+        <v>3101.221744017849</v>
       </c>
       <c r="D25">
-        <v>3510.886862023607</v>
+        <v>3503.525744017849</v>
       </c>
       <c r="E25">
-        <v>-1083.167</v>
+        <v>-1052.596</v>
       </c>
       <c r="F25">
-        <v>703.133</v>
+        <v>733.7040000000001</v>
       </c>
       <c r="G25">
         <v>331.4</v>
@@ -3337,28 +3337,28 @@
         <v>680.4</v>
       </c>
       <c r="M25">
-        <v>50.67310387385115</v>
+        <v>52.87628230314903</v>
       </c>
       <c r="N25">
-        <v>629.7268961261489</v>
+        <v>627.5237176968509</v>
       </c>
       <c r="O25">
-        <v>100.7563033801838</v>
+        <v>100.4037948314961</v>
       </c>
       <c r="P25">
-        <v>528.9705927459651</v>
+        <v>527.1199228653547</v>
       </c>
       <c r="Q25">
-        <v>853.6705927459651</v>
+        <v>851.8199228653548</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09421279054547121</v>
+        <v>0.09476832287272187</v>
       </c>
       <c r="T25">
-        <v>0.666420284674004</v>
+        <v>0.6740673962637455</v>
       </c>
       <c r="U25">
         <v>0.07206759442929168</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.4272414354927</v>
+        <v>12.86777304234717</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08655275242021383</v>
+        <v>0.08695319687667567</v>
       </c>
       <c r="C26">
-        <v>3101.221744017849</v>
+        <v>3036.559408016236</v>
       </c>
       <c r="D26">
-        <v>3503.525744017849</v>
+        <v>3469.434408016236</v>
       </c>
       <c r="E26">
-        <v>-1052.596</v>
+        <v>-1022.025</v>
       </c>
       <c r="F26">
-        <v>733.704</v>
+        <v>764.275</v>
       </c>
       <c r="G26">
         <v>331.4</v>
@@ -3419,45 +3419,45 @@
         <v>680.4</v>
       </c>
       <c r="M26">
-        <v>52.87628230314903</v>
+        <v>56.22587323244689</v>
       </c>
       <c r="N26">
-        <v>627.523717696851</v>
+        <v>624.174126767553</v>
       </c>
       <c r="O26">
-        <v>100.4037948314962</v>
+        <v>99.86786028280849</v>
       </c>
       <c r="P26">
-        <v>527.1199228653549</v>
+        <v>524.3062664847446</v>
       </c>
       <c r="Q26">
-        <v>851.8199228653549</v>
+        <v>849.0062664847446</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09476832287272187</v>
+        <v>0.09533866939536589</v>
       </c>
       <c r="T26">
-        <v>0.6740673962637455</v>
+        <v>0.6819184308292134</v>
       </c>
       <c r="U26">
-        <v>0.07206759442929168</v>
+        <v>0.07356759442929167</v>
       </c>
       <c r="V26">
         <v>0.16</v>
       </c>
       <c r="W26">
-        <v>0.06053677932060501</v>
+        <v>0.061796779320605</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>12.86777304234717</v>
+        <v>12.1011904463825</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08695319687667567</v>
+        <v>0.08705124133313751</v>
       </c>
       <c r="C27">
-        <v>3036.559408016236</v>
+        <v>2997.742381962938</v>
       </c>
       <c r="D27">
-        <v>3469.434408016236</v>
+        <v>3461.188381962938</v>
       </c>
       <c r="E27">
-        <v>-1022.025</v>
+        <v>-991.454</v>
       </c>
       <c r="F27">
-        <v>764.275</v>
+        <v>794.846</v>
       </c>
       <c r="G27">
         <v>331.4</v>
@@ -3501,28 +3501,28 @@
         <v>680.4</v>
       </c>
       <c r="M27">
-        <v>56.22587323244689</v>
+        <v>58.47490816174477</v>
       </c>
       <c r="N27">
-        <v>624.174126767553</v>
+        <v>621.9250918382552</v>
       </c>
       <c r="O27">
-        <v>99.86786028280849</v>
+        <v>99.50801469412083</v>
       </c>
       <c r="P27">
-        <v>524.3062664847446</v>
+        <v>522.4170771441344</v>
       </c>
       <c r="Q27">
-        <v>849.0062664847446</v>
+        <v>847.1170771441344</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09533866939536589</v>
+        <v>0.09592443068889217</v>
       </c>
       <c r="T27">
-        <v>0.6819184308292134</v>
+        <v>0.6899816555180723</v>
       </c>
       <c r="U27">
         <v>0.07356759442929167</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.1011904463825</v>
+        <v>11.63576004459856</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08705124133313751</v>
+        <v>0.08714928578959935</v>
       </c>
       <c r="C28">
-        <v>2997.742381962938</v>
+        <v>2958.964460679017</v>
       </c>
       <c r="D28">
-        <v>3461.188381962938</v>
+        <v>3452.981460679017</v>
       </c>
       <c r="E28">
-        <v>-991.454</v>
+        <v>-960.8829999999999</v>
       </c>
       <c r="F28">
-        <v>794.846</v>
+        <v>825.417</v>
       </c>
       <c r="G28">
         <v>331.4</v>
@@ -3583,28 +3583,28 @@
         <v>680.4</v>
       </c>
       <c r="M28">
-        <v>58.47490816174477</v>
+        <v>60.72394309104265</v>
       </c>
       <c r="N28">
-        <v>621.9250918382552</v>
+        <v>619.6760569089573</v>
       </c>
       <c r="O28">
-        <v>99.50801469412083</v>
+        <v>99.14816910543317</v>
       </c>
       <c r="P28">
-        <v>522.4170771441344</v>
+        <v>520.5278878035242</v>
       </c>
       <c r="Q28">
-        <v>847.1170771441344</v>
+        <v>845.2278878035243</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09592443068889217</v>
+        <v>0.09652624023703561</v>
       </c>
       <c r="T28">
-        <v>0.6899816555180723</v>
+        <v>0.6982657904723795</v>
       </c>
       <c r="U28">
         <v>0.07356759442929167</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.63576004459856</v>
+        <v>11.20480596887269</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08714928578959935</v>
+        <v>0.08724733024606118</v>
       </c>
       <c r="C29">
-        <v>2958.964460679017</v>
+        <v>2920.225366655223</v>
       </c>
       <c r="D29">
-        <v>3452.981460679017</v>
+        <v>3444.813366655223</v>
       </c>
       <c r="E29">
-        <v>-960.8829999999999</v>
+        <v>-930.3119999999999</v>
       </c>
       <c r="F29">
-        <v>825.417</v>
+        <v>855.9880000000001</v>
       </c>
       <c r="G29">
         <v>331.4</v>
@@ -3665,28 +3665,28 @@
         <v>680.4</v>
       </c>
       <c r="M29">
-        <v>60.72394309104265</v>
+        <v>62.97297802034053</v>
       </c>
       <c r="N29">
-        <v>619.6760569089573</v>
+        <v>617.4270219796595</v>
       </c>
       <c r="O29">
-        <v>99.14816910543317</v>
+        <v>98.78832351674552</v>
       </c>
       <c r="P29">
-        <v>520.5278878035242</v>
+        <v>518.6386984629139</v>
       </c>
       <c r="Q29">
-        <v>845.2278878035243</v>
+        <v>843.338698462914</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09652624023703561</v>
+        <v>0.09714476671707192</v>
       </c>
       <c r="T29">
-        <v>0.6982657904723795</v>
+        <v>0.7067800402865284</v>
       </c>
       <c r="U29">
         <v>0.07356759442929167</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.20480596887269</v>
+        <v>10.80463432712723</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08724733024606118</v>
+        <v>0.08734537470252303</v>
       </c>
       <c r="C30">
-        <v>2920.225366655223</v>
+        <v>2881.52482500192</v>
       </c>
       <c r="D30">
-        <v>3444.813366655223</v>
+        <v>3436.68382500192</v>
       </c>
       <c r="E30">
-        <v>-930.3119999999999</v>
+        <v>-899.7409999999999</v>
       </c>
       <c r="F30">
-        <v>855.9880000000001</v>
+        <v>886.5590000000001</v>
       </c>
       <c r="G30">
         <v>331.4</v>
@@ -3747,28 +3747,28 @@
         <v>680.4</v>
       </c>
       <c r="M30">
-        <v>62.97297802034053</v>
+        <v>65.2220129496384</v>
       </c>
       <c r="N30">
-        <v>617.4270219796595</v>
+        <v>615.1779870503616</v>
       </c>
       <c r="O30">
-        <v>98.78832351674552</v>
+        <v>98.42847792805786</v>
       </c>
       <c r="P30">
-        <v>518.6386984629139</v>
+        <v>516.7495091223037</v>
       </c>
       <c r="Q30">
-        <v>843.338698462914</v>
+        <v>841.4495091223038</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09714476671707192</v>
+        <v>0.09778071647823604</v>
       </c>
       <c r="T30">
-        <v>0.7067800402865284</v>
+        <v>0.7155341281236113</v>
       </c>
       <c r="U30">
         <v>0.07356759442929167</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.80463432712723</v>
+        <v>10.43206072964009</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08734537470252303</v>
+        <v>0.08744341915898488</v>
       </c>
       <c r="C31">
-        <v>2881.52482500192</v>
+        <v>2842.862563418256</v>
       </c>
       <c r="D31">
-        <v>3436.68382500192</v>
+        <v>3428.592563418256</v>
       </c>
       <c r="E31">
-        <v>-899.741</v>
+        <v>-869.17</v>
       </c>
       <c r="F31">
-        <v>886.559</v>
+        <v>917.13</v>
       </c>
       <c r="G31">
         <v>331.4</v>
@@ -3829,28 +3829,28 @@
         <v>680.4</v>
       </c>
       <c r="M31">
-        <v>65.2220129496384</v>
+        <v>67.47104787893628</v>
       </c>
       <c r="N31">
-        <v>615.1779870503616</v>
+        <v>612.9289521210637</v>
       </c>
       <c r="O31">
-        <v>98.42847792805786</v>
+        <v>98.0686323393702</v>
       </c>
       <c r="P31">
-        <v>516.7495091223037</v>
+        <v>514.8603197816935</v>
       </c>
       <c r="Q31">
-        <v>841.4495091223038</v>
+        <v>839.5603197816936</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09778071647823602</v>
+        <v>0.09843483623257625</v>
       </c>
       <c r="T31">
-        <v>0.7155341281236112</v>
+        <v>0.7245383327560392</v>
       </c>
       <c r="U31">
         <v>0.07356759442929167</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.43206072964009</v>
+        <v>10.08432537198542</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08744341915898488</v>
+        <v>0.08754146361544671</v>
       </c>
       <c r="C32">
-        <v>2842.862563418256</v>
+        <v>2804.238312161752</v>
       </c>
       <c r="D32">
-        <v>3428.592563418256</v>
+        <v>3420.539312161752</v>
       </c>
       <c r="E32">
-        <v>-869.17</v>
+        <v>-838.5989999999999</v>
       </c>
       <c r="F32">
-        <v>917.13</v>
+        <v>947.701</v>
       </c>
       <c r="G32">
         <v>331.4</v>
@@ -3911,28 +3911,28 @@
         <v>680.4</v>
       </c>
       <c r="M32">
-        <v>67.47104787893628</v>
+        <v>69.72008280823415</v>
       </c>
       <c r="N32">
-        <v>612.9289521210637</v>
+        <v>610.6799171917659</v>
       </c>
       <c r="O32">
-        <v>98.0686323393702</v>
+        <v>97.70878675068253</v>
       </c>
       <c r="P32">
-        <v>514.8603197816935</v>
+        <v>512.9711304410833</v>
       </c>
       <c r="Q32">
-        <v>839.5603197816936</v>
+        <v>837.6711304410834</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09843483623257625</v>
+        <v>0.0991079159797959</v>
       </c>
       <c r="T32">
-        <v>0.7245383327560392</v>
+        <v>0.7338035288270883</v>
       </c>
       <c r="U32">
         <v>0.07356759442929167</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.08432537198542</v>
+        <v>9.759024553534276</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08754146361544671</v>
+        <v>0.08809646807190856</v>
       </c>
       <c r="C33">
-        <v>2804.238312161752</v>
+        <v>2728.783787643222</v>
       </c>
       <c r="D33">
-        <v>3420.539312161752</v>
+        <v>3375.655787643222</v>
       </c>
       <c r="E33">
-        <v>-838.5989999999999</v>
+        <v>-808.028</v>
       </c>
       <c r="F33">
-        <v>947.701</v>
+        <v>978.2719999999999</v>
       </c>
       <c r="G33">
         <v>331.4</v>
@@ -3993,45 +3993,45 @@
         <v>680.4</v>
       </c>
       <c r="M33">
-        <v>69.72008280823415</v>
+        <v>73.63218013753202</v>
       </c>
       <c r="N33">
-        <v>610.6799171917659</v>
+        <v>606.7678198624679</v>
       </c>
       <c r="O33">
-        <v>97.70878675068253</v>
+        <v>97.08285117799487</v>
       </c>
       <c r="P33">
-        <v>512.9711304410833</v>
+        <v>509.6849686844731</v>
       </c>
       <c r="Q33">
-        <v>837.6711304410834</v>
+        <v>834.3849686844731</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.0991079159797959</v>
+        <v>0.09980079219016906</v>
       </c>
       <c r="T33">
-        <v>0.7338035288270883</v>
+        <v>0.743341230664933</v>
       </c>
       <c r="U33">
-        <v>0.07356759442929167</v>
+        <v>0.07526759442929168</v>
       </c>
       <c r="V33">
         <v>0.16</v>
       </c>
       <c r="W33">
-        <v>0.061796779320605</v>
+        <v>0.06322477932060501</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>9.759024553534276</v>
+        <v>9.240524981456911</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.08809646807190856</v>
+        <v>0.0882087925283704</v>
       </c>
       <c r="C34">
-        <v>2728.783787643222</v>
+        <v>2689.271983650851</v>
       </c>
       <c r="D34">
-        <v>3375.655787643222</v>
+        <v>3366.714983650851</v>
       </c>
       <c r="E34">
-        <v>-808.028</v>
+        <v>-777.457</v>
       </c>
       <c r="F34">
-        <v>978.2719999999999</v>
+        <v>1008.843</v>
       </c>
       <c r="G34">
         <v>331.4</v>
@@ -4075,28 +4075,28 @@
         <v>680.4</v>
       </c>
       <c r="M34">
-        <v>73.63218013753202</v>
+        <v>75.93318576682991</v>
       </c>
       <c r="N34">
-        <v>606.7678198624679</v>
+        <v>604.4668142331701</v>
       </c>
       <c r="O34">
-        <v>97.08285117799487</v>
+        <v>96.71469027730723</v>
       </c>
       <c r="P34">
-        <v>509.6849686844731</v>
+        <v>507.7521239558629</v>
       </c>
       <c r="Q34">
-        <v>834.3849686844731</v>
+        <v>832.4521239558629</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09980079219016906</v>
+        <v>0.1005143512724937</v>
       </c>
       <c r="T34">
-        <v>0.743341230664933</v>
+        <v>0.7531636400203252</v>
       </c>
       <c r="U34">
         <v>0.07526759442929168</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.240524981456911</v>
+        <v>8.960509072927913</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0882087925283704</v>
+        <v>0.08832111698483225</v>
       </c>
       <c r="C35">
-        <v>2689.271983650851</v>
+        <v>2649.807415997502</v>
       </c>
       <c r="D35">
-        <v>3366.714983650851</v>
+        <v>3357.821415997502</v>
       </c>
       <c r="E35">
-        <v>-777.457</v>
+        <v>-746.886</v>
       </c>
       <c r="F35">
-        <v>1008.843</v>
+        <v>1039.414</v>
       </c>
       <c r="G35">
         <v>331.4</v>
@@ -4157,28 +4157,28 @@
         <v>680.4</v>
       </c>
       <c r="M35">
-        <v>75.93318576682991</v>
+        <v>78.23419139612778</v>
       </c>
       <c r="N35">
-        <v>604.4668142331701</v>
+        <v>602.1658086038722</v>
       </c>
       <c r="O35">
-        <v>96.71469027730723</v>
+        <v>96.34652937661954</v>
       </c>
       <c r="P35">
-        <v>507.7521239558629</v>
+        <v>505.8192792272527</v>
       </c>
       <c r="Q35">
-        <v>832.4521239558629</v>
+        <v>830.5192792272527</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1005143512724937</v>
+        <v>0.1012495333573129</v>
       </c>
       <c r="T35">
-        <v>0.7531636400203252</v>
+        <v>0.7632836981440627</v>
       </c>
       <c r="U35">
         <v>0.07526759442929168</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.960509072927913</v>
+        <v>8.696964688430032</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.08832111698483225</v>
+        <v>0.08843344144129409</v>
       </c>
       <c r="C36">
-        <v>2649.807415997502</v>
+        <v>2610.389711328653</v>
       </c>
       <c r="D36">
-        <v>3357.821415997502</v>
+        <v>3348.974711328653</v>
       </c>
       <c r="E36">
-        <v>-746.886</v>
+        <v>-716.3149999999998</v>
       </c>
       <c r="F36">
-        <v>1039.414</v>
+        <v>1069.985</v>
       </c>
       <c r="G36">
         <v>331.4</v>
@@ -4239,28 +4239,28 @@
         <v>680.4</v>
       </c>
       <c r="M36">
-        <v>78.23419139612778</v>
+        <v>80.53519702542566</v>
       </c>
       <c r="N36">
-        <v>602.1658086038722</v>
+        <v>599.8648029745743</v>
       </c>
       <c r="O36">
-        <v>96.34652937661954</v>
+        <v>95.9783684759319</v>
       </c>
       <c r="P36">
-        <v>505.8192792272527</v>
+        <v>503.8864344986424</v>
       </c>
       <c r="Q36">
-        <v>830.5192792272527</v>
+        <v>828.5864344986425</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1012495333573129</v>
+        <v>0.1020073364293574</v>
       </c>
       <c r="T36">
-        <v>0.7632836981440627</v>
+        <v>0.7737151426716075</v>
       </c>
       <c r="U36">
         <v>0.07526759442929168</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.696964688430032</v>
+        <v>8.448479983046317</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.08843344144129409</v>
+        <v>0.08854576589775592</v>
       </c>
       <c r="C37">
-        <v>2610.389711328653</v>
+        <v>2571.018500214078</v>
       </c>
       <c r="D37">
-        <v>3348.974711328653</v>
+        <v>3340.174500214078</v>
       </c>
       <c r="E37">
-        <v>-716.3149999999998</v>
+        <v>-685.7439999999999</v>
       </c>
       <c r="F37">
-        <v>1069.985</v>
+        <v>1100.556</v>
       </c>
       <c r="G37">
         <v>331.4</v>
@@ -4321,28 +4321,28 @@
         <v>680.4</v>
       </c>
       <c r="M37">
-        <v>80.53519702542566</v>
+        <v>82.83620265472354</v>
       </c>
       <c r="N37">
-        <v>599.8648029745743</v>
+        <v>597.5637973452765</v>
       </c>
       <c r="O37">
-        <v>95.9783684759319</v>
+        <v>95.61020757524425</v>
       </c>
       <c r="P37">
-        <v>503.8864344986424</v>
+        <v>501.9535897700322</v>
       </c>
       <c r="Q37">
-        <v>828.5864344986425</v>
+        <v>826.6535897700323</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1020073364293574</v>
+        <v>0.1027888208474033</v>
       </c>
       <c r="T37">
-        <v>0.7737151426716075</v>
+        <v>0.7844725698406381</v>
       </c>
       <c r="U37">
         <v>0.07526759442929168</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.448479983046317</v>
+        <v>8.213799983517253</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08854576589775592</v>
+        <v>0.08865809035421779</v>
       </c>
       <c r="C38">
-        <v>2571.018500214078</v>
+        <v>2531.693417096434</v>
       </c>
       <c r="D38">
-        <v>3340.174500214078</v>
+        <v>3331.420417096434</v>
       </c>
       <c r="E38">
-        <v>-685.7439999999999</v>
+        <v>-655.173</v>
       </c>
       <c r="F38">
-        <v>1100.556</v>
+        <v>1131.127</v>
       </c>
       <c r="G38">
         <v>331.4</v>
@@ -4403,28 +4403,28 @@
         <v>680.4</v>
       </c>
       <c r="M38">
-        <v>82.83620265472354</v>
+        <v>85.13720828402141</v>
       </c>
       <c r="N38">
-        <v>597.5637973452765</v>
+        <v>595.2627917159786</v>
       </c>
       <c r="O38">
-        <v>95.61020757524425</v>
+        <v>95.24204667455658</v>
       </c>
       <c r="P38">
-        <v>501.9535897700322</v>
+        <v>500.0207450414219</v>
       </c>
       <c r="Q38">
-        <v>826.6535897700323</v>
+        <v>824.720745041422</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1027888208474033</v>
+        <v>0.1035951142945935</v>
       </c>
       <c r="T38">
-        <v>0.784472569840638</v>
+        <v>0.7955715026340823</v>
       </c>
       <c r="U38">
         <v>0.07526759442929168</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.213799983517253</v>
+        <v>7.991805389368137</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.08865809035421779</v>
+        <v>0.08877041481067961</v>
       </c>
       <c r="C39">
-        <v>2531.693417096434</v>
+        <v>2492.414100240643</v>
       </c>
       <c r="D39">
-        <v>3331.420417096434</v>
+        <v>3322.712100240643</v>
       </c>
       <c r="E39">
-        <v>-655.173</v>
+        <v>-624.6020000000001</v>
       </c>
       <c r="F39">
-        <v>1131.127</v>
+        <v>1161.698</v>
       </c>
       <c r="G39">
         <v>331.4</v>
@@ -4485,28 +4485,28 @@
         <v>680.4</v>
       </c>
       <c r="M39">
-        <v>85.13720828402141</v>
+        <v>87.43821391331927</v>
       </c>
       <c r="N39">
-        <v>595.2627917159786</v>
+        <v>592.9617860866807</v>
       </c>
       <c r="O39">
-        <v>95.24204667455658</v>
+        <v>94.87388577386892</v>
       </c>
       <c r="P39">
-        <v>500.0207450414219</v>
+        <v>498.0879003128118</v>
       </c>
       <c r="Q39">
-        <v>824.720745041422</v>
+        <v>822.7879003128119</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1035951142945935</v>
+        <v>0.1044274172078221</v>
       </c>
       <c r="T39">
-        <v>0.7955715026340823</v>
+        <v>0.8070284655176375</v>
       </c>
       <c r="U39">
         <v>0.07526759442929168</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.991805389368137</v>
+        <v>7.781494721226872</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08877041481067961</v>
+        <v>0.08888273926714146</v>
       </c>
       <c r="C40">
-        <v>2492.414100240643</v>
+        <v>2453.18019168405</v>
       </c>
       <c r="D40">
-        <v>3322.712100240643</v>
+        <v>3314.049191684051</v>
       </c>
       <c r="E40">
-        <v>-624.6020000000001</v>
+        <v>-594.0309999999999</v>
       </c>
       <c r="F40">
-        <v>1161.698</v>
+        <v>1192.269</v>
       </c>
       <c r="G40">
         <v>331.4</v>
@@ -4567,28 +4567,28 @@
         <v>680.4</v>
       </c>
       <c r="M40">
-        <v>87.43821391331927</v>
+        <v>89.73921954261716</v>
       </c>
       <c r="N40">
-        <v>592.9617860866807</v>
+        <v>590.6607804573828</v>
       </c>
       <c r="O40">
-        <v>94.87388577386892</v>
+        <v>94.50572487318125</v>
       </c>
       <c r="P40">
-        <v>498.0879003128118</v>
+        <v>496.1550555842015</v>
       </c>
       <c r="Q40">
-        <v>822.7879003128119</v>
+        <v>820.8550555842016</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1044274172078221</v>
+        <v>0.1052870087411566</v>
       </c>
       <c r="T40">
-        <v>0.8070284655176375</v>
+        <v>0.8188610665285225</v>
       </c>
       <c r="U40">
         <v>0.07526759442929168</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.781494721226872</v>
+        <v>7.581969215554387</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08888273926714146</v>
+        <v>0.0892638637236033</v>
       </c>
       <c r="C41">
-        <v>2453.18019168405</v>
+        <v>2393.549069351151</v>
       </c>
       <c r="D41">
-        <v>3314.049191684051</v>
+        <v>3284.989069351151</v>
       </c>
       <c r="E41">
-        <v>-594.0309999999999</v>
+        <v>-563.46</v>
       </c>
       <c r="F41">
-        <v>1192.269</v>
+        <v>1222.84</v>
       </c>
       <c r="G41">
         <v>331.4</v>
@@ -4649,45 +4649,45 @@
         <v>680.4</v>
       </c>
       <c r="M41">
-        <v>89.73921954261716</v>
+        <v>93.01849717191503</v>
       </c>
       <c r="N41">
-        <v>590.6607804573828</v>
+        <v>587.381502828085</v>
       </c>
       <c r="O41">
-        <v>94.50572487318125</v>
+        <v>93.9810404524936</v>
       </c>
       <c r="P41">
-        <v>496.1550555842015</v>
+        <v>493.4004623755914</v>
       </c>
       <c r="Q41">
-        <v>820.8550555842016</v>
+        <v>818.1004623755914</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1052870087411566</v>
+        <v>0.1061752533256022</v>
       </c>
       <c r="T41">
-        <v>0.8188610665285225</v>
+        <v>0.8310880875731038</v>
       </c>
       <c r="U41">
-        <v>0.07526759442929168</v>
+        <v>0.07606759442929167</v>
       </c>
       <c r="V41">
         <v>0.16</v>
       </c>
       <c r="W41">
-        <v>0.06322477932060501</v>
+        <v>0.063896779320605</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.581969215554387</v>
+        <v>7.314674185097805</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.0892638637236033</v>
+        <v>0.08938290818006514</v>
       </c>
       <c r="C42">
-        <v>2393.549069351151</v>
+        <v>2354.005291843319</v>
       </c>
       <c r="D42">
-        <v>3284.989069351151</v>
+        <v>3276.016291843319</v>
       </c>
       <c r="E42">
-        <v>-563.46</v>
+        <v>-532.8889999999999</v>
       </c>
       <c r="F42">
-        <v>1222.84</v>
+        <v>1253.411</v>
       </c>
       <c r="G42">
         <v>331.4</v>
@@ -4731,28 +4731,28 @@
         <v>680.4</v>
       </c>
       <c r="M42">
-        <v>93.01849717191503</v>
+        <v>95.34395960121292</v>
       </c>
       <c r="N42">
-        <v>587.381502828085</v>
+        <v>585.0560403987871</v>
       </c>
       <c r="O42">
-        <v>93.9810404524936</v>
+        <v>93.60896646380594</v>
       </c>
       <c r="P42">
-        <v>493.4004623755914</v>
+        <v>491.4470739349812</v>
       </c>
       <c r="Q42">
-        <v>818.1004623755914</v>
+        <v>816.1470739349812</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1061752533256022</v>
+        <v>0.1070936078959612</v>
       </c>
       <c r="T42">
-        <v>0.8310880875731038</v>
+        <v>0.8437295839073318</v>
       </c>
       <c r="U42">
         <v>0.07606759442929167</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.314674185097805</v>
+        <v>7.136267497656394</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08938290818006514</v>
+        <v>0.08950195263652698</v>
       </c>
       <c r="C43">
-        <v>2354.005291843319</v>
+        <v>2314.510398165932</v>
       </c>
       <c r="D43">
-        <v>3276.016291843319</v>
+        <v>3267.092398165932</v>
       </c>
       <c r="E43">
-        <v>-532.8889999999999</v>
+        <v>-502.318</v>
       </c>
       <c r="F43">
-        <v>1253.411</v>
+        <v>1283.982</v>
       </c>
       <c r="G43">
         <v>331.4</v>
@@ -4813,28 +4813,28 @@
         <v>680.4</v>
       </c>
       <c r="M43">
-        <v>95.34395960121292</v>
+        <v>97.66942203051077</v>
       </c>
       <c r="N43">
-        <v>585.0560403987871</v>
+        <v>582.7305779694892</v>
       </c>
       <c r="O43">
-        <v>93.60896646380594</v>
+        <v>93.23689247511828</v>
       </c>
       <c r="P43">
-        <v>491.4470739349812</v>
+        <v>489.4936854943709</v>
       </c>
       <c r="Q43">
-        <v>816.1470739349812</v>
+        <v>814.193685494371</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1070936078959612</v>
+        <v>0.1080436298652981</v>
       </c>
       <c r="T43">
-        <v>0.8437295839073318</v>
+        <v>0.8568069939082573</v>
       </c>
       <c r="U43">
         <v>0.07606759442929167</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.136267497656394</v>
+        <v>6.966356366759814</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08950195263652699</v>
+        <v>0.08962099709298883</v>
       </c>
       <c r="C44">
-        <v>2314.51039816593</v>
+        <v>2275.063989924421</v>
       </c>
       <c r="D44">
-        <v>3267.09239816593</v>
+        <v>3258.216989924421</v>
       </c>
       <c r="E44">
-        <v>-502.318</v>
+        <v>-471.7470000000001</v>
       </c>
       <c r="F44">
-        <v>1283.982</v>
+        <v>1314.553</v>
       </c>
       <c r="G44">
         <v>331.4</v>
@@ -4895,28 +4895,28 @@
         <v>680.4</v>
       </c>
       <c r="M44">
-        <v>97.66942203051077</v>
+        <v>99.99488445980865</v>
       </c>
       <c r="N44">
-        <v>582.7305779694892</v>
+        <v>580.4051155401913</v>
       </c>
       <c r="O44">
-        <v>93.23689247511828</v>
+        <v>92.86481848643062</v>
       </c>
       <c r="P44">
-        <v>489.4936854943709</v>
+        <v>487.5402970537607</v>
       </c>
       <c r="Q44">
-        <v>814.193685494371</v>
+        <v>812.2402970537607</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1080436298652981</v>
+        <v>0.1090269859388222</v>
       </c>
       <c r="T44">
-        <v>0.8568069939082573</v>
+        <v>0.8703432604004433</v>
       </c>
       <c r="U44">
         <v>0.07606759442929167</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.966356366759814</v>
+        <v>6.804348079160749</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08962099709298883</v>
+        <v>0.08974004154945067</v>
       </c>
       <c r="C45">
-        <v>2275.063989924421</v>
+        <v>2235.665673041623</v>
       </c>
       <c r="D45">
-        <v>3258.216989924421</v>
+        <v>3249.389673041623</v>
       </c>
       <c r="E45">
-        <v>-471.7470000000001</v>
+        <v>-441.1759999999999</v>
       </c>
       <c r="F45">
-        <v>1314.553</v>
+        <v>1345.124</v>
       </c>
       <c r="G45">
         <v>331.4</v>
@@ -4977,28 +4977,28 @@
         <v>680.4</v>
       </c>
       <c r="M45">
-        <v>99.99488445980865</v>
+        <v>102.3203468891065</v>
       </c>
       <c r="N45">
-        <v>580.4051155401913</v>
+        <v>578.0796531108934</v>
       </c>
       <c r="O45">
-        <v>92.86481848643062</v>
+        <v>92.49274449774295</v>
       </c>
       <c r="P45">
-        <v>487.5402970537607</v>
+        <v>485.5869086131505</v>
       </c>
       <c r="Q45">
-        <v>812.2402970537607</v>
+        <v>810.2869086131506</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1090269859388222</v>
+        <v>0.1100454618721151</v>
       </c>
       <c r="T45">
-        <v>0.8703432604004433</v>
+        <v>0.884362964981636</v>
       </c>
       <c r="U45">
         <v>0.07606759442929167</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.804348079160749</v>
+        <v>6.649703804634368</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08974004154945067</v>
+        <v>0.08985908600591251</v>
       </c>
       <c r="C46">
-        <v>2235.665673041623</v>
+        <v>2196.315057699443</v>
       </c>
       <c r="D46">
-        <v>3249.389673041623</v>
+        <v>3240.610057699443</v>
       </c>
       <c r="E46">
-        <v>-441.1759999999999</v>
+        <v>-410.605</v>
       </c>
       <c r="F46">
-        <v>1345.124</v>
+        <v>1375.695</v>
       </c>
       <c r="G46">
         <v>331.4</v>
@@ -5059,28 +5059,28 @@
         <v>680.4</v>
       </c>
       <c r="M46">
-        <v>102.3203468891065</v>
+        <v>104.6458093184044</v>
       </c>
       <c r="N46">
-        <v>578.0796531108934</v>
+        <v>575.7541906815956</v>
       </c>
       <c r="O46">
-        <v>92.49274449774295</v>
+        <v>92.12067050905529</v>
       </c>
       <c r="P46">
-        <v>485.5869086131505</v>
+        <v>483.6335201725403</v>
       </c>
       <c r="Q46">
-        <v>810.2869086131506</v>
+        <v>808.3335201725404</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1100454618721151</v>
+        <v>0.1111009732938914</v>
       </c>
       <c r="T46">
-        <v>0.884362964981636</v>
+        <v>0.8988924770021448</v>
       </c>
       <c r="U46">
         <v>0.07606759442929167</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.649703804634368</v>
+        <v>6.501932608975826</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08985908600591251</v>
+        <v>0.08997813046237436</v>
       </c>
       <c r="C47">
-        <v>2196.315057699443</v>
+        <v>2157.011758281472</v>
       </c>
       <c r="D47">
-        <v>3240.610057699443</v>
+        <v>3231.877758281472</v>
       </c>
       <c r="E47">
-        <v>-410.605</v>
+        <v>-380.0339999999999</v>
       </c>
       <c r="F47">
-        <v>1375.695</v>
+        <v>1406.266</v>
       </c>
       <c r="G47">
         <v>331.4</v>
@@ -5141,28 +5141,28 @@
         <v>680.4</v>
       </c>
       <c r="M47">
-        <v>104.6458093184044</v>
+        <v>106.9712717477023</v>
       </c>
       <c r="N47">
-        <v>575.7541906815956</v>
+        <v>573.4287282522977</v>
       </c>
       <c r="O47">
-        <v>92.12067050905529</v>
+        <v>91.74859652036763</v>
       </c>
       <c r="P47">
-        <v>483.6335201725403</v>
+        <v>481.68013173193</v>
       </c>
       <c r="Q47">
-        <v>808.3335201725404</v>
+        <v>806.3801317319301</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1111009732938914</v>
+        <v>0.112195577731289</v>
       </c>
       <c r="T47">
-        <v>0.8988924770021448</v>
+        <v>0.9139601190974873</v>
       </c>
       <c r="U47">
         <v>0.07606759442929167</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.501932608975826</v>
+        <v>6.360586247911134</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08997813046237436</v>
+        <v>0.0900971749188362</v>
       </c>
       <c r="C48">
-        <v>2157.011758281472</v>
+        <v>2117.755393316535</v>
       </c>
       <c r="D48">
-        <v>3231.877758281472</v>
+        <v>3223.192393316535</v>
       </c>
       <c r="E48">
-        <v>-380.0339999999999</v>
+        <v>-349.463</v>
       </c>
       <c r="F48">
-        <v>1406.266</v>
+        <v>1436.837</v>
       </c>
       <c r="G48">
         <v>331.4</v>
@@ -5223,28 +5223,28 @@
         <v>680.4</v>
       </c>
       <c r="M48">
-        <v>106.9712717477023</v>
+        <v>109.2967341770002</v>
       </c>
       <c r="N48">
-        <v>573.4287282522977</v>
+        <v>571.1032658229998</v>
       </c>
       <c r="O48">
-        <v>91.74859652036763</v>
+        <v>91.37652253167997</v>
       </c>
       <c r="P48">
-        <v>481.68013173193</v>
+        <v>479.7267432913198</v>
       </c>
       <c r="Q48">
-        <v>806.3801317319301</v>
+        <v>804.4267432913199</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.112195577731289</v>
+        <v>0.1133314879965129</v>
       </c>
       <c r="T48">
-        <v>0.9139601190974873</v>
+        <v>0.9295963514605786</v>
       </c>
       <c r="U48">
         <v>0.07606759442929167</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.360586247911134</v>
+        <v>6.225254625615152</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.0900971749188362</v>
+        <v>0.09021621937529806</v>
       </c>
       <c r="C49">
-        <v>2117.755393316535</v>
+        <v>2078.545585423135</v>
       </c>
       <c r="D49">
-        <v>3223.192393316535</v>
+        <v>3214.553585423135</v>
       </c>
       <c r="E49">
-        <v>-349.463</v>
+        <v>-318.8919999999998</v>
       </c>
       <c r="F49">
-        <v>1436.837</v>
+        <v>1467.408</v>
       </c>
       <c r="G49">
         <v>331.4</v>
@@ -5305,28 +5305,28 @@
         <v>680.4</v>
       </c>
       <c r="M49">
-        <v>109.2967341770002</v>
+        <v>111.622196606298</v>
       </c>
       <c r="N49">
-        <v>571.1032658229998</v>
+        <v>568.7778033937019</v>
       </c>
       <c r="O49">
-        <v>91.37652253167997</v>
+        <v>91.00444854299231</v>
       </c>
       <c r="P49">
-        <v>479.7267432913198</v>
+        <v>477.7733548507096</v>
       </c>
       <c r="Q49">
-        <v>804.4267432913199</v>
+        <v>802.4733548507097</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1133314879965129</v>
+        <v>0.1145110871180916</v>
       </c>
       <c r="T49">
-        <v>0.9295963514605786</v>
+        <v>0.9458339773760965</v>
       </c>
       <c r="U49">
         <v>0.07606759442929167</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.225254625615152</v>
+        <v>6.095561820914836</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09021621937529806</v>
+        <v>0.09074686383175989</v>
       </c>
       <c r="C50">
-        <v>2078.545585423135</v>
+        <v>2010.023438342235</v>
       </c>
       <c r="D50">
-        <v>3214.553585423135</v>
+        <v>3176.602438342235</v>
       </c>
       <c r="E50">
-        <v>-318.8920000000001</v>
+        <v>-288.3209999999999</v>
       </c>
       <c r="F50">
-        <v>1467.408</v>
+        <v>1497.979</v>
       </c>
       <c r="G50">
         <v>331.4</v>
@@ -5387,45 +5387,45 @@
         <v>680.4</v>
       </c>
       <c r="M50">
-        <v>111.622196606298</v>
+        <v>115.4456380355959</v>
       </c>
       <c r="N50">
-        <v>568.7778033937019</v>
+        <v>564.954361964404</v>
       </c>
       <c r="O50">
-        <v>91.00444854299231</v>
+        <v>90.39269791430465</v>
       </c>
       <c r="P50">
-        <v>477.7733548507096</v>
+        <v>474.5616640500994</v>
       </c>
       <c r="Q50">
-        <v>802.4733548507097</v>
+        <v>799.2616640500994</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1145110871180916</v>
+        <v>0.1157369450287518</v>
       </c>
       <c r="T50">
-        <v>0.9458339773760964</v>
+        <v>0.96270837293536</v>
       </c>
       <c r="U50">
-        <v>0.07606759442929167</v>
+        <v>0.07706759442929167</v>
       </c>
       <c r="V50">
         <v>0.16</v>
       </c>
       <c r="W50">
-        <v>0.063896779320605</v>
+        <v>0.06473677932060501</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.095561820914837</v>
+        <v>5.893683049247897</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09074686383175989</v>
+        <v>0.09087430828822173</v>
       </c>
       <c r="C51">
-        <v>2010.023438342235</v>
+        <v>1970.470816959137</v>
       </c>
       <c r="D51">
-        <v>3176.602438342235</v>
+        <v>3167.620816959136</v>
       </c>
       <c r="E51">
-        <v>-288.3209999999999</v>
+        <v>-257.75</v>
       </c>
       <c r="F51">
-        <v>1497.979</v>
+        <v>1528.55</v>
       </c>
       <c r="G51">
         <v>331.4</v>
@@ -5469,28 +5469,28 @@
         <v>680.4</v>
       </c>
       <c r="M51">
-        <v>115.4456380355959</v>
+        <v>117.8016714648938</v>
       </c>
       <c r="N51">
-        <v>564.954361964404</v>
+        <v>562.5983285351062</v>
       </c>
       <c r="O51">
-        <v>90.39269791430465</v>
+        <v>90.015732565617</v>
       </c>
       <c r="P51">
-        <v>474.5616640500994</v>
+        <v>472.5825959694893</v>
       </c>
       <c r="Q51">
-        <v>799.2616640500994</v>
+        <v>797.2825959694893</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1157369450287518</v>
+        <v>0.1170118372558384</v>
       </c>
       <c r="T51">
-        <v>0.96270837293536</v>
+        <v>0.9802577443169942</v>
       </c>
       <c r="U51">
         <v>0.07706759442929167</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.893683049247897</v>
+        <v>5.77580938826294</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09087430828822173</v>
+        <v>0.09100175274468358</v>
       </c>
       <c r="C52">
-        <v>1970.470816959137</v>
+        <v>1930.968842189754</v>
       </c>
       <c r="D52">
-        <v>3167.620816959136</v>
+        <v>3158.689842189754</v>
       </c>
       <c r="E52">
-        <v>-257.75</v>
+        <v>-227.1790000000001</v>
       </c>
       <c r="F52">
-        <v>1528.55</v>
+        <v>1559.121</v>
       </c>
       <c r="G52">
         <v>331.4</v>
@@ -5551,28 +5551,28 @@
         <v>680.4</v>
       </c>
       <c r="M52">
-        <v>117.8016714648938</v>
+        <v>120.1577048941917</v>
       </c>
       <c r="N52">
-        <v>562.5983285351062</v>
+        <v>560.2422951058084</v>
       </c>
       <c r="O52">
-        <v>90.015732565617</v>
+        <v>89.63876721692934</v>
       </c>
       <c r="P52">
-        <v>472.5825959694893</v>
+        <v>470.603527888879</v>
       </c>
       <c r="Q52">
-        <v>797.2825959694893</v>
+        <v>795.303527888879</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1170118372558384</v>
+        <v>0.1183387659003572</v>
       </c>
       <c r="T52">
-        <v>0.9802577443169942</v>
+        <v>0.9985234165713481</v>
       </c>
       <c r="U52">
         <v>0.07706759442929167</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.77580938826294</v>
+        <v>5.662558223787197</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09100175274468358</v>
+        <v>0.09112919720114543</v>
       </c>
       <c r="C53">
-        <v>1930.968842189754</v>
+        <v>1891.517086850472</v>
       </c>
       <c r="D53">
-        <v>3158.689842189754</v>
+        <v>3149.809086850472</v>
       </c>
       <c r="E53">
-        <v>-227.1790000000001</v>
+        <v>-196.6079999999999</v>
       </c>
       <c r="F53">
-        <v>1559.121</v>
+        <v>1589.692</v>
       </c>
       <c r="G53">
         <v>331.4</v>
@@ -5633,28 +5633,28 @@
         <v>680.4</v>
       </c>
       <c r="M53">
-        <v>120.1577048941917</v>
+        <v>122.5137383234895</v>
       </c>
       <c r="N53">
-        <v>560.2422951058084</v>
+        <v>557.8862616765105</v>
       </c>
       <c r="O53">
-        <v>89.63876721692934</v>
+        <v>89.26180186824168</v>
       </c>
       <c r="P53">
-        <v>470.603527888879</v>
+        <v>468.6244598082688</v>
       </c>
       <c r="Q53">
-        <v>795.303527888879</v>
+        <v>793.3244598082688</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1183387659003572</v>
+        <v>0.1197209832383975</v>
       </c>
       <c r="T53">
-        <v>0.9985234165713481</v>
+        <v>1.017550158502967</v>
       </c>
       <c r="U53">
         <v>0.07706759442929167</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.662558223787197</v>
+        <v>5.553662873329749</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09112919720114543</v>
+        <v>0.09125664165760725</v>
       </c>
       <c r="C54">
-        <v>1891.517086850472</v>
+        <v>1852.115128548366</v>
       </c>
       <c r="D54">
-        <v>3149.809086850472</v>
+        <v>3140.978128548365</v>
       </c>
       <c r="E54">
-        <v>-196.6079999999999</v>
+        <v>-166.037</v>
       </c>
       <c r="F54">
-        <v>1589.692</v>
+        <v>1620.263</v>
       </c>
       <c r="G54">
         <v>331.4</v>
@@ -5715,28 +5715,28 @@
         <v>680.4</v>
       </c>
       <c r="M54">
-        <v>122.5137383234895</v>
+        <v>124.8697717527874</v>
       </c>
       <c r="N54">
-        <v>557.8862616765105</v>
+        <v>555.5302282472126</v>
       </c>
       <c r="O54">
-        <v>89.26180186824168</v>
+        <v>88.88483651955401</v>
       </c>
       <c r="P54">
-        <v>468.6244598082688</v>
+        <v>466.6453917276585</v>
       </c>
       <c r="Q54">
-        <v>793.3244598082688</v>
+        <v>791.3453917276586</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1197209832383975</v>
+        <v>0.1211620183355034</v>
       </c>
       <c r="T54">
-        <v>1.017550158502967</v>
+        <v>1.03738654902742</v>
       </c>
       <c r="U54">
         <v>0.07706759442929167</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.553662873329749</v>
+        <v>5.448876781380132</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09125664165760725</v>
+        <v>0.0913840861140691</v>
       </c>
       <c r="C55">
-        <v>1852.115128548366</v>
+        <v>1812.762549614223</v>
       </c>
       <c r="D55">
-        <v>3140.978128548365</v>
+        <v>3132.196549614223</v>
       </c>
       <c r="E55">
-        <v>-166.037</v>
+        <v>-135.4659999999999</v>
       </c>
       <c r="F55">
-        <v>1620.263</v>
+        <v>1650.834</v>
       </c>
       <c r="G55">
         <v>331.4</v>
@@ -5797,28 +5797,28 @@
         <v>680.4</v>
       </c>
       <c r="M55">
-        <v>124.8697717527874</v>
+        <v>127.2258051820853</v>
       </c>
       <c r="N55">
-        <v>555.5302282472126</v>
+        <v>553.1741948179147</v>
       </c>
       <c r="O55">
-        <v>88.88483651955401</v>
+        <v>88.50787117086635</v>
       </c>
       <c r="P55">
-        <v>466.6453917276585</v>
+        <v>464.6663236470483</v>
       </c>
       <c r="Q55">
-        <v>791.3453917276586</v>
+        <v>789.3663236470484</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1211620183355034</v>
+        <v>0.1226657071324835</v>
       </c>
       <c r="T55">
-        <v>1.03738654902742</v>
+        <v>1.058085391313807</v>
       </c>
       <c r="U55">
         <v>0.07706759442929167</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.448876781380132</v>
+        <v>5.347971655799018</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.0913840861140691</v>
+        <v>0.09151153057053094</v>
       </c>
       <c r="C56">
-        <v>1812.762549614223</v>
+        <v>1773.458937036719</v>
       </c>
       <c r="D56">
-        <v>3132.196549614223</v>
+        <v>3123.463937036719</v>
       </c>
       <c r="E56">
-        <v>-135.4659999999999</v>
+        <v>-104.895</v>
       </c>
       <c r="F56">
-        <v>1650.834</v>
+        <v>1681.405</v>
       </c>
       <c r="G56">
         <v>331.4</v>
@@ -5879,28 +5879,28 @@
         <v>680.4</v>
       </c>
       <c r="M56">
-        <v>127.2258051820853</v>
+        <v>129.5818386113832</v>
       </c>
       <c r="N56">
-        <v>553.1741948179147</v>
+        <v>550.8181613886168</v>
       </c>
       <c r="O56">
-        <v>88.50787117086635</v>
+        <v>88.13090582217869</v>
       </c>
       <c r="P56">
-        <v>464.6663236470483</v>
+        <v>462.6872555664381</v>
       </c>
       <c r="Q56">
-        <v>789.3663236470484</v>
+        <v>787.3872555664382</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1226657071324835</v>
+        <v>0.1242362265426626</v>
       </c>
       <c r="T56">
-        <v>1.058085391313807</v>
+        <v>1.079704182146255</v>
       </c>
       <c r="U56">
         <v>0.07706759442929167</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.347971655799018</v>
+        <v>5.250735807511763</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09151153057053094</v>
+        <v>0.09163897502699279</v>
       </c>
       <c r="C57">
-        <v>1773.458937036719</v>
+        <v>1734.203882397638</v>
       </c>
       <c r="D57">
-        <v>3123.463937036719</v>
+        <v>3114.779882397638</v>
       </c>
       <c r="E57">
-        <v>-104.895</v>
+        <v>-74.32399999999984</v>
       </c>
       <c r="F57">
-        <v>1681.405</v>
+        <v>1711.976</v>
       </c>
       <c r="G57">
         <v>331.4</v>
@@ -5961,28 +5961,28 @@
         <v>680.4</v>
       </c>
       <c r="M57">
-        <v>129.5818386113832</v>
+        <v>131.937872040681</v>
       </c>
       <c r="N57">
-        <v>550.8181613886168</v>
+        <v>548.4621279593189</v>
       </c>
       <c r="O57">
-        <v>88.13090582217869</v>
+        <v>87.75394047349103</v>
       </c>
       <c r="P57">
-        <v>462.6872555664381</v>
+        <v>460.7081874858279</v>
       </c>
       <c r="Q57">
-        <v>787.3872555664382</v>
+        <v>785.408187485828</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1242362265426626</v>
+        <v>0.1258781331987591</v>
       </c>
       <c r="T57">
-        <v>1.079704182146255</v>
+        <v>1.102305645289268</v>
       </c>
       <c r="U57">
         <v>0.07706759442929167</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.250735807511763</v>
+        <v>5.15697266809191</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09163897502699279</v>
+        <v>0.09176641948345463</v>
       </c>
       <c r="C58">
-        <v>1734.203882397638</v>
+        <v>1694.996981808224</v>
       </c>
       <c r="D58">
-        <v>3114.779882397638</v>
+        <v>3106.143981808224</v>
       </c>
       <c r="E58">
-        <v>-74.32399999999984</v>
+        <v>-43.75299999999993</v>
       </c>
       <c r="F58">
-        <v>1711.976</v>
+        <v>1742.547</v>
       </c>
       <c r="G58">
         <v>331.4</v>
@@ -6043,28 +6043,28 @@
         <v>680.4</v>
       </c>
       <c r="M58">
-        <v>131.937872040681</v>
+        <v>134.2939054699789</v>
       </c>
       <c r="N58">
-        <v>548.4621279593189</v>
+        <v>546.1060945300211</v>
       </c>
       <c r="O58">
-        <v>87.75394047349103</v>
+        <v>87.37697512480338</v>
       </c>
       <c r="P58">
-        <v>460.7081874858279</v>
+        <v>458.7291194052177</v>
       </c>
       <c r="Q58">
-        <v>785.408187485828</v>
+        <v>783.4291194052178</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1258781331987591</v>
+        <v>0.1275964076063018</v>
       </c>
       <c r="T58">
-        <v>1.102305645289268</v>
+        <v>1.125958339276143</v>
       </c>
       <c r="U58">
         <v>0.07706759442929167</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.15697266809191</v>
+        <v>5.066499463388544</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09176641948345463</v>
+        <v>0.09189386393991647</v>
       </c>
       <c r="C59">
-        <v>1694.996981808224</v>
+        <v>1655.837835846545</v>
       </c>
       <c r="D59">
-        <v>3106.143981808224</v>
+        <v>3097.555835846545</v>
       </c>
       <c r="E59">
-        <v>-43.75299999999993</v>
+        <v>-13.18199999999979</v>
       </c>
       <c r="F59">
-        <v>1742.547</v>
+        <v>1773.118</v>
       </c>
       <c r="G59">
         <v>331.4</v>
@@ -6125,28 +6125,28 @@
         <v>680.4</v>
       </c>
       <c r="M59">
-        <v>134.2939054699789</v>
+        <v>136.6499388992768</v>
       </c>
       <c r="N59">
-        <v>546.1060945300211</v>
+        <v>543.7500611007232</v>
       </c>
       <c r="O59">
-        <v>87.37697512480338</v>
+        <v>87.00000977611572</v>
       </c>
       <c r="P59">
-        <v>458.7291194052177</v>
+        <v>456.7500513246075</v>
       </c>
       <c r="Q59">
-        <v>783.4291194052178</v>
+        <v>781.4500513246076</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1275964076063018</v>
+        <v>0.1293965046046799</v>
       </c>
       <c r="T59">
-        <v>1.125958339276143</v>
+        <v>1.150737352024298</v>
       </c>
       <c r="U59">
         <v>0.07706759442929167</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.066499463388544</v>
+        <v>4.979146024364603</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09189386393991647</v>
+        <v>0.09202130839637832</v>
       </c>
       <c r="C60">
-        <v>1655.837835846545</v>
+        <v>1616.726049495923</v>
       </c>
       <c r="D60">
-        <v>3097.555835846545</v>
+        <v>3089.015049495923</v>
       </c>
       <c r="E60">
-        <v>-13.18200000000002</v>
+        <v>17.3889999999999</v>
       </c>
       <c r="F60">
-        <v>1773.118</v>
+        <v>1803.689</v>
       </c>
       <c r="G60">
         <v>331.4</v>
@@ -6207,28 +6207,28 @@
         <v>680.4</v>
       </c>
       <c r="M60">
-        <v>136.6499388992768</v>
+        <v>139.0059723285747</v>
       </c>
       <c r="N60">
-        <v>543.7500611007232</v>
+        <v>541.3940276714253</v>
       </c>
       <c r="O60">
-        <v>87.00000977611572</v>
+        <v>86.62304442742806</v>
       </c>
       <c r="P60">
-        <v>456.7500513246075</v>
+        <v>454.7709832439973</v>
       </c>
       <c r="Q60">
-        <v>781.4500513246076</v>
+        <v>779.4709832439974</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1293965046046799</v>
+        <v>0.131284411212735</v>
       </c>
       <c r="T60">
-        <v>1.150737352024297</v>
+        <v>1.17672509710163</v>
       </c>
       <c r="U60">
         <v>0.07706759442929167</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.979146024364603</v>
+        <v>4.894753718866898</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09202130839637832</v>
+        <v>0.09214875285284016</v>
       </c>
       <c r="C61">
-        <v>1616.726049495923</v>
+        <v>1577.661232084365</v>
       </c>
       <c r="D61">
-        <v>3089.015049495923</v>
+        <v>3080.521232084365</v>
       </c>
       <c r="E61">
-        <v>17.3889999999999</v>
+        <v>47.96000000000004</v>
       </c>
       <c r="F61">
-        <v>1803.689</v>
+        <v>1834.26</v>
       </c>
       <c r="G61">
         <v>331.4</v>
@@ -6289,28 +6289,28 @@
         <v>680.4</v>
       </c>
       <c r="M61">
-        <v>139.0059723285747</v>
+        <v>141.3620057578725</v>
       </c>
       <c r="N61">
-        <v>541.3940276714253</v>
+        <v>539.0379942421274</v>
       </c>
       <c r="O61">
-        <v>86.62304442742806</v>
+        <v>86.24607907874039</v>
       </c>
       <c r="P61">
-        <v>454.7709832439973</v>
+        <v>452.791915163387</v>
       </c>
       <c r="Q61">
-        <v>779.4709832439974</v>
+        <v>777.491915163387</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.131284411212735</v>
+        <v>0.1332667131511929</v>
       </c>
       <c r="T61">
-        <v>1.17672509710163</v>
+        <v>1.20401222943283</v>
       </c>
       <c r="U61">
         <v>0.07706759442929167</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.894753718866898</v>
+        <v>4.813174490219117</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09214875285284016</v>
+        <v>0.092276197309302</v>
       </c>
       <c r="C62">
-        <v>1577.661232084365</v>
+        <v>1538.642997224993</v>
       </c>
       <c r="D62">
-        <v>3080.521232084365</v>
+        <v>3072.073997224993</v>
       </c>
       <c r="E62">
-        <v>47.96000000000004</v>
+        <v>78.53099999999995</v>
       </c>
       <c r="F62">
-        <v>1834.26</v>
+        <v>1864.831</v>
       </c>
       <c r="G62">
         <v>331.4</v>
@@ -6371,28 +6371,28 @@
         <v>680.4</v>
       </c>
       <c r="M62">
-        <v>141.3620057578725</v>
+        <v>143.7180391871704</v>
       </c>
       <c r="N62">
-        <v>539.0379942421274</v>
+        <v>536.6819608128296</v>
       </c>
       <c r="O62">
-        <v>86.24607907874039</v>
+        <v>85.86911373005275</v>
       </c>
       <c r="P62">
-        <v>452.791915163387</v>
+        <v>450.8128470827769</v>
       </c>
       <c r="Q62">
-        <v>777.491915163387</v>
+        <v>775.5128470827769</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1332667131511929</v>
+        <v>0.1353506715993152</v>
       </c>
       <c r="T62">
-        <v>1.20401222943283</v>
+        <v>1.232698701883578</v>
       </c>
       <c r="U62">
         <v>0.07706759442929167</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.813174490219117</v>
+        <v>4.73426999037946</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.092276197309302</v>
+        <v>0.09240364176576385</v>
       </c>
       <c r="C63">
-        <v>1538.642997224993</v>
+        <v>1499.670962757456</v>
       </c>
       <c r="D63">
-        <v>3072.073997224993</v>
+        <v>3063.672962757456</v>
       </c>
       <c r="E63">
-        <v>78.53099999999995</v>
+        <v>109.1020000000001</v>
       </c>
       <c r="F63">
-        <v>1864.831</v>
+        <v>1895.402</v>
       </c>
       <c r="G63">
         <v>331.4</v>
@@ -6453,28 +6453,28 @@
         <v>680.4</v>
       </c>
       <c r="M63">
-        <v>143.7180391871704</v>
+        <v>146.0740726164683</v>
       </c>
       <c r="N63">
-        <v>536.6819608128296</v>
+        <v>534.3259273835317</v>
       </c>
       <c r="O63">
-        <v>85.86911373005275</v>
+        <v>85.49214838136508</v>
       </c>
       <c r="P63">
-        <v>450.8128470827769</v>
+        <v>448.8337790021666</v>
       </c>
       <c r="Q63">
-        <v>775.5128470827769</v>
+        <v>773.5337790021667</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1353506715993152</v>
+        <v>0.137544312071023</v>
       </c>
       <c r="T63">
-        <v>1.232698701883578</v>
+        <v>1.262894988673839</v>
       </c>
       <c r="U63">
         <v>0.07706759442929167</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.73426999037946</v>
+        <v>4.657910796986242</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09240364176576385</v>
+        <v>0.09253108622222569</v>
       </c>
       <c r="C64">
-        <v>1499.670962757456</v>
+        <v>1460.744750690295</v>
       </c>
       <c r="D64">
-        <v>3063.672962757456</v>
+        <v>3055.317750690295</v>
       </c>
       <c r="E64">
-        <v>109.1020000000001</v>
+        <v>139.673</v>
       </c>
       <c r="F64">
-        <v>1895.402</v>
+        <v>1925.973</v>
       </c>
       <c r="G64">
         <v>331.4</v>
@@ -6535,28 +6535,28 @@
         <v>680.4</v>
       </c>
       <c r="M64">
-        <v>146.0740726164683</v>
+        <v>148.4301060457662</v>
       </c>
       <c r="N64">
-        <v>534.3259273835317</v>
+        <v>531.9698939542338</v>
       </c>
       <c r="O64">
-        <v>85.49214838136508</v>
+        <v>85.11518303267742</v>
       </c>
       <c r="P64">
-        <v>448.8337790021666</v>
+        <v>446.8547109215564</v>
       </c>
       <c r="Q64">
-        <v>773.5337790021667</v>
+        <v>771.5547109215565</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.137544312071023</v>
+        <v>0.1398565277033636</v>
       </c>
       <c r="T64">
-        <v>1.262894988673839</v>
+        <v>1.294723507182493</v>
       </c>
       <c r="U64">
         <v>0.07706759442929167</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.657910796986242</v>
+        <v>4.583975704970587</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09253108622222569</v>
+        <v>0.09265853067868753</v>
       </c>
       <c r="C65">
-        <v>1460.744750690295</v>
+        <v>1421.863987144252</v>
       </c>
       <c r="D65">
-        <v>3055.317750690295</v>
+        <v>3047.007987144252</v>
       </c>
       <c r="E65">
-        <v>139.673</v>
+        <v>170.2439999999999</v>
       </c>
       <c r="F65">
-        <v>1925.973</v>
+        <v>1956.544</v>
       </c>
       <c r="G65">
         <v>331.4</v>
@@ -6617,28 +6617,28 @@
         <v>680.4</v>
       </c>
       <c r="M65">
-        <v>148.4301060457662</v>
+        <v>150.786139475064</v>
       </c>
       <c r="N65">
-        <v>531.9698939542338</v>
+        <v>529.6138605249359</v>
       </c>
       <c r="O65">
-        <v>85.11518303267742</v>
+        <v>84.73821768398976</v>
       </c>
       <c r="P65">
-        <v>446.8547109215564</v>
+        <v>444.8756428409462</v>
       </c>
       <c r="Q65">
-        <v>771.5547109215565</v>
+        <v>769.5756428409462</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1398565277033636</v>
+        <v>0.1422971997597231</v>
       </c>
       <c r="T65">
-        <v>1.294723507182493</v>
+        <v>1.328320276719405</v>
       </c>
       <c r="U65">
         <v>0.07706759442929167</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.583975704970587</v>
+        <v>4.512351084580422</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09265853067868753</v>
+        <v>0.09415097513514938</v>
       </c>
       <c r="C66">
-        <v>1421.863987144252</v>
+        <v>1297.241312560702</v>
       </c>
       <c r="D66">
-        <v>3047.007987144252</v>
+        <v>2952.956312560702</v>
       </c>
       <c r="E66">
-        <v>170.2439999999999</v>
+        <v>200.8150000000001</v>
       </c>
       <c r="F66">
-        <v>1956.544</v>
+        <v>1987.115</v>
       </c>
       <c r="G66">
         <v>331.4</v>
@@ -6699,45 +6699,45 @@
         <v>680.4</v>
       </c>
       <c r="M66">
-        <v>150.786139475064</v>
+        <v>158.1099604043619</v>
       </c>
       <c r="N66">
-        <v>529.6138605249359</v>
+        <v>522.2900395956381</v>
       </c>
       <c r="O66">
-        <v>84.73821768398976</v>
+        <v>83.56640633530209</v>
       </c>
       <c r="P66">
-        <v>444.8756428409462</v>
+        <v>438.723633260336</v>
       </c>
       <c r="Q66">
-        <v>769.5756428409462</v>
+        <v>763.423633260336</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1422971997597231</v>
+        <v>0.1448773387907318</v>
       </c>
       <c r="T66">
-        <v>1.328320276719405</v>
+        <v>1.363836861658427</v>
       </c>
       <c r="U66">
-        <v>0.07706759442929167</v>
+        <v>0.07956759442929168</v>
       </c>
       <c r="V66">
         <v>0.16</v>
       </c>
       <c r="W66">
-        <v>0.06473677932060501</v>
+        <v>0.066836779320605</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.512351084580422</v>
+        <v>4.303334200197732</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09415097513514938</v>
+        <v>0.09429941959161123</v>
       </c>
       <c r="C67">
-        <v>1297.241312560702</v>
+        <v>1257.632060176142</v>
       </c>
       <c r="D67">
-        <v>2952.956312560702</v>
+        <v>2943.918060176141</v>
       </c>
       <c r="E67">
-        <v>200.8150000000001</v>
+        <v>231.386</v>
       </c>
       <c r="F67">
-        <v>1987.115</v>
+        <v>2017.686</v>
       </c>
       <c r="G67">
         <v>331.4</v>
@@ -6781,28 +6781,28 @@
         <v>680.4</v>
       </c>
       <c r="M67">
-        <v>158.1099604043619</v>
+        <v>160.5424213336598</v>
       </c>
       <c r="N67">
-        <v>522.2900395956381</v>
+        <v>519.8575786663401</v>
       </c>
       <c r="O67">
-        <v>83.56640633530209</v>
+        <v>83.17721258661443</v>
       </c>
       <c r="P67">
-        <v>438.723633260336</v>
+        <v>436.6803660797257</v>
       </c>
       <c r="Q67">
-        <v>763.423633260336</v>
+        <v>761.3803660797257</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1448773387907318</v>
+        <v>0.1476092507059174</v>
       </c>
       <c r="T67">
-        <v>1.363836861658427</v>
+        <v>1.401442657476214</v>
       </c>
       <c r="U67">
         <v>0.07956759442929168</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.303334200197732</v>
+        <v>4.238132166861403</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09429941959161123</v>
+        <v>0.09444786404807305</v>
       </c>
       <c r="C68">
-        <v>1257.632060176142</v>
+        <v>1218.077966573529</v>
       </c>
       <c r="D68">
-        <v>2943.918060176141</v>
+        <v>2934.934966573529</v>
       </c>
       <c r="E68">
-        <v>231.386</v>
+        <v>261.9570000000001</v>
       </c>
       <c r="F68">
-        <v>2017.686</v>
+        <v>2048.257</v>
       </c>
       <c r="G68">
         <v>331.4</v>
@@ -6863,28 +6863,28 @@
         <v>680.4</v>
       </c>
       <c r="M68">
-        <v>160.5424213336598</v>
+        <v>162.9748822629577</v>
       </c>
       <c r="N68">
-        <v>519.8575786663401</v>
+        <v>517.4251177370422</v>
       </c>
       <c r="O68">
-        <v>83.17721258661443</v>
+        <v>82.78801883792676</v>
       </c>
       <c r="P68">
-        <v>436.6803660797257</v>
+        <v>434.6370988991155</v>
       </c>
       <c r="Q68">
-        <v>761.3803660797257</v>
+        <v>759.3370988991155</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1476092507059174</v>
+        <v>0.1505067330402052</v>
       </c>
       <c r="T68">
-        <v>1.401442657476214</v>
+        <v>1.441327592434474</v>
       </c>
       <c r="U68">
         <v>0.07956759442929168</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.238132166861403</v>
+        <v>4.174876462878396</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09444786404807305</v>
+        <v>0.09459630850453489</v>
       </c>
       <c r="C69">
-        <v>1218.077966573529</v>
+        <v>1178.57852835318</v>
       </c>
       <c r="D69">
-        <v>2934.934966573529</v>
+        <v>2926.006528353179</v>
       </c>
       <c r="E69">
-        <v>261.9570000000001</v>
+        <v>292.528</v>
       </c>
       <c r="F69">
-        <v>2048.257</v>
+        <v>2078.828</v>
       </c>
       <c r="G69">
         <v>331.4</v>
@@ -6945,28 +6945,28 @@
         <v>680.4</v>
       </c>
       <c r="M69">
-        <v>162.9748822629577</v>
+        <v>165.4073431922556</v>
       </c>
       <c r="N69">
-        <v>517.4251177370422</v>
+        <v>514.9926568077444</v>
       </c>
       <c r="O69">
-        <v>82.78801883792676</v>
+        <v>82.39882508923911</v>
       </c>
       <c r="P69">
-        <v>434.6370988991155</v>
+        <v>432.5938317185053</v>
       </c>
       <c r="Q69">
-        <v>759.3370988991155</v>
+        <v>757.2938317185053</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1505067330402052</v>
+        <v>0.1535853080203859</v>
       </c>
       <c r="T69">
-        <v>1.441327592434474</v>
+        <v>1.483705335827624</v>
       </c>
       <c r="U69">
         <v>0.07956759442929168</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.174876462878396</v>
+        <v>4.113481220777244</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09459630850453489</v>
+        <v>0.09474475296099674</v>
       </c>
       <c r="C70">
-        <v>1178.57852835318</v>
+        <v>1139.133248222451</v>
       </c>
       <c r="D70">
-        <v>2926.006528353179</v>
+        <v>2917.13224822245</v>
       </c>
       <c r="E70">
-        <v>292.528</v>
+        <v>323.0989999999999</v>
       </c>
       <c r="F70">
-        <v>2078.828</v>
+        <v>2109.399</v>
       </c>
       <c r="G70">
         <v>331.4</v>
@@ -7027,28 +7027,28 @@
         <v>680.4</v>
       </c>
       <c r="M70">
-        <v>165.4073431922556</v>
+        <v>167.8398041215534</v>
       </c>
       <c r="N70">
-        <v>514.9926568077444</v>
+        <v>512.5601958784466</v>
       </c>
       <c r="O70">
-        <v>82.39882508923911</v>
+        <v>82.00963134055146</v>
       </c>
       <c r="P70">
-        <v>432.5938317185053</v>
+        <v>430.5505645378952</v>
       </c>
       <c r="Q70">
-        <v>757.2938317185053</v>
+        <v>755.2505645378952</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1535853080203859</v>
+        <v>0.1568625007412235</v>
       </c>
       <c r="T70">
-        <v>1.483705335827624</v>
+        <v>1.528817127181624</v>
       </c>
       <c r="U70">
         <v>0.07956759442929168</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.113481220777244</v>
+        <v>4.053865550910908</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09474475296099674</v>
+        <v>0.09695119741745858</v>
       </c>
       <c r="C71">
-        <v>1139.133248222451</v>
+        <v>982.7296068997734</v>
       </c>
       <c r="D71">
-        <v>2917.13224822245</v>
+        <v>2791.299606899774</v>
       </c>
       <c r="E71">
-        <v>323.0989999999999</v>
+        <v>353.6700000000003</v>
       </c>
       <c r="F71">
-        <v>2109.399</v>
+        <v>2139.97</v>
       </c>
       <c r="G71">
         <v>331.4</v>
@@ -7109,45 +7109,45 @@
         <v>680.4</v>
       </c>
       <c r="M71">
-        <v>167.8398041215534</v>
+        <v>177.7621600508513</v>
       </c>
       <c r="N71">
-        <v>512.5601958784466</v>
+        <v>502.6378399491487</v>
       </c>
       <c r="O71">
-        <v>82.00963134055146</v>
+        <v>80.42205439186378</v>
       </c>
       <c r="P71">
-        <v>430.5505645378952</v>
+        <v>422.2157855572849</v>
       </c>
       <c r="Q71">
-        <v>755.2505645378952</v>
+        <v>746.9157855572849</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1568625007412235</v>
+        <v>0.1603581729767836</v>
       </c>
       <c r="T71">
-        <v>1.528817127181624</v>
+        <v>1.576936371292556</v>
       </c>
       <c r="U71">
-        <v>0.07956759442929168</v>
+        <v>0.08306759442929168</v>
       </c>
       <c r="V71">
         <v>0.16</v>
       </c>
       <c r="W71">
-        <v>0.066836779320605</v>
+        <v>0.06977677932060501</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.053865550910908</v>
+        <v>3.827586252357431</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09695119741745858</v>
+        <v>0.09712904187392044</v>
       </c>
       <c r="C72">
-        <v>982.7296068997734</v>
+        <v>942.4873341994062</v>
       </c>
       <c r="D72">
-        <v>2791.299606899774</v>
+        <v>2781.628334199406</v>
       </c>
       <c r="E72">
-        <v>353.6700000000003</v>
+        <v>384.2410000000002</v>
       </c>
       <c r="F72">
-        <v>2139.97</v>
+        <v>2170.541</v>
       </c>
       <c r="G72">
         <v>331.4</v>
@@ -7191,28 +7191,28 @@
         <v>680.4</v>
       </c>
       <c r="M72">
-        <v>177.7621600508513</v>
+        <v>180.3016194801492</v>
       </c>
       <c r="N72">
-        <v>502.6378399491487</v>
+        <v>500.0983805198508</v>
       </c>
       <c r="O72">
-        <v>80.42205439186378</v>
+        <v>80.01574088317612</v>
       </c>
       <c r="P72">
-        <v>422.2157855572849</v>
+        <v>420.0826396366746</v>
       </c>
       <c r="Q72">
-        <v>746.9157855572849</v>
+        <v>744.7826396366747</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1603581729767836</v>
+        <v>0.1640949260561755</v>
       </c>
       <c r="T72">
-        <v>1.576936371292556</v>
+        <v>1.628374183962864</v>
       </c>
       <c r="U72">
         <v>0.08306759442929168</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.827586252357431</v>
+        <v>3.77367658683127</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09712904187392044</v>
+        <v>0.09730688633038229</v>
       </c>
       <c r="C73">
-        <v>942.4873341994066</v>
+        <v>902.31184799534</v>
       </c>
       <c r="D73">
-        <v>2781.628334199406</v>
+        <v>2772.02384799534</v>
       </c>
       <c r="E73">
-        <v>384.2409999999998</v>
+        <v>414.8120000000001</v>
       </c>
       <c r="F73">
-        <v>2170.541</v>
+        <v>2201.112</v>
       </c>
       <c r="G73">
         <v>331.4</v>
@@ -7273,28 +7273,28 @@
         <v>680.4</v>
       </c>
       <c r="M73">
-        <v>180.3016194801492</v>
+        <v>182.8410789094471</v>
       </c>
       <c r="N73">
-        <v>500.0983805198508</v>
+        <v>497.5589210905529</v>
       </c>
       <c r="O73">
-        <v>80.01574088317614</v>
+        <v>79.60942737448846</v>
       </c>
       <c r="P73">
-        <v>420.0826396366747</v>
+        <v>417.9494937160644</v>
       </c>
       <c r="Q73">
-        <v>744.7826396366747</v>
+        <v>742.6494937160644</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1640949260561754</v>
+        <v>0.1680985900698095</v>
       </c>
       <c r="T73">
-        <v>1.628374183962863</v>
+        <v>1.68348612610962</v>
       </c>
       <c r="U73">
         <v>0.08306759442929168</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.773676586831272</v>
+        <v>3.72126441201417</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09730688633038229</v>
+        <v>0.09748473078684411</v>
       </c>
       <c r="C74">
-        <v>902.31184799534</v>
+        <v>862.2024588610498</v>
       </c>
       <c r="D74">
-        <v>2772.02384799534</v>
+        <v>2762.48545886105</v>
       </c>
       <c r="E74">
-        <v>414.8120000000001</v>
+        <v>445.383</v>
       </c>
       <c r="F74">
-        <v>2201.112</v>
+        <v>2231.683</v>
       </c>
       <c r="G74">
         <v>331.4</v>
@@ -7355,28 +7355,28 @@
         <v>680.4</v>
       </c>
       <c r="M74">
-        <v>182.8410789094471</v>
+        <v>185.3805383387449</v>
       </c>
       <c r="N74">
-        <v>497.5589210905529</v>
+        <v>495.019461661255</v>
       </c>
       <c r="O74">
-        <v>79.60942737448846</v>
+        <v>79.2031138658008</v>
       </c>
       <c r="P74">
-        <v>417.9494937160644</v>
+        <v>415.8163477954542</v>
       </c>
       <c r="Q74">
-        <v>742.6494937160644</v>
+        <v>740.5163477954543</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1680985900698095</v>
+        <v>0.1723988217881572</v>
       </c>
       <c r="T74">
-        <v>1.68348612610962</v>
+        <v>1.742680434341323</v>
       </c>
       <c r="U74">
         <v>0.08306759442929168</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.72126441201417</v>
+        <v>3.670288187192058</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09748473078684411</v>
+        <v>0.09766257524330596</v>
       </c>
       <c r="C75">
-        <v>862.2024588610498</v>
+        <v>822.1584868265904</v>
       </c>
       <c r="D75">
-        <v>2762.48545886105</v>
+        <v>2753.01248682659</v>
       </c>
       <c r="E75">
-        <v>445.383</v>
+        <v>475.954</v>
       </c>
       <c r="F75">
-        <v>2231.683</v>
+        <v>2262.254</v>
       </c>
       <c r="G75">
         <v>331.4</v>
@@ -7437,28 +7437,28 @@
         <v>680.4</v>
       </c>
       <c r="M75">
-        <v>185.3805383387449</v>
+        <v>187.9199977680428</v>
       </c>
       <c r="N75">
-        <v>495.019461661255</v>
+        <v>492.4800022319572</v>
       </c>
       <c r="O75">
-        <v>79.2031138658008</v>
+        <v>78.79680035711316</v>
       </c>
       <c r="P75">
-        <v>415.8163477954542</v>
+        <v>413.683201874844</v>
       </c>
       <c r="Q75">
-        <v>740.5163477954543</v>
+        <v>738.3832018748441</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1723988217881572</v>
+        <v>0.1770298405617625</v>
       </c>
       <c r="T75">
-        <v>1.742680434341323</v>
+        <v>1.806428150898541</v>
       </c>
       <c r="U75">
         <v>0.08306759442929168</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.670288187192058</v>
+        <v>3.62068969817595</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09766257524330596</v>
+        <v>0.09784041969976781</v>
       </c>
       <c r="C76">
-        <v>822.1584868265904</v>
+        <v>782.1792612170157</v>
       </c>
       <c r="D76">
-        <v>2753.01248682659</v>
+        <v>2743.604261217015</v>
       </c>
       <c r="E76">
-        <v>475.954</v>
+        <v>506.5249999999999</v>
       </c>
       <c r="F76">
-        <v>2262.254</v>
+        <v>2292.825</v>
       </c>
       <c r="G76">
         <v>331.4</v>
@@ -7519,28 +7519,28 @@
         <v>680.4</v>
       </c>
       <c r="M76">
-        <v>187.9199977680428</v>
+        <v>190.4594571973407</v>
       </c>
       <c r="N76">
-        <v>492.4800022319572</v>
+        <v>489.9405428026593</v>
       </c>
       <c r="O76">
-        <v>78.79680035711316</v>
+        <v>78.3904868484255</v>
       </c>
       <c r="P76">
-        <v>413.683201874844</v>
+        <v>411.5500559542338</v>
       </c>
       <c r="Q76">
-        <v>738.3832018748441</v>
+        <v>736.2500559542339</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1770298405617625</v>
+        <v>0.1820313408372562</v>
       </c>
       <c r="T76">
-        <v>1.806428150898541</v>
+        <v>1.875275684780337</v>
       </c>
       <c r="U76">
         <v>0.08306759442929168</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.62068969817595</v>
+        <v>3.572413835533604</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09784041969976781</v>
+        <v>0.09801826415622965</v>
       </c>
       <c r="C77">
-        <v>782.1792612170157</v>
+        <v>742.2641204940937</v>
       </c>
       <c r="D77">
-        <v>2743.604261217015</v>
+        <v>2734.260120494093</v>
       </c>
       <c r="E77">
-        <v>506.5249999999999</v>
+        <v>537.0959999999998</v>
       </c>
       <c r="F77">
-        <v>2292.825</v>
+        <v>2323.396</v>
       </c>
       <c r="G77">
         <v>331.4</v>
@@ -7601,28 +7601,28 @@
         <v>680.4</v>
       </c>
       <c r="M77">
-        <v>190.4594571973407</v>
+        <v>192.9989166266386</v>
       </c>
       <c r="N77">
-        <v>489.9405428026593</v>
+        <v>487.4010833733614</v>
       </c>
       <c r="O77">
-        <v>78.3904868484255</v>
+        <v>77.98417333973782</v>
       </c>
       <c r="P77">
-        <v>411.5500559542338</v>
+        <v>409.4169100336236</v>
       </c>
       <c r="Q77">
-        <v>736.2500559542339</v>
+        <v>734.1169100336236</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1820313408372562</v>
+        <v>0.1874496328023743</v>
       </c>
       <c r="T77">
-        <v>1.875275684780337</v>
+        <v>1.949860513152282</v>
       </c>
       <c r="U77">
         <v>0.08306759442929168</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.572413835533604</v>
+        <v>3.525408390329214</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09801826415622965</v>
+        <v>0.1000071486126915</v>
       </c>
       <c r="C78">
-        <v>742.2641204940937</v>
+        <v>611.37189732057</v>
       </c>
       <c r="D78">
-        <v>2734.260120494093</v>
+        <v>2633.93889732057</v>
       </c>
       <c r="E78">
-        <v>537.0959999999998</v>
+        <v>567.6670000000001</v>
       </c>
       <c r="F78">
-        <v>2323.396</v>
+        <v>2353.967</v>
       </c>
       <c r="G78">
         <v>331.4</v>
@@ -7683,45 +7683,45 @@
         <v>680.4</v>
       </c>
       <c r="M78">
-        <v>192.9989166266386</v>
+        <v>202.1294836559364</v>
       </c>
       <c r="N78">
-        <v>487.4010833733614</v>
+        <v>478.2705163440635</v>
       </c>
       <c r="O78">
-        <v>77.98417333973782</v>
+        <v>76.52328261505016</v>
       </c>
       <c r="P78">
-        <v>409.4169100336236</v>
+        <v>401.7472337290134</v>
       </c>
       <c r="Q78">
-        <v>734.1169100336236</v>
+        <v>726.4472337290134</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1874496328023743</v>
+        <v>0.1933390805905462</v>
       </c>
       <c r="T78">
-        <v>1.949860513152282</v>
+        <v>2.030930978773962</v>
       </c>
       <c r="U78">
-        <v>0.08306759442929168</v>
+        <v>0.08586759442929168</v>
       </c>
       <c r="V78">
         <v>0.16</v>
       </c>
       <c r="W78">
-        <v>0.06977677932060501</v>
+        <v>0.072128779320605</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>3.525408390329214</v>
+        <v>3.366159096107783</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1000071486126915</v>
+        <v>0.1002085130691533</v>
       </c>
       <c r="C79">
-        <v>611.37189732057</v>
+        <v>571.0527596764018</v>
       </c>
       <c r="D79">
-        <v>2633.93889732057</v>
+        <v>2624.190759676402</v>
       </c>
       <c r="E79">
-        <v>567.6670000000001</v>
+        <v>598.2380000000001</v>
       </c>
       <c r="F79">
-        <v>2353.967</v>
+        <v>2384.538</v>
       </c>
       <c r="G79">
         <v>331.4</v>
@@ -7765,28 +7765,28 @@
         <v>680.4</v>
       </c>
       <c r="M79">
-        <v>202.1294836559364</v>
+        <v>204.7545418852343</v>
       </c>
       <c r="N79">
-        <v>478.2705163440635</v>
+        <v>475.6454581147657</v>
       </c>
       <c r="O79">
-        <v>76.52328261505016</v>
+        <v>76.10327329836251</v>
       </c>
       <c r="P79">
-        <v>401.7472337290134</v>
+        <v>399.5421848164032</v>
       </c>
       <c r="Q79">
-        <v>726.4472337290134</v>
+        <v>724.2421848164032</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1933390805905462</v>
+        <v>0.1997639327230974</v>
       </c>
       <c r="T79">
-        <v>2.030930978773962</v>
+        <v>2.119371486724885</v>
       </c>
       <c r="U79">
         <v>0.08586759442929168</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.366159096107783</v>
+        <v>3.323003210260248</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1002085130691533</v>
+        <v>0.1004098775256152</v>
       </c>
       <c r="C80">
-        <v>571.0527596764018</v>
+        <v>530.8055111675749</v>
       </c>
       <c r="D80">
-        <v>2624.190759676402</v>
+        <v>2614.514511167575</v>
       </c>
       <c r="E80">
-        <v>598.2380000000001</v>
+        <v>628.809</v>
       </c>
       <c r="F80">
-        <v>2384.538</v>
+        <v>2415.109</v>
       </c>
       <c r="G80">
         <v>331.4</v>
@@ -7847,28 +7847,28 @@
         <v>680.4</v>
       </c>
       <c r="M80">
-        <v>204.7545418852343</v>
+        <v>207.3796001145322</v>
       </c>
       <c r="N80">
-        <v>475.6454581147657</v>
+        <v>473.0203998854678</v>
       </c>
       <c r="O80">
-        <v>76.10327329836251</v>
+        <v>75.68326398167484</v>
       </c>
       <c r="P80">
-        <v>399.5421848164032</v>
+        <v>397.337135903793</v>
       </c>
       <c r="Q80">
-        <v>724.2421848164032</v>
+        <v>722.037135903793</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1997639327230974</v>
+        <v>0.2068006755349391</v>
       </c>
       <c r="T80">
-        <v>2.119371486724885</v>
+        <v>2.216234900194944</v>
       </c>
       <c r="U80">
         <v>0.08586759442929168</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.323003210260248</v>
+        <v>3.280939878484801</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1004098775256152</v>
+        <v>0.100611241982077</v>
       </c>
       <c r="C81">
-        <v>530.8055111675749</v>
+        <v>490.6293594794411</v>
       </c>
       <c r="D81">
-        <v>2614.514511167575</v>
+        <v>2604.909359479441</v>
       </c>
       <c r="E81">
-        <v>628.809</v>
+        <v>659.3799999999999</v>
       </c>
       <c r="F81">
-        <v>2415.109</v>
+        <v>2445.68</v>
       </c>
       <c r="G81">
         <v>331.4</v>
@@ -7929,28 +7929,28 @@
         <v>680.4</v>
       </c>
       <c r="M81">
-        <v>207.3796001145322</v>
+        <v>210.00465834383</v>
       </c>
       <c r="N81">
-        <v>473.0203998854678</v>
+        <v>470.3953416561699</v>
       </c>
       <c r="O81">
-        <v>75.68326398167484</v>
+        <v>75.26325466498719</v>
       </c>
       <c r="P81">
-        <v>397.337135903793</v>
+        <v>395.1320869911827</v>
       </c>
       <c r="Q81">
-        <v>722.037135903793</v>
+        <v>719.8320869911828</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2068006755349391</v>
+        <v>0.2145410926279651</v>
       </c>
       <c r="T81">
-        <v>2.216234900194944</v>
+        <v>2.322784655012009</v>
       </c>
       <c r="U81">
         <v>0.08586759442929168</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.280939878484801</v>
+        <v>3.239928130003742</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.100611241982077</v>
+        <v>0.1008126064385389</v>
       </c>
       <c r="C82">
-        <v>490.6293594794411</v>
+        <v>450.5235238978908</v>
       </c>
       <c r="D82">
-        <v>2604.909359479441</v>
+        <v>2595.374523897891</v>
       </c>
       <c r="E82">
-        <v>659.3799999999999</v>
+        <v>689.9510000000002</v>
       </c>
       <c r="F82">
-        <v>2445.68</v>
+        <v>2476.251</v>
       </c>
       <c r="G82">
         <v>331.4</v>
@@ -8011,28 +8011,28 @@
         <v>680.4</v>
       </c>
       <c r="M82">
-        <v>210.00465834383</v>
+        <v>212.629716573128</v>
       </c>
       <c r="N82">
-        <v>470.3953416561699</v>
+        <v>467.770283426872</v>
       </c>
       <c r="O82">
-        <v>75.26325466498719</v>
+        <v>74.84324534829953</v>
       </c>
       <c r="P82">
-        <v>395.1320869911827</v>
+        <v>392.9270380785725</v>
       </c>
       <c r="Q82">
-        <v>719.8320869911828</v>
+        <v>717.6270380785725</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2145410926279651</v>
+        <v>0.2230962904676253</v>
       </c>
       <c r="T82">
-        <v>2.322784655012009</v>
+        <v>2.440550173494028</v>
       </c>
       <c r="U82">
         <v>0.08586759442929168</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.239928130003742</v>
+        <v>3.199929017287646</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1008126064385389</v>
+        <v>0.1010139708950007</v>
       </c>
       <c r="C83">
-        <v>450.5235238978908</v>
+        <v>410.4872350978262</v>
       </c>
       <c r="D83">
-        <v>2595.374523897891</v>
+        <v>2585.909235097826</v>
       </c>
       <c r="E83">
-        <v>689.9510000000002</v>
+        <v>720.5220000000002</v>
       </c>
       <c r="F83">
-        <v>2476.251</v>
+        <v>2506.822</v>
       </c>
       <c r="G83">
         <v>331.4</v>
@@ -8093,28 +8093,28 @@
         <v>680.4</v>
       </c>
       <c r="M83">
-        <v>212.629716573128</v>
+        <v>215.2547748024258</v>
       </c>
       <c r="N83">
-        <v>467.770283426872</v>
+        <v>465.1452251975742</v>
       </c>
       <c r="O83">
-        <v>74.84324534829953</v>
+        <v>74.42323603161186</v>
       </c>
       <c r="P83">
-        <v>392.9270380785725</v>
+        <v>390.7219891659623</v>
       </c>
       <c r="Q83">
-        <v>717.6270380785725</v>
+        <v>715.4219891659624</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2230962904676253</v>
+        <v>0.2326020658450256</v>
       </c>
       <c r="T83">
-        <v>2.440550173494028</v>
+        <v>2.571400749585159</v>
       </c>
       <c r="U83">
         <v>0.08586759442929168</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.199929017287646</v>
+        <v>3.160905492686577</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1010139708950007</v>
+        <v>0.1012153353514625</v>
       </c>
       <c r="C84">
-        <v>410.4872350978262</v>
+        <v>370.5197349362256</v>
       </c>
       <c r="D84">
-        <v>2585.909235097826</v>
+        <v>2576.512734936226</v>
       </c>
       <c r="E84">
-        <v>720.5220000000002</v>
+        <v>751.0930000000001</v>
       </c>
       <c r="F84">
-        <v>2506.822</v>
+        <v>2537.393</v>
       </c>
       <c r="G84">
         <v>331.4</v>
@@ -8175,28 +8175,28 @@
         <v>680.4</v>
       </c>
       <c r="M84">
-        <v>215.2547748024258</v>
+        <v>217.8798330317237</v>
       </c>
       <c r="N84">
-        <v>465.1452251975742</v>
+        <v>462.5201669682763</v>
       </c>
       <c r="O84">
-        <v>74.42323603161186</v>
+        <v>74.00322671492421</v>
       </c>
       <c r="P84">
-        <v>390.7219891659623</v>
+        <v>388.5169402533521</v>
       </c>
       <c r="Q84">
-        <v>715.4219891659624</v>
+        <v>713.216940253352</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2326020658450256</v>
+        <v>0.2432261677374141</v>
       </c>
       <c r="T84">
-        <v>2.571400749585159</v>
+        <v>2.717645511098778</v>
       </c>
       <c r="U84">
         <v>0.08586759442929168</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.160905492686577</v>
+        <v>3.12282229397951</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1012153353514625</v>
+        <v>0.1014166998079244</v>
       </c>
       <c r="C85">
-        <v>370.5197349362256</v>
+        <v>330.6202762497301</v>
       </c>
       <c r="D85">
-        <v>2576.512734936226</v>
+        <v>2567.18427624973</v>
       </c>
       <c r="E85">
-        <v>751.0930000000001</v>
+        <v>781.664</v>
       </c>
       <c r="F85">
-        <v>2537.393</v>
+        <v>2567.964</v>
       </c>
       <c r="G85">
         <v>331.4</v>
@@ -8257,28 +8257,28 @@
         <v>680.4</v>
       </c>
       <c r="M85">
-        <v>217.8798330317237</v>
+        <v>220.5048912610216</v>
       </c>
       <c r="N85">
-        <v>462.5201669682763</v>
+        <v>459.8951087389784</v>
       </c>
       <c r="O85">
-        <v>74.00322671492421</v>
+        <v>73.58321739823656</v>
       </c>
       <c r="P85">
-        <v>388.5169402533521</v>
+        <v>386.3118913407419</v>
       </c>
       <c r="Q85">
-        <v>713.216940253352</v>
+        <v>711.0118913407418</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2432261677374141</v>
+        <v>0.2551782823663512</v>
       </c>
       <c r="T85">
-        <v>2.717645511098778</v>
+        <v>2.882170867801598</v>
       </c>
       <c r="U85">
         <v>0.08586759442929168</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.12282229397951</v>
+        <v>3.085645838098801</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1014166998079244</v>
+        <v>0.1016180642643862</v>
       </c>
       <c r="C86">
-        <v>330.6202762497301</v>
+        <v>290.7881226565873</v>
       </c>
       <c r="D86">
-        <v>2567.18427624973</v>
+        <v>2557.923122656587</v>
       </c>
       <c r="E86">
-        <v>781.664</v>
+        <v>812.2349999999999</v>
       </c>
       <c r="F86">
-        <v>2567.964</v>
+        <v>2598.535</v>
       </c>
       <c r="G86">
         <v>331.4</v>
@@ -8339,28 +8339,28 @@
         <v>680.4</v>
       </c>
       <c r="M86">
-        <v>220.5048912610216</v>
+        <v>223.1299494903194</v>
       </c>
       <c r="N86">
-        <v>459.8951087389784</v>
+        <v>457.2700505096806</v>
       </c>
       <c r="O86">
-        <v>73.58321739823656</v>
+        <v>73.16320808154889</v>
       </c>
       <c r="P86">
-        <v>386.3118913407419</v>
+        <v>384.1068424281317</v>
       </c>
       <c r="Q86">
-        <v>711.0118913407418</v>
+        <v>708.8068424281317</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2551782823663511</v>
+        <v>0.2687240122791464</v>
       </c>
       <c r="T86">
-        <v>2.882170867801597</v>
+        <v>3.06863293873146</v>
       </c>
       <c r="U86">
         <v>0.08586759442929168</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.085645838098801</v>
+        <v>3.049344122356463</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1016180642643862</v>
+        <v>0.1018194287208481</v>
       </c>
       <c r="C87">
-        <v>290.7881226565873</v>
+        <v>251.0225483628797</v>
       </c>
       <c r="D87">
-        <v>2557.923122656587</v>
+        <v>2548.728548362879</v>
       </c>
       <c r="E87">
-        <v>812.2349999999999</v>
+        <v>842.8059999999998</v>
       </c>
       <c r="F87">
-        <v>2598.535</v>
+        <v>2629.106</v>
       </c>
       <c r="G87">
         <v>331.4</v>
@@ -8421,28 +8421,28 @@
         <v>680.4</v>
       </c>
       <c r="M87">
-        <v>223.1299494903194</v>
+        <v>225.7550077196173</v>
       </c>
       <c r="N87">
-        <v>457.2700505096806</v>
+        <v>454.6449922803827</v>
       </c>
       <c r="O87">
-        <v>73.16320808154889</v>
+        <v>72.74319876486123</v>
       </c>
       <c r="P87">
-        <v>384.1068424281317</v>
+        <v>381.9017935155214</v>
       </c>
       <c r="Q87">
-        <v>708.8068424281317</v>
+        <v>706.6017935155214</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2687240122791464</v>
+        <v>0.2842048464651983</v>
       </c>
       <c r="T87">
-        <v>3.06863293873146</v>
+        <v>3.281732448365589</v>
       </c>
       <c r="U87">
         <v>0.08586759442929168</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.049344122356463</v>
+        <v>3.01388663256162</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1018194287208481</v>
+        <v>0.1077210331773099</v>
       </c>
       <c r="C88">
-        <v>251.0225483628797</v>
+        <v>-22.46409737995828</v>
       </c>
       <c r="D88">
-        <v>2548.728548362879</v>
+        <v>2305.812902620042</v>
       </c>
       <c r="E88">
-        <v>842.8059999999998</v>
+        <v>873.3770000000002</v>
       </c>
       <c r="F88">
-        <v>2629.106</v>
+        <v>2659.677</v>
       </c>
       <c r="G88">
         <v>331.4</v>
@@ -8503,45 +8503,45 @@
         <v>680.4</v>
       </c>
       <c r="M88">
-        <v>225.7550077196173</v>
+        <v>249.1255465489152</v>
       </c>
       <c r="N88">
-        <v>454.6449922803827</v>
+        <v>431.2744534510848</v>
       </c>
       <c r="O88">
-        <v>72.74319876486123</v>
+        <v>69.00391255217356</v>
       </c>
       <c r="P88">
-        <v>381.9017935155214</v>
+        <v>362.2705408989112</v>
       </c>
       <c r="Q88">
-        <v>706.6017935155214</v>
+        <v>686.9705408989112</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2842048464651983</v>
+        <v>0.3020673474491043</v>
       </c>
       <c r="T88">
-        <v>3.281732448365589</v>
+        <v>3.527616497943431</v>
       </c>
       <c r="U88">
-        <v>0.08586759442929168</v>
+        <v>0.09366759442929168</v>
       </c>
       <c r="V88">
         <v>0.16</v>
       </c>
       <c r="W88">
-        <v>0.072128779320605</v>
+        <v>0.07868077932060501</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y88">
-        <v>3.01388663256162</v>
+        <v>2.731153064892143</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1077210331773099</v>
+        <v>0.1079879176337718</v>
       </c>
       <c r="C89">
-        <v>-22.46409737995828</v>
+        <v>-62.93067913657069</v>
       </c>
       <c r="D89">
-        <v>2305.812902620042</v>
+        <v>2295.917320863429</v>
       </c>
       <c r="E89">
-        <v>873.3770000000002</v>
+        <v>903.9480000000001</v>
       </c>
       <c r="F89">
-        <v>2659.677</v>
+        <v>2690.248</v>
       </c>
       <c r="G89">
         <v>331.4</v>
@@ -8585,28 +8585,28 @@
         <v>680.4</v>
       </c>
       <c r="M89">
-        <v>249.1255465489152</v>
+        <v>251.9890585782131</v>
       </c>
       <c r="N89">
-        <v>431.2744534510848</v>
+        <v>428.4109414217869</v>
       </c>
       <c r="O89">
-        <v>69.00391255217356</v>
+        <v>68.5457506274859</v>
       </c>
       <c r="P89">
-        <v>362.2705408989112</v>
+        <v>359.865190794301</v>
       </c>
       <c r="Q89">
-        <v>686.9705408989112</v>
+        <v>684.5651907943011</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3020673474491043</v>
+        <v>0.3229069319303279</v>
       </c>
       <c r="T89">
-        <v>3.527616497943431</v>
+        <v>3.814481222450913</v>
       </c>
       <c r="U89">
         <v>0.09366759442929168</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.731153064892143</v>
+        <v>2.700117234609277</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1079879176337718</v>
+        <v>0.1082548020902336</v>
       </c>
       <c r="C90">
-        <v>-62.93067913657069</v>
+        <v>-103.312688470563</v>
       </c>
       <c r="D90">
-        <v>2295.917320863429</v>
+        <v>2286.106311529437</v>
       </c>
       <c r="E90">
-        <v>903.9480000000001</v>
+        <v>934.519</v>
       </c>
       <c r="F90">
-        <v>2690.248</v>
+        <v>2720.819</v>
       </c>
       <c r="G90">
         <v>331.4</v>
@@ -8667,28 +8667,28 @@
         <v>680.4</v>
       </c>
       <c r="M90">
-        <v>251.9890585782131</v>
+        <v>254.852570607511</v>
       </c>
       <c r="N90">
-        <v>428.4109414217869</v>
+        <v>425.547429392489</v>
       </c>
       <c r="O90">
-        <v>68.5457506274859</v>
+        <v>68.08758870279824</v>
       </c>
       <c r="P90">
-        <v>359.865190794301</v>
+        <v>357.4598406896907</v>
       </c>
       <c r="Q90">
-        <v>684.5651907943011</v>
+        <v>682.1598406896908</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.3229069319303279</v>
+        <v>0.347535531771774</v>
       </c>
       <c r="T90">
-        <v>3.814481222450913</v>
+        <v>4.153503169596118</v>
       </c>
       <c r="U90">
         <v>0.09366759442929168</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.700117234609277</v>
+        <v>2.669778838714791</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1082548020902336</v>
+        <v>0.1085216865466954</v>
       </c>
       <c r="C91">
-        <v>-103.312688470563</v>
+        <v>-143.6112049637986</v>
       </c>
       <c r="D91">
-        <v>2286.106311529437</v>
+        <v>2276.378795036201</v>
       </c>
       <c r="E91">
-        <v>934.519</v>
+        <v>965.0899999999999</v>
       </c>
       <c r="F91">
-        <v>2720.819</v>
+        <v>2751.39</v>
       </c>
       <c r="G91">
         <v>331.4</v>
@@ -8749,28 +8749,28 @@
         <v>680.4</v>
       </c>
       <c r="M91">
-        <v>254.852570607511</v>
+        <v>257.7160826368088</v>
       </c>
       <c r="N91">
-        <v>425.547429392489</v>
+        <v>422.6839173631911</v>
       </c>
       <c r="O91">
-        <v>68.08758870279824</v>
+        <v>67.62942677811058</v>
       </c>
       <c r="P91">
-        <v>357.4598406896907</v>
+        <v>355.0544905850805</v>
       </c>
       <c r="Q91">
-        <v>682.1598406896908</v>
+        <v>679.7544905850806</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.347535531771774</v>
+        <v>0.3770898515815094</v>
       </c>
       <c r="T91">
-        <v>4.153503169596118</v>
+        <v>4.560329506170365</v>
       </c>
       <c r="U91">
         <v>0.09366759442929168</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.669778838714791</v>
+        <v>2.640114629395738</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1085216865466954</v>
+        <v>0.1087885710031573</v>
       </c>
       <c r="C92">
-        <v>-143.6112049637986</v>
+        <v>-183.8272899012559</v>
       </c>
       <c r="D92">
-        <v>2276.378795036201</v>
+        <v>2266.733710098744</v>
       </c>
       <c r="E92">
-        <v>965.0899999999999</v>
+        <v>995.6609999999998</v>
       </c>
       <c r="F92">
-        <v>2751.39</v>
+        <v>2781.961</v>
       </c>
       <c r="G92">
         <v>331.4</v>
@@ -8831,28 +8831,28 @@
         <v>680.4</v>
       </c>
       <c r="M92">
-        <v>257.7160826368088</v>
+        <v>260.5795946661067</v>
       </c>
       <c r="N92">
-        <v>422.6839173631911</v>
+        <v>419.8204053338933</v>
       </c>
       <c r="O92">
-        <v>67.62942677811058</v>
+        <v>67.17126485342293</v>
       </c>
       <c r="P92">
-        <v>355.0544905850805</v>
+        <v>352.6491404804704</v>
       </c>
       <c r="Q92">
-        <v>679.7544905850806</v>
+        <v>677.3491404804704</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3770898515815094</v>
+        <v>0.4132117980156304</v>
       </c>
       <c r="T92">
-        <v>4.560329506170365</v>
+        <v>5.057561695316667</v>
       </c>
       <c r="U92">
         <v>0.09366759442929168</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.640114629395738</v>
+        <v>2.61110238072106</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1087885710031573</v>
+        <v>0.1090554554596191</v>
       </c>
       <c r="C93">
-        <v>-183.8272899012559</v>
+        <v>-223.9619866570183</v>
       </c>
       <c r="D93">
-        <v>2266.733710098744</v>
+        <v>2257.170013342982</v>
       </c>
       <c r="E93">
-        <v>995.6609999999998</v>
+        <v>1026.232</v>
       </c>
       <c r="F93">
-        <v>2781.961</v>
+        <v>2812.532</v>
       </c>
       <c r="G93">
         <v>331.4</v>
@@ -8913,28 +8913,28 @@
         <v>680.4</v>
       </c>
       <c r="M93">
-        <v>260.5795946661067</v>
+        <v>263.4431066954046</v>
       </c>
       <c r="N93">
-        <v>419.8204053338933</v>
+        <v>416.9568933045954</v>
       </c>
       <c r="O93">
-        <v>67.17126485342293</v>
+        <v>66.71310292873527</v>
       </c>
       <c r="P93">
-        <v>352.6491404804704</v>
+        <v>350.2437903758601</v>
       </c>
       <c r="Q93">
-        <v>677.3491404804704</v>
+        <v>674.9437903758601</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.4132117980156304</v>
+        <v>0.4583642310582817</v>
       </c>
       <c r="T93">
-        <v>5.057561695316667</v>
+        <v>5.679101931749545</v>
       </c>
       <c r="U93">
         <v>0.09366759442929168</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.61110238072106</v>
+        <v>2.582720833104526</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1090554554596191</v>
+        <v>0.109322339916081</v>
       </c>
       <c r="C94">
-        <v>-223.9619866570183</v>
+        <v>-264.0163210705309</v>
       </c>
       <c r="D94">
-        <v>2257.170013342982</v>
+        <v>2247.686678929469</v>
       </c>
       <c r="E94">
-        <v>1026.232</v>
+        <v>1056.803</v>
       </c>
       <c r="F94">
-        <v>2812.532</v>
+        <v>2843.103</v>
       </c>
       <c r="G94">
         <v>331.4</v>
@@ -8995,28 +8995,28 @@
         <v>680.4</v>
       </c>
       <c r="M94">
-        <v>263.4431066954046</v>
+        <v>266.3066187247024</v>
       </c>
       <c r="N94">
-        <v>416.9568933045954</v>
+        <v>414.0933812752975</v>
       </c>
       <c r="O94">
-        <v>66.71310292873527</v>
+        <v>66.25494100404761</v>
       </c>
       <c r="P94">
-        <v>350.2437903758601</v>
+        <v>347.8384402712499</v>
       </c>
       <c r="Q94">
-        <v>674.9437903758601</v>
+        <v>672.53844027125</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4583642310582817</v>
+        <v>0.5164173592559761</v>
       </c>
       <c r="T94">
-        <v>5.679101931749545</v>
+        <v>6.478225092877531</v>
       </c>
       <c r="U94">
         <v>0.09366759442929168</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.582720833104526</v>
+        <v>2.554949641350714</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.109322339916081</v>
+        <v>0.1095892243725428</v>
       </c>
       <c r="C95">
-        <v>-264.0163210705309</v>
+        <v>-303.9913018134102</v>
       </c>
       <c r="D95">
-        <v>2247.686678929469</v>
+        <v>2238.28269818659</v>
       </c>
       <c r="E95">
-        <v>1056.803</v>
+        <v>1087.374</v>
       </c>
       <c r="F95">
-        <v>2843.103</v>
+        <v>2873.674</v>
       </c>
       <c r="G95">
         <v>331.4</v>
@@ -9077,28 +9077,28 @@
         <v>680.4</v>
       </c>
       <c r="M95">
-        <v>266.3066187247024</v>
+        <v>269.1701307540004</v>
       </c>
       <c r="N95">
-        <v>414.0933812752975</v>
+        <v>411.2298692459996</v>
       </c>
       <c r="O95">
-        <v>66.25494100404761</v>
+        <v>65.79677907935994</v>
       </c>
       <c r="P95">
-        <v>347.8384402712499</v>
+        <v>345.4330901666397</v>
       </c>
       <c r="Q95">
-        <v>672.53844027125</v>
+        <v>670.1330901666397</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5164173592559761</v>
+        <v>0.5938215301862355</v>
       </c>
       <c r="T95">
-        <v>6.478225092877531</v>
+        <v>7.54372264104818</v>
       </c>
       <c r="U95">
         <v>0.09366759442929168</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.554949641350714</v>
+        <v>2.527769326017196</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1095892243725428</v>
+        <v>0.1098561088290047</v>
       </c>
       <c r="C96">
-        <v>-303.9913018134102</v>
+        <v>-343.8879207470882</v>
       </c>
       <c r="D96">
-        <v>2238.28269818659</v>
+        <v>2228.957079252912</v>
       </c>
       <c r="E96">
-        <v>1087.374</v>
+        <v>1117.945</v>
       </c>
       <c r="F96">
-        <v>2873.674</v>
+        <v>2904.245</v>
       </c>
       <c r="G96">
         <v>331.4</v>
@@ -9159,28 +9159,28 @@
         <v>680.4</v>
       </c>
       <c r="M96">
-        <v>269.1701307540004</v>
+        <v>272.0336427832982</v>
       </c>
       <c r="N96">
-        <v>411.2298692459996</v>
+        <v>408.3663572167018</v>
       </c>
       <c r="O96">
-        <v>65.79677907935994</v>
+        <v>65.33861715467228</v>
       </c>
       <c r="P96">
-        <v>345.4330901666397</v>
+        <v>343.0277400620295</v>
       </c>
       <c r="Q96">
-        <v>670.1330901666397</v>
+        <v>667.7277400620295</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5938215301862355</v>
+        <v>0.7021873694885988</v>
       </c>
       <c r="T96">
-        <v>7.54372264104818</v>
+        <v>9.03541920848709</v>
       </c>
       <c r="U96">
         <v>0.09366759442929168</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.527769326017196</v>
+        <v>2.501161227848594</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1098561088290047</v>
+        <v>0.1132679532854665</v>
       </c>
       <c r="C97">
-        <v>-343.8879207470882</v>
+        <v>-487.1769518153083</v>
       </c>
       <c r="D97">
-        <v>2228.957079252912</v>
+        <v>2116.239048184692</v>
       </c>
       <c r="E97">
-        <v>1117.945</v>
+        <v>1148.516</v>
       </c>
       <c r="F97">
-        <v>2904.245</v>
+        <v>2934.816</v>
       </c>
       <c r="G97">
         <v>331.4</v>
@@ -9241,45 +9241,45 @@
         <v>680.4</v>
       </c>
       <c r="M97">
-        <v>272.0336427832982</v>
+        <v>286.3429372125961</v>
       </c>
       <c r="N97">
-        <v>408.3663572167018</v>
+        <v>394.0570627874039</v>
       </c>
       <c r="O97">
-        <v>65.33861715467228</v>
+        <v>63.04913004598462</v>
       </c>
       <c r="P97">
-        <v>343.0277400620295</v>
+        <v>331.0079327414193</v>
       </c>
       <c r="Q97">
-        <v>667.7277400620295</v>
+        <v>655.7079327414193</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7021873694885988</v>
+        <v>0.8647361284421438</v>
       </c>
       <c r="T97">
-        <v>9.03541920848709</v>
+        <v>11.27296405964545</v>
       </c>
       <c r="U97">
-        <v>0.09366759442929168</v>
+        <v>0.09756759442929168</v>
       </c>
       <c r="V97">
         <v>0.16</v>
       </c>
       <c r="W97">
-        <v>0.07868077932060501</v>
+        <v>0.08195677932060501</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.501161227848594</v>
+        <v>2.376171756228215</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1132679532854665</v>
+        <v>0.1135675977419283</v>
       </c>
       <c r="C98">
-        <v>-487.1769518153078</v>
+        <v>-527.1052157654258</v>
       </c>
       <c r="D98">
-        <v>2116.239048184692</v>
+        <v>2106.881784234574</v>
       </c>
       <c r="E98">
-        <v>1148.516</v>
+        <v>1179.087</v>
       </c>
       <c r="F98">
-        <v>2934.816</v>
+        <v>2965.387</v>
       </c>
       <c r="G98">
         <v>331.4</v>
@@ -9323,28 +9323,28 @@
         <v>680.4</v>
       </c>
       <c r="M98">
-        <v>286.342937212596</v>
+        <v>289.325676141894</v>
       </c>
       <c r="N98">
-        <v>394.0570627874039</v>
+        <v>391.074323858106</v>
       </c>
       <c r="O98">
-        <v>63.04913004598463</v>
+        <v>62.57189181729697</v>
       </c>
       <c r="P98">
-        <v>331.0079327414193</v>
+        <v>328.5024320408091</v>
       </c>
       <c r="Q98">
-        <v>655.7079327414194</v>
+        <v>653.2024320408091</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.8647361284421415</v>
+        <v>1.135650726698049</v>
       </c>
       <c r="T98">
-        <v>11.27296405964542</v>
+        <v>15.00220547824268</v>
       </c>
       <c r="U98">
         <v>0.09756759442929168</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.376171756228215</v>
+        <v>2.351675140184625</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1135675977419283</v>
+        <v>0.1138672421983902</v>
       </c>
       <c r="C99">
-        <v>-527.1052157654258</v>
+        <v>-566.9510949389683</v>
       </c>
       <c r="D99">
-        <v>2106.881784234574</v>
+        <v>2097.606905061032</v>
       </c>
       <c r="E99">
-        <v>1179.087</v>
+        <v>1209.658</v>
       </c>
       <c r="F99">
-        <v>2965.387</v>
+        <v>2995.958</v>
       </c>
       <c r="G99">
         <v>331.4</v>
@@ -9405,28 +9405,28 @@
         <v>680.4</v>
       </c>
       <c r="M99">
-        <v>289.325676141894</v>
+        <v>292.3084150711919</v>
       </c>
       <c r="N99">
-        <v>391.074323858106</v>
+        <v>388.0915849288081</v>
       </c>
       <c r="O99">
-        <v>62.57189181729697</v>
+        <v>62.0946535886093</v>
       </c>
       <c r="P99">
-        <v>328.5024320408091</v>
+        <v>325.9969313401988</v>
       </c>
       <c r="Q99">
-        <v>653.2024320408091</v>
+        <v>650.6969313401989</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.135650726698049</v>
+        <v>1.677479923209862</v>
       </c>
       <c r="T99">
-        <v>15.00220547824268</v>
+        <v>22.4606883154372</v>
       </c>
       <c r="U99">
         <v>0.09756759442929168</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.351675140184625</v>
+        <v>2.3276784550807</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1138672421983902</v>
+        <v>0.114166886654852</v>
       </c>
       <c r="C100">
-        <v>-566.9510949389683</v>
+        <v>-606.7156725858604</v>
       </c>
       <c r="D100">
-        <v>2097.606905061032</v>
+        <v>2088.41332741414</v>
       </c>
       <c r="E100">
-        <v>1209.658</v>
+        <v>1240.229</v>
       </c>
       <c r="F100">
-        <v>2995.958</v>
+        <v>3026.529</v>
       </c>
       <c r="G100">
         <v>331.4</v>
@@ -9487,28 +9487,28 @@
         <v>680.4</v>
       </c>
       <c r="M100">
-        <v>292.3084150711919</v>
+        <v>295.2911540004897</v>
       </c>
       <c r="N100">
-        <v>388.0915849288081</v>
+        <v>385.1088459995103</v>
       </c>
       <c r="O100">
-        <v>62.0946535886093</v>
+        <v>61.61741535992164</v>
       </c>
       <c r="P100">
-        <v>325.9969313401988</v>
+        <v>323.4914306395886</v>
       </c>
       <c r="Q100">
-        <v>650.6969313401989</v>
+        <v>648.1914306395886</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.677479923209862</v>
+        <v>3.302967512745304</v>
       </c>
       <c r="T100">
-        <v>22.4606883154372</v>
+        <v>44.83613682702074</v>
       </c>
       <c r="U100">
         <v>0.09756759442929168</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.3276784550807</v>
+        <v>2.304166551494027</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.114166886654852</v>
-      </c>
-      <c r="C101">
-        <v>-606.7156725858604</v>
-      </c>
-      <c r="D101">
-        <v>2088.41332741414</v>
-      </c>
-      <c r="E101">
-        <v>1240.229</v>
-      </c>
-      <c r="F101">
-        <v>3026.529</v>
-      </c>
-      <c r="G101">
-        <v>331.4</v>
-      </c>
-      <c r="H101">
-        <v>1270.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1005.1</v>
-      </c>
-      <c r="K101">
-        <v>324.7</v>
-      </c>
-      <c r="L101">
-        <v>680.4</v>
-      </c>
-      <c r="M101">
-        <v>295.2911540004897</v>
-      </c>
-      <c r="N101">
-        <v>385.1088459995103</v>
-      </c>
-      <c r="O101">
-        <v>61.61741535992164</v>
-      </c>
-      <c r="P101">
-        <v>323.4914306395886</v>
-      </c>
-      <c r="Q101">
-        <v>648.1914306395886</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.302967512745304</v>
-      </c>
-      <c r="T101">
-        <v>44.83613682702074</v>
-      </c>
-      <c r="U101">
-        <v>0.09756759442929168</v>
-      </c>
-      <c r="V101">
-        <v>0.16</v>
-      </c>
-      <c r="W101">
-        <v>0.08195677932060501</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.304166551494027</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
